--- a/Assets/Localization/翻译文本/FlowyGraphLocalizationExport.xlsx
+++ b/Assets/Localization/翻译文本/FlowyGraphLocalizationExport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="1443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="1442">
   <si>
     <t>#var</t>
   </si>
@@ -23,12 +23,12 @@
     <t>lTips1</t>
   </si>
   <si>
+    <t>zh-CN</t>
+  </si>
+  <si>
     <t>lTips2</t>
   </si>
   <si>
-    <t>zh-CN</t>
-  </si>
-  <si>
     <t>en</t>
   </si>
   <si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>第一天_便利店冷藏车_节点图_调查冷藏车.95.0</t>
-  </si>
-  <si>
-    <t>AI</t>
   </si>
   <si>
     <t>全部完成</t>
@@ -4374,8 +4371,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4388,6 +4388,16 @@
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:H319"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1" style="1"/>
+    <col min="5" max="5" width="50" customWidth="1" style="1"/>
+    <col min="6" max="6" width="50" customWidth="1" style="1"/>
+    <col min="7" max="7" width="50" customWidth="1" style="1"/>
+    <col min="8" max="8" width="50" customWidth="1" style="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -4399,19 +4409,19 @@
       <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4425,19 +4435,19 @@
       <c r="C2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4445,6340 +4455,5389 @@
       <c r="B3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>12</v>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="F7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="G7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="H7" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="F8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="G8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="H8" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="F9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="G9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="0" t="s">
+      <c r="H9" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D10" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="G10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="0" t="s">
+      <c r="H10" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="0" t="s">
+      <c r="F11" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="G11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="0" t="s">
+      <c r="H11" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="H11" s="0" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="0" t="s">
+      <c r="F12" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="G12" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="0" t="s">
+      <c r="H12" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="H12" s="0" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="0" t="s">
+      <c r="F13" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="G13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G13" s="0" t="s">
+      <c r="H13" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="H13" s="0" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="0" t="s">
+      <c r="F14" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="G14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="0" t="s">
+      <c r="H14" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="H14" s="0" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D15" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="0" t="s">
+      <c r="F15" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="G15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G15" s="0" t="s">
-        <v>73</v>
-      </c>
-      <c r="H15" s="0" t="s">
-        <v>71</v>
+      <c r="H15" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="0" t="s">
+      <c r="F16" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="G16" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G16" s="0" t="s">
+      <c r="H16" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="H16" s="0" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="0" t="s">
+      <c r="F17" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="G17" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G17" s="0" t="s">
+      <c r="H17" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="H17" s="0" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="0" t="s">
+      <c r="F18" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="G18" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="0" t="s">
+      <c r="H18" s="1" t="s">
         <v>87</v>
-      </c>
-      <c r="H18" s="0" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="0" t="s">
+      <c r="F19" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="G19" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="G19" s="0" t="s">
+      <c r="H19" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="H19" s="0" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="0" t="s">
+      <c r="F20" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="G20" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G20" s="0" t="s">
-        <v>97</v>
-      </c>
-      <c r="H20" s="0" t="s">
-        <v>95</v>
+      <c r="H20" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="0" t="s">
+      <c r="F21" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="G21" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="G21" s="0" t="s">
+      <c r="H21" s="1" t="s">
         <v>101</v>
-      </c>
-      <c r="H21" s="0" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="s">
+        <v>102</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D22" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="0" t="s">
+      <c r="F22" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="G22" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G22" s="0" t="s">
+      <c r="H22" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="H22" s="0" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="0" t="s">
+      <c r="F23" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="G23" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G23" s="0" t="s">
+      <c r="H23" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="H23" s="0" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="0" t="s">
+      <c r="F24" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F24" s="0" t="s">
+      <c r="G24" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="0" t="s">
+      <c r="H24" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="H24" s="0" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="s">
+        <v>117</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D25" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="0" t="s">
+      <c r="F25" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="F25" s="0" t="s">
+      <c r="G25" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G25" s="0" t="s">
+      <c r="H25" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="0" t="s">
+      <c r="F26" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="F26" s="0" t="s">
+      <c r="G26" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="G26" s="0" t="s">
+      <c r="H26" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="H26" s="0" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="D27" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="0" t="s">
+      <c r="F27" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F27" s="0" t="s">
+      <c r="G27" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="G27" s="0" t="s">
+      <c r="H27" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="H27" s="0" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="s">
+        <v>132</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D28" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="0" t="s">
+      <c r="F28" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F28" s="0" t="s">
+      <c r="G28" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G28" s="0" t="s">
+      <c r="H28" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="H28" s="0" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="0" t="s">
+      <c r="F29" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F29" s="0" t="s">
+      <c r="G29" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="G29" s="0" t="s">
+      <c r="H29" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="H29" s="0" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="s">
+        <v>142</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D30" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="0" t="s">
+      <c r="F30" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="F30" s="0" t="s">
+      <c r="G30" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G30" s="0" t="s">
+      <c r="H30" s="1" t="s">
         <v>146</v>
-      </c>
-      <c r="H30" s="0" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D31" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="0" t="s">
+      <c r="F31" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F31" s="0" t="s">
+      <c r="G31" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G31" s="0" t="s">
+      <c r="H31" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="H31" s="0" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="s">
+        <v>152</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D32" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="0" t="s">
+      <c r="F32" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F32" s="0" t="s">
+      <c r="G32" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G32" s="0" t="s">
+      <c r="H32" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="H32" s="0" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="D33" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="0" t="s">
+      <c r="F33" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F33" s="0" t="s">
-        <v>160</v>
-      </c>
-      <c r="G33" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="H33" s="0" t="s">
-        <v>159</v>
+      <c r="G33" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="0" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D34" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="0" t="s">
+      <c r="F34" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F34" s="0" t="s">
+      <c r="G34" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G34" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="H34" s="0" t="s">
-        <v>162</v>
+      <c r="H34" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="0" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D35" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="0" t="s">
+      <c r="F35" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="F35" s="0" t="s">
+      <c r="G35" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G35" s="0" t="s">
+      <c r="H35" s="1" t="s">
         <v>168</v>
-      </c>
-      <c r="H35" s="0" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="0" t="s">
+        <v>169</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D36" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="0" t="s">
+      <c r="F36" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F36" s="0" t="s">
+      <c r="G36" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="G36" s="0" t="s">
+      <c r="H36" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="H36" s="0" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="D37" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="0" t="s">
+      <c r="F37" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F37" s="0" t="s">
+      <c r="G37" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="G37" s="0" t="s">
-        <v>178</v>
-      </c>
-      <c r="H37" s="0" t="s">
-        <v>176</v>
+      <c r="H37" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="s">
+        <v>178</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D38" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="0" t="s">
+      <c r="F38" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F38" s="0" t="s">
+      <c r="G38" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G38" s="0" t="s">
+      <c r="H38" s="1" t="s">
         <v>182</v>
-      </c>
-      <c r="H38" s="0" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="s">
+        <v>183</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D39" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="0" t="s">
+      <c r="F39" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="F39" s="0" t="s">
+      <c r="G39" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="G39" s="0" t="s">
+      <c r="H39" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="H39" s="0" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="s">
+        <v>188</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="0" t="s">
+      <c r="F40" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F40" s="0" t="s">
+      <c r="G40" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G40" s="0" t="s">
-        <v>192</v>
-      </c>
-      <c r="H40" s="0" t="s">
-        <v>190</v>
+      <c r="H40" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="0" t="s">
+        <v>192</v>
+      </c>
+      <c r="D41" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D41" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="0" t="s">
+      <c r="F41" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F41" s="0" t="s">
+      <c r="G41" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="G41" s="0" t="s">
+      <c r="H41" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="H41" s="0" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="s">
+        <v>197</v>
+      </c>
+      <c r="D42" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D42" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="0" t="s">
+      <c r="F42" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F42" s="0" t="s">
+      <c r="G42" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G42" s="0" t="s">
+      <c r="H42" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="H42" s="0" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="s">
+        <v>202</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="D43" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="0" t="s">
+      <c r="F43" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F43" s="0" t="s">
+      <c r="G43" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G43" s="0" t="s">
+      <c r="H43" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="H43" s="0" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="s">
+        <v>207</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D44" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="0" t="s">
+      <c r="F44" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F44" s="0" t="s">
+      <c r="G44" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="G44" s="0" t="s">
+      <c r="H44" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="H44" s="0" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="s">
+        <v>212</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="D45" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="0" t="s">
+      <c r="F45" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F45" s="0" t="s">
+      <c r="G45" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="G45" s="0" t="s">
-        <v>216</v>
-      </c>
-      <c r="H45" s="0" t="s">
-        <v>214</v>
+      <c r="H45" s="1" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="s">
+        <v>216</v>
+      </c>
+      <c r="D46" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D46" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="0" t="s">
+      <c r="F46" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="F46" s="0" t="s">
+      <c r="G46" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="G46" s="0" t="s">
+      <c r="H46" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="H46" s="0" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="0" t="s">
+        <v>221</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D47" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="0" t="s">
+      <c r="F47" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="F47" s="0" t="s">
+      <c r="G47" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="G47" s="0" t="s">
+      <c r="H47" s="1" t="s">
         <v>225</v>
-      </c>
-      <c r="H47" s="0" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="0" t="s">
+        <v>226</v>
+      </c>
+      <c r="D48" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="D48" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="0" t="s">
+      <c r="F48" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="F48" s="0" t="s">
+      <c r="G48" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="G48" s="0" t="s">
+      <c r="H48" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="H48" s="0" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="0" t="s">
+        <v>231</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D49" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="0" t="s">
+      <c r="F49" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="F49" s="0" t="s">
+      <c r="G49" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="G49" s="0" t="s">
+      <c r="H49" s="1" t="s">
         <v>235</v>
-      </c>
-      <c r="H49" s="0" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="0" t="s">
+        <v>236</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D50" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="0" t="s">
+      <c r="F50" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="F50" s="0" t="s">
+      <c r="G50" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="G50" s="0" t="s">
+      <c r="H50" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="H50" s="0" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="0" t="s">
+        <v>241</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D51" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="0" t="s">
+      <c r="F51" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="F51" s="0" t="s">
+      <c r="G51" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="G51" s="0" t="s">
+      <c r="H51" s="1" t="s">
         <v>245</v>
-      </c>
-      <c r="H51" s="0" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="0" t="s">
+        <v>246</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D52" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="0" t="s">
+      <c r="F52" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F52" s="0" t="s">
+      <c r="G52" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="G52" s="0" t="s">
+      <c r="H52" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="H52" s="0" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="0" t="s">
+        <v>251</v>
+      </c>
+      <c r="D53" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D53" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="0" t="s">
+      <c r="F53" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F53" s="0" t="s">
+      <c r="G53" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="G53" s="0" t="s">
+      <c r="H53" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="H53" s="0" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="0" t="s">
+        <v>256</v>
+      </c>
+      <c r="D54" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D54" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="0" t="s">
+      <c r="F54" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="F54" s="0" t="s">
+      <c r="G54" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="G54" s="0" t="s">
+      <c r="H54" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="H54" s="0" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D55" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="0" t="s">
+      <c r="F55" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="F55" s="0" t="s">
+      <c r="G55" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="G55" s="0" t="s">
+      <c r="H55" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="H55" s="0" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="D56" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="D56" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="0" t="s">
+      <c r="F56" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="F56" s="0" t="s">
+      <c r="G56" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="G56" s="0" t="s">
+      <c r="H56" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="H56" s="0" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="0" t="s">
+        <v>271</v>
+      </c>
+      <c r="D57" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="D57" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="0" t="s">
+      <c r="F57" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="F57" s="0" t="s">
+      <c r="G57" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="G57" s="0" t="s">
+      <c r="H57" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="H57" s="0" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="0" t="s">
+        <v>276</v>
+      </c>
+      <c r="D58" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="D58" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="0" t="s">
+      <c r="F58" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="F58" s="0" t="s">
+      <c r="G58" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G58" s="0" t="s">
+      <c r="H58" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="H58" s="0" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="0" t="s">
+        <v>281</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="D59" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="0" t="s">
+      <c r="F59" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F59" s="0" t="s">
+      <c r="G59" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="G59" s="0" t="s">
+      <c r="H59" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="H59" s="0" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="0" t="s">
+        <v>286</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="D60" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="0" t="s">
+      <c r="F60" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="F60" s="0" t="s">
+      <c r="G60" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="G60" s="0" t="s">
+      <c r="H60" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="H60" s="0" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="0" t="s">
+        <v>291</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="D61" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="0" t="s">
+      <c r="F61" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="F61" s="0" t="s">
+      <c r="G61" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="G61" s="0" t="s">
+      <c r="H61" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="H61" s="0" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="0" t="s">
+        <v>296</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D62" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="0" t="s">
+      <c r="F62" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F62" s="0" t="s">
+      <c r="G62" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="G62" s="0" t="s">
+      <c r="H62" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="H62" s="0" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="0" t="s">
+        <v>301</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="D63" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="0" t="s">
+      <c r="F63" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="F63" s="0" t="s">
+      <c r="G63" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="G63" s="0" t="s">
+      <c r="H63" s="1" t="s">
         <v>305</v>
-      </c>
-      <c r="H63" s="0" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="0" t="s">
+        <v>306</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="D64" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="0" t="s">
+      <c r="F64" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="F64" s="0" t="s">
+      <c r="G64" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="G64" s="0" t="s">
+      <c r="H64" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="H64" s="0" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="0" t="s">
+        <v>311</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="D65" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="0" t="s">
+      <c r="F65" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="F65" s="0" t="s">
+      <c r="G65" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="G65" s="0" t="s">
+      <c r="H65" s="1" t="s">
         <v>315</v>
-      </c>
-      <c r="H65" s="0" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="0" t="s">
+        <v>316</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="D66" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="0" t="s">
+      <c r="F66" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="F66" s="0" t="s">
+      <c r="G66" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="G66" s="0" t="s">
+      <c r="H66" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="H66" s="0" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="0" t="s">
+        <v>321</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="D67" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="0" t="s">
+      <c r="F67" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="F67" s="0" t="s">
+      <c r="G67" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="G67" s="0" t="s">
+      <c r="H67" s="1" t="s">
         <v>325</v>
-      </c>
-      <c r="H67" s="0" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="0" t="s">
+        <v>326</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="D68" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="0" t="s">
+      <c r="F68" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="F68" s="0" t="s">
+      <c r="G68" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="G68" s="0" t="s">
+      <c r="H68" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="H68" s="0" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="0" t="s">
+        <v>331</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="D69" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="0" t="s">
+      <c r="F69" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="F69" s="0" t="s">
+      <c r="G69" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="G69" s="0" t="s">
+      <c r="H69" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="H69" s="0" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="0" t="s">
+        <v>336</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D70" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="0" t="s">
+      <c r="F70" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="F70" s="0" t="s">
+      <c r="G70" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="G70" s="0" t="s">
+      <c r="H70" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="H70" s="0" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="0" t="s">
+        <v>341</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="D71" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="0" t="s">
+      <c r="F71" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="F71" s="0" t="s">
+      <c r="G71" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="G71" s="0" t="s">
+      <c r="H71" s="1" t="s">
         <v>345</v>
-      </c>
-      <c r="H71" s="0" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="D72" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="0" t="s">
+      <c r="F72" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F72" s="0" t="s">
+      <c r="G72" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="G72" s="0" t="s">
+      <c r="H72" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="H72" s="0" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="0" t="s">
+        <v>351</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="D73" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="0" t="s">
+      <c r="F73" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="F73" s="0" t="s">
+      <c r="G73" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="G73" s="0" t="s">
+      <c r="H73" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="H73" s="0" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="0" t="s">
+        <v>356</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="D74" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="0" t="s">
+      <c r="F74" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="F74" s="0" t="s">
+      <c r="G74" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="G74" s="0" t="s">
+      <c r="H74" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="H74" s="0" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="0" t="s">
+        <v>361</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="D75" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" s="0" t="s">
+      <c r="F75" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="F75" s="0" t="s">
+      <c r="G75" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="G75" s="0" t="s">
+      <c r="H75" s="1" t="s">
         <v>365</v>
-      </c>
-      <c r="H75" s="0" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="0" t="s">
+        <v>366</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="D76" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="0" t="s">
+      <c r="F76" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="F76" s="0" t="s">
+      <c r="G76" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="G76" s="0" t="s">
+      <c r="H76" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="H76" s="0" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="D77" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" s="0" t="s">
+      <c r="F77" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="F77" s="0" t="s">
+      <c r="G77" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="G77" s="0" t="s">
+      <c r="H77" s="1" t="s">
         <v>375</v>
-      </c>
-      <c r="H77" s="0" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D78" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="0" t="s">
+      <c r="F78" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="F78" s="0" t="s">
+      <c r="G78" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="G78" s="0" t="s">
+      <c r="H78" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="H78" s="0" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D79" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E79" s="0" t="s">
+      <c r="F79" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="F79" s="0" t="s">
+      <c r="G79" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="G79" s="0" t="s">
+      <c r="H79" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="H79" s="0" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="D80" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="0" t="s">
+      <c r="F80" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="F80" s="0" t="s">
+      <c r="G80" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="G80" s="0" t="s">
+      <c r="H80" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="H80" s="0" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="0" t="s">
+        <v>391</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D81" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" s="0" t="s">
+      <c r="F81" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="F81" s="0" t="s">
+      <c r="G81" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="G81" s="0" t="s">
+      <c r="H81" s="1" t="s">
         <v>395</v>
-      </c>
-      <c r="H81" s="0" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D82" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="0" t="s">
+      <c r="F82" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="F82" s="0" t="s">
+      <c r="G82" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="G82" s="0" t="s">
+      <c r="H82" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="H82" s="0" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="0" t="s">
+        <v>401</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="D83" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="0" t="s">
+      <c r="F83" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="F83" s="0" t="s">
+      <c r="G83" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="G83" s="0" t="s">
+      <c r="H83" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="H83" s="0" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="D84" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E84" s="0" t="s">
+      <c r="F84" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="F84" s="0" t="s">
+      <c r="G84" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="G84" s="0" t="s">
+      <c r="H84" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="H84" s="0" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D85" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E85" s="0" t="s">
+      <c r="F85" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="F85" s="0" t="s">
+      <c r="G85" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="G85" s="0" t="s">
+      <c r="H85" s="1" t="s">
         <v>415</v>
-      </c>
-      <c r="H85" s="0" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="D86" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="0" t="s">
+      <c r="F86" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="F86" s="0" t="s">
+      <c r="G86" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="G86" s="0" t="s">
+      <c r="H86" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="H86" s="0" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="D87" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E87" s="0" t="s">
+      <c r="F87" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="F87" s="0" t="s">
+      <c r="G87" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="G87" s="0" t="s">
+      <c r="H87" s="1" t="s">
         <v>425</v>
-      </c>
-      <c r="H87" s="0" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D88" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="0" t="s">
+      <c r="F88" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="F88" s="0" t="s">
+      <c r="G88" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="G88" s="0" t="s">
+      <c r="H88" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="H88" s="0" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="0" t="s">
+        <v>431</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D89" s="0" t="s">
+      <c r="G89" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="H89" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="E89" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="F89" s="0" t="s">
-        <v>433</v>
-      </c>
-      <c r="G89" s="0" t="s">
-        <v>434</v>
-      </c>
-      <c r="H89" s="0" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="0" t="s">
+        <v>434</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="D90" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="0" t="s">
+      <c r="F90" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="F90" s="0" t="s">
+      <c r="G90" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="G90" s="0" t="s">
+      <c r="H90" s="1" t="s">
         <v>438</v>
-      </c>
-      <c r="H90" s="0" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="D91" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E91" s="0" t="s">
+      <c r="F91" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G91" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="F91" s="0" t="s">
-        <v>264</v>
-      </c>
-      <c r="G91" s="0" t="s">
+      <c r="H91" s="1" t="s">
         <v>442</v>
-      </c>
-      <c r="H91" s="0" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="D92" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="0" t="s">
+      <c r="F92" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="F92" s="0" t="s">
+      <c r="G92" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="G92" s="0" t="s">
+      <c r="H92" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="H92" s="0" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D93" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E93" s="0" t="s">
+      <c r="F93" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="F93" s="0" t="s">
-        <v>451</v>
-      </c>
-      <c r="G93" s="0" t="s">
-        <v>450</v>
-      </c>
-      <c r="H93" s="0" t="s">
-        <v>450</v>
+      <c r="G93" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="D94" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" s="0" t="s">
+      <c r="F94" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="F94" s="0" t="s">
+      <c r="G94" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="G94" s="0" t="s">
-        <v>455</v>
-      </c>
-      <c r="H94" s="0" t="s">
-        <v>453</v>
+      <c r="H94" s="1" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="D95" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E95" s="0" t="s">
+      <c r="F95" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="F95" s="0" t="s">
+      <c r="G95" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="G95" s="0" t="s">
+      <c r="H95" s="1" t="s">
         <v>459</v>
-      </c>
-      <c r="H95" s="0" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="0" t="s">
+        <v>460</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D96" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="0" t="s">
+      <c r="F96" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="F96" s="0" t="s">
+      <c r="G96" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="G96" s="0" t="s">
+      <c r="H96" s="1" t="s">
         <v>464</v>
-      </c>
-      <c r="H96" s="0" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="D97" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="0" t="s">
+      <c r="F97" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="F97" s="0" t="s">
+      <c r="G97" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="G97" s="0" t="s">
+      <c r="H97" s="1" t="s">
         <v>469</v>
-      </c>
-      <c r="H97" s="0" t="s">
-        <v>470</v>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="0" t="s">
+        <v>470</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="D98" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="0" t="s">
+      <c r="F98" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="F98" s="0" t="s">
+      <c r="G98" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="G98" s="0" t="s">
+      <c r="H98" s="1" t="s">
         <v>474</v>
-      </c>
-      <c r="H98" s="0" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="D99" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="0" t="s">
+      <c r="F99" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="F99" s="0" t="s">
+      <c r="G99" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="G99" s="0" t="s">
+      <c r="H99" s="1" t="s">
         <v>479</v>
-      </c>
-      <c r="H99" s="0" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="D100" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="0" t="s">
+      <c r="F100" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="F100" s="0" t="s">
+      <c r="G100" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="G100" s="0" t="s">
+      <c r="H100" s="1" t="s">
         <v>484</v>
-      </c>
-      <c r="H100" s="0" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="0" t="s">
+        <v>485</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="D101" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E101" s="0" t="s">
+      <c r="F101" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="F101" s="0" t="s">
+      <c r="G101" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="G101" s="0" t="s">
+      <c r="H101" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="H101" s="0" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="0" t="s">
+        <v>490</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="D102" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="0" t="s">
+      <c r="F102" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="F102" s="0" t="s">
+      <c r="G102" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="G102" s="0" t="s">
+      <c r="H102" s="1" t="s">
         <v>494</v>
-      </c>
-      <c r="H102" s="0" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="D103" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" s="0" t="s">
+      <c r="F103" s="1" t="s">
         <v>497</v>
       </c>
-      <c r="F103" s="0" t="s">
+      <c r="G103" s="1" t="s">
         <v>498</v>
       </c>
-      <c r="G103" s="0" t="s">
+      <c r="H103" s="1" t="s">
         <v>499</v>
-      </c>
-      <c r="H103" s="0" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="104">
       <c r="B104" s="0" t="s">
+        <v>500</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>501</v>
       </c>
-      <c r="D104" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="0" t="s">
+      <c r="F104" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="F104" s="0" t="s">
+      <c r="G104" s="1" t="s">
         <v>503</v>
       </c>
-      <c r="G104" s="0" t="s">
+      <c r="H104" s="1" t="s">
         <v>504</v>
-      </c>
-      <c r="H104" s="0" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="105">
       <c r="B105" s="0" t="s">
+        <v>505</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>506</v>
       </c>
-      <c r="D105" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" s="0" t="s">
+      <c r="F105" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="F105" s="0" t="s">
+      <c r="G105" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="G105" s="0" t="s">
+      <c r="H105" s="1" t="s">
         <v>509</v>
-      </c>
-      <c r="H105" s="0" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="106">
       <c r="B106" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="D106" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="0" t="s">
+      <c r="F106" s="1" t="s">
         <v>512</v>
       </c>
-      <c r="F106" s="0" t="s">
+      <c r="G106" s="1" t="s">
         <v>513</v>
       </c>
-      <c r="G106" s="0" t="s">
+      <c r="H106" s="1" t="s">
         <v>514</v>
-      </c>
-      <c r="H106" s="0" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="107">
       <c r="B107" s="0" t="s">
+        <v>515</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="D107" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E107" s="0" t="s">
+      <c r="F107" s="1" t="s">
         <v>517</v>
       </c>
-      <c r="F107" s="0" t="s">
+      <c r="G107" s="1" t="s">
         <v>518</v>
       </c>
-      <c r="G107" s="0" t="s">
+      <c r="H107" s="1" t="s">
         <v>519</v>
-      </c>
-      <c r="H107" s="0" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="0" t="s">
+        <v>520</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>521</v>
       </c>
-      <c r="D108" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" s="0" t="s">
+      <c r="F108" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="F108" s="0" t="s">
+      <c r="G108" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="G108" s="0" t="s">
+      <c r="H108" s="1" t="s">
         <v>524</v>
-      </c>
-      <c r="H108" s="0" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="0" t="s">
+        <v>525</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="D109" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E109" s="0" t="s">
+      <c r="F109" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="F109" s="0" t="s">
+      <c r="G109" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="G109" s="0" t="s">
+      <c r="H109" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="H109" s="0" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="0" t="s">
+        <v>530</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>531</v>
       </c>
-      <c r="D110" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" s="0" t="s">
+      <c r="F110" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="F110" s="0" t="s">
+      <c r="G110" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="G110" s="0" t="s">
+      <c r="H110" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="H110" s="0" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="0" t="s">
+        <v>535</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="D111" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="0" t="s">
+      <c r="F111" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="F111" s="0" t="s">
+      <c r="G111" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="G111" s="0" t="s">
+      <c r="H111" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="H111" s="0" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="0" t="s">
+        <v>540</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>541</v>
       </c>
-      <c r="D112" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="0" t="s">
+      <c r="F112" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="F112" s="0" t="s">
+      <c r="G112" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="G112" s="0" t="s">
+      <c r="H112" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="H112" s="0" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="0" t="s">
+        <v>545</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="D113" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" s="0" t="s">
+      <c r="F113" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="F113" s="0" t="s">
+      <c r="G113" s="1" t="s">
         <v>548</v>
       </c>
-      <c r="G113" s="0" t="s">
+      <c r="H113" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="H113" s="0" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="0" t="s">
+        <v>550</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="D114" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="0" t="s">
+      <c r="F114" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="F114" s="0" t="s">
+      <c r="G114" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="G114" s="0" t="s">
+      <c r="H114" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="H114" s="0" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="115">
       <c r="B115" s="0" t="s">
+        <v>555</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>556</v>
       </c>
-      <c r="D115" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" s="0" t="s">
+      <c r="F115" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="F115" s="0" t="s">
+      <c r="G115" s="1" t="s">
         <v>558</v>
       </c>
-      <c r="G115" s="0" t="s">
+      <c r="H115" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="H115" s="0" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="116">
       <c r="B116" s="0" t="s">
+        <v>560</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>561</v>
       </c>
-      <c r="D116" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E116" s="0" t="s">
+      <c r="F116" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="F116" s="0" t="s">
+      <c r="G116" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="G116" s="0" t="s">
+      <c r="H116" s="1" t="s">
         <v>564</v>
-      </c>
-      <c r="H116" s="0" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="117">
       <c r="B117" s="0" t="s">
+        <v>565</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="D117" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E117" s="0" t="s">
+      <c r="F117" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="F117" s="0" t="s">
+      <c r="G117" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="G117" s="0" t="s">
+      <c r="H117" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="H117" s="0" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="118">
       <c r="B118" s="0" t="s">
+        <v>570</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="D118" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E118" s="0" t="s">
+      <c r="F118" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="F118" s="0" t="s">
+      <c r="G118" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="G118" s="0" t="s">
-        <v>574</v>
-      </c>
-      <c r="H118" s="0" t="s">
-        <v>572</v>
+      <c r="H118" s="1" t="s">
+        <v>571</v>
       </c>
     </row>
     <row r="119">
       <c r="B119" s="0" t="s">
+        <v>574</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="D119" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E119" s="0" t="s">
+      <c r="F119" s="1" t="s">
         <v>576</v>
       </c>
-      <c r="F119" s="0" t="s">
+      <c r="G119" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="G119" s="0" t="s">
+      <c r="H119" s="1" t="s">
         <v>578</v>
-      </c>
-      <c r="H119" s="0" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="120">
       <c r="B120" s="0" t="s">
+        <v>579</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>580</v>
       </c>
-      <c r="D120" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" s="0" t="s">
+      <c r="F120" s="1" t="s">
         <v>581</v>
       </c>
-      <c r="F120" s="0" t="s">
+      <c r="G120" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="G120" s="0" t="s">
+      <c r="H120" s="1" t="s">
         <v>583</v>
-      </c>
-      <c r="H120" s="0" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="121">
       <c r="B121" s="0" t="s">
+        <v>584</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="D121" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="0" t="s">
+      <c r="F121" s="1" t="s">
         <v>586</v>
       </c>
-      <c r="F121" s="0" t="s">
+      <c r="G121" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="G121" s="0" t="s">
+      <c r="H121" s="1" t="s">
         <v>588</v>
-      </c>
-      <c r="H121" s="0" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="122">
       <c r="B122" s="0" t="s">
+        <v>589</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="D122" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="0" t="s">
+      <c r="F122" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="F122" s="0" t="s">
+      <c r="G122" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="G122" s="0" t="s">
-        <v>593</v>
-      </c>
-      <c r="H122" s="0" t="s">
-        <v>591</v>
+      <c r="H122" s="1" t="s">
+        <v>590</v>
       </c>
     </row>
     <row r="123">
       <c r="B123" s="0" t="s">
+        <v>593</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>594</v>
       </c>
-      <c r="D123" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E123" s="0" t="s">
+      <c r="F123" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="F123" s="0" t="s">
+      <c r="G123" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="G123" s="0" t="s">
+      <c r="H123" s="1" t="s">
         <v>597</v>
-      </c>
-      <c r="H123" s="0" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="124">
       <c r="B124" s="0" t="s">
+        <v>598</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="D124" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="0" t="s">
+      <c r="F124" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="F124" s="0" t="s">
+      <c r="G124" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="G124" s="0" t="s">
+      <c r="H124" s="1" t="s">
         <v>602</v>
-      </c>
-      <c r="H124" s="0" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" s="0" t="s">
+        <v>603</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="D125" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" s="0" t="s">
+      <c r="F125" s="1" t="s">
         <v>605</v>
       </c>
-      <c r="F125" s="0" t="s">
+      <c r="G125" s="1" t="s">
         <v>606</v>
       </c>
-      <c r="G125" s="0" t="s">
+      <c r="H125" s="1" t="s">
         <v>607</v>
-      </c>
-      <c r="H125" s="0" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="126">
       <c r="B126" s="0" t="s">
-        <v>609</v>
-      </c>
-      <c r="D126" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E126" s="0" t="s">
+        <v>608</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="F126" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="F126" s="0" t="s">
+      <c r="G126" s="1" t="s">
         <v>543</v>
       </c>
-      <c r="G126" s="0" t="s">
+      <c r="H126" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="H126" s="0" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="127">
       <c r="B127" s="0" t="s">
+        <v>609</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>610</v>
       </c>
-      <c r="D127" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E127" s="0" t="s">
+      <c r="F127" s="1" t="s">
         <v>611</v>
       </c>
-      <c r="F127" s="0" t="s">
+      <c r="G127" s="1" t="s">
         <v>612</v>
       </c>
-      <c r="G127" s="0" t="s">
+      <c r="H127" s="1" t="s">
         <v>613</v>
-      </c>
-      <c r="H127" s="0" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="128">
       <c r="B128" s="0" t="s">
+        <v>614</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="D128" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E128" s="0" t="s">
+      <c r="F128" s="1" t="s">
         <v>616</v>
       </c>
-      <c r="F128" s="0" t="s">
+      <c r="G128" s="1" t="s">
         <v>617</v>
       </c>
-      <c r="G128" s="0" t="s">
+      <c r="H128" s="1" t="s">
         <v>618</v>
-      </c>
-      <c r="H128" s="0" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="129">
       <c r="B129" s="0" t="s">
+        <v>619</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>620</v>
       </c>
-      <c r="D129" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E129" s="0" t="s">
+      <c r="F129" s="1" t="s">
         <v>621</v>
       </c>
-      <c r="F129" s="0" t="s">
+      <c r="G129" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="G129" s="0" t="s">
-        <v>623</v>
-      </c>
-      <c r="H129" s="0" t="s">
-        <v>621</v>
+      <c r="H129" s="1" t="s">
+        <v>620</v>
       </c>
     </row>
     <row r="130">
       <c r="B130" s="0" t="s">
+        <v>623</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="D130" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E130" s="0" t="s">
+      <c r="F130" s="1" t="s">
         <v>625</v>
       </c>
-      <c r="F130" s="0" t="s">
+      <c r="G130" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="G130" s="0" t="s">
+      <c r="H130" s="1" t="s">
         <v>627</v>
-      </c>
-      <c r="H130" s="0" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="131">
       <c r="B131" s="0" t="s">
+        <v>628</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>629</v>
       </c>
-      <c r="D131" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E131" s="0" t="s">
+      <c r="F131" s="1" t="s">
         <v>630</v>
       </c>
-      <c r="F131" s="0" t="s">
+      <c r="G131" s="1" t="s">
         <v>631</v>
       </c>
-      <c r="G131" s="0" t="s">
+      <c r="H131" s="1" t="s">
         <v>632</v>
-      </c>
-      <c r="H131" s="0" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="132">
       <c r="B132" s="0" t="s">
+        <v>633</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="D132" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" s="0" t="s">
+      <c r="F132" s="1" t="s">
         <v>635</v>
       </c>
-      <c r="F132" s="0" t="s">
+      <c r="G132" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="G132" s="0" t="s">
+      <c r="H132" s="1" t="s">
         <v>637</v>
-      </c>
-      <c r="H132" s="0" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="133">
       <c r="B133" s="0" t="s">
+        <v>638</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="D133" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E133" s="0" t="s">
+      <c r="F133" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="F133" s="0" t="s">
+      <c r="G133" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="G133" s="0" t="s">
+      <c r="H133" s="1" t="s">
         <v>642</v>
-      </c>
-      <c r="H133" s="0" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="134">
       <c r="B134" s="0" t="s">
+        <v>643</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>644</v>
       </c>
-      <c r="D134" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E134" s="0" t="s">
+      <c r="F134" s="1" t="s">
         <v>645</v>
       </c>
-      <c r="F134" s="0" t="s">
+      <c r="G134" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="G134" s="0" t="s">
+      <c r="H134" s="1" t="s">
         <v>647</v>
-      </c>
-      <c r="H134" s="0" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="135">
       <c r="B135" s="0" t="s">
+        <v>648</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F135" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="D135" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E135" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="F135" s="0" t="s">
+      <c r="G135" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="G135" s="0" t="s">
-        <v>651</v>
-      </c>
-      <c r="H135" s="0" t="s">
-        <v>127</v>
+      <c r="H135" s="1" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" s="0" t="s">
+        <v>651</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="D136" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E136" s="0" t="s">
+      <c r="F136" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="F136" s="0" t="s">
+      <c r="G136" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="G136" s="0" t="s">
+      <c r="H136" s="1" t="s">
         <v>655</v>
-      </c>
-      <c r="H136" s="0" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" s="0" t="s">
+        <v>656</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>657</v>
       </c>
-      <c r="D137" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E137" s="0" t="s">
+      <c r="F137" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="F137" s="0" t="s">
+      <c r="G137" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="G137" s="0" t="s">
+      <c r="H137" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="H137" s="0" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="138">
       <c r="B138" s="0" t="s">
+        <v>661</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>662</v>
       </c>
-      <c r="D138" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E138" s="0" t="s">
+      <c r="F138" s="1" t="s">
         <v>663</v>
       </c>
-      <c r="F138" s="0" t="s">
+      <c r="G138" s="1" t="s">
         <v>664</v>
       </c>
-      <c r="G138" s="0" t="s">
+      <c r="H138" s="1" t="s">
         <v>665</v>
-      </c>
-      <c r="H138" s="0" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="139">
       <c r="B139" s="0" t="s">
+        <v>666</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="D139" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E139" s="0" t="s">
+      <c r="F139" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="F139" s="0" t="s">
+      <c r="G139" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="G139" s="0" t="s">
+      <c r="H139" s="1" t="s">
         <v>670</v>
-      </c>
-      <c r="H139" s="0" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" s="0" t="s">
+        <v>671</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>672</v>
       </c>
-      <c r="D140" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E140" s="0" t="s">
+      <c r="F140" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="F140" s="0" t="s">
+      <c r="G140" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="G140" s="0" t="s">
+      <c r="H140" s="1" t="s">
         <v>675</v>
-      </c>
-      <c r="H140" s="0" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="141">
       <c r="B141" s="0" t="s">
+        <v>676</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="D141" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E141" s="0" t="s">
+      <c r="F141" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="F141" s="0" t="s">
+      <c r="G141" s="1" t="s">
         <v>679</v>
       </c>
-      <c r="G141" s="0" t="s">
+      <c r="H141" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="H141" s="0" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="142">
       <c r="B142" s="0" t="s">
+        <v>681</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="D142" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E142" s="0" t="s">
+      <c r="F142" s="1" t="s">
         <v>683</v>
       </c>
-      <c r="F142" s="0" t="s">
+      <c r="G142" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="G142" s="0" t="s">
+      <c r="H142" s="1" t="s">
         <v>685</v>
-      </c>
-      <c r="H142" s="0" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="143">
       <c r="B143" s="0" t="s">
+        <v>686</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="D143" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E143" s="0" t="s">
+      <c r="F143" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="F143" s="0" t="s">
+      <c r="G143" s="1" t="s">
         <v>689</v>
       </c>
-      <c r="G143" s="0" t="s">
+      <c r="H143" s="1" t="s">
         <v>690</v>
-      </c>
-      <c r="H143" s="0" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="144">
       <c r="B144" s="0" t="s">
+        <v>691</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="D144" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E144" s="0" t="s">
+      <c r="F144" s="1" t="s">
         <v>693</v>
       </c>
-      <c r="F144" s="0" t="s">
+      <c r="G144" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="G144" s="0" t="s">
+      <c r="H144" s="1" t="s">
         <v>695</v>
-      </c>
-      <c r="H144" s="0" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="145">
       <c r="B145" s="0" t="s">
+        <v>696</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="D145" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E145" s="0" t="s">
+      <c r="F145" s="1" t="s">
         <v>698</v>
       </c>
-      <c r="F145" s="0" t="s">
+      <c r="G145" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="G145" s="0" t="s">
+      <c r="H145" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="H145" s="0" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="146">
       <c r="B146" s="0" t="s">
+        <v>701</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>702</v>
       </c>
-      <c r="D146" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E146" s="0" t="s">
+      <c r="F146" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="F146" s="0" t="s">
+      <c r="G146" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="G146" s="0" t="s">
+      <c r="H146" s="1" t="s">
         <v>705</v>
-      </c>
-      <c r="H146" s="0" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="147">
       <c r="B147" s="0" t="s">
+        <v>706</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="D147" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E147" s="0" t="s">
+      <c r="F147" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="F147" s="0" t="s">
+      <c r="G147" s="1" t="s">
         <v>709</v>
       </c>
-      <c r="G147" s="0" t="s">
+      <c r="H147" s="1" t="s">
         <v>710</v>
-      </c>
-      <c r="H147" s="0" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="148">
       <c r="B148" s="0" t="s">
+        <v>711</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>712</v>
       </c>
-      <c r="D148" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E148" s="0" t="s">
+      <c r="F148" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="F148" s="0" t="s">
+      <c r="G148" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="G148" s="0" t="s">
+      <c r="H148" s="1" t="s">
         <v>715</v>
-      </c>
-      <c r="H148" s="0" t="s">
-        <v>716</v>
       </c>
     </row>
     <row r="149">
       <c r="B149" s="0" t="s">
+        <v>716</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="D149" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E149" s="0" t="s">
+      <c r="F149" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="F149" s="0" t="s">
+      <c r="G149" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="G149" s="0" t="s">
+      <c r="H149" s="1" t="s">
         <v>720</v>
-      </c>
-      <c r="H149" s="0" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="150">
       <c r="B150" s="0" t="s">
+        <v>721</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="D150" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E150" s="0" t="s">
+      <c r="F150" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="F150" s="0" t="s">
+      <c r="G150" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="G150" s="0" t="s">
+      <c r="H150" s="1" t="s">
         <v>725</v>
-      </c>
-      <c r="H150" s="0" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="151">
       <c r="B151" s="0" t="s">
+        <v>726</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="D151" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E151" s="0" t="s">
+      <c r="F151" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="F151" s="0" t="s">
+      <c r="G151" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="G151" s="0" t="s">
+      <c r="H151" s="1" t="s">
         <v>730</v>
-      </c>
-      <c r="H151" s="0" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="152">
       <c r="B152" s="0" t="s">
+        <v>731</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="G152" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="D152" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E152" s="0" t="s">
-        <v>625</v>
-      </c>
-      <c r="F152" s="0" t="s">
-        <v>626</v>
-      </c>
-      <c r="G152" s="0" t="s">
-        <v>733</v>
-      </c>
-      <c r="H152" s="0" t="s">
-        <v>628</v>
+      <c r="H152" s="1" t="s">
+        <v>627</v>
       </c>
     </row>
     <row r="153">
       <c r="B153" s="0" t="s">
+        <v>733</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="D153" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E153" s="0" t="s">
+      <c r="F153" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="F153" s="0" t="s">
+      <c r="G153" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="G153" s="0" t="s">
+      <c r="H153" s="1" t="s">
         <v>737</v>
-      </c>
-      <c r="H153" s="0" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="154">
       <c r="B154" s="0" t="s">
+        <v>738</v>
+      </c>
+      <c r="D154" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="D154" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E154" s="0" t="s">
+      <c r="F154" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="F154" s="0" t="s">
+      <c r="G154" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="G154" s="0" t="s">
+      <c r="H154" s="1" t="s">
         <v>742</v>
-      </c>
-      <c r="H154" s="0" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" s="0" t="s">
+        <v>743</v>
+      </c>
+      <c r="D155" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="D155" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E155" s="0" t="s">
+      <c r="F155" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="F155" s="0" t="s">
+      <c r="G155" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="G155" s="0" t="s">
+      <c r="H155" s="1" t="s">
         <v>747</v>
-      </c>
-      <c r="H155" s="0" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="156">
       <c r="B156" s="0" t="s">
+        <v>748</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>749</v>
       </c>
-      <c r="D156" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E156" s="0" t="s">
+      <c r="F156" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="F156" s="0" t="s">
+      <c r="G156" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="G156" s="0" t="s">
+      <c r="H156" s="1" t="s">
         <v>752</v>
-      </c>
-      <c r="H156" s="0" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="157">
       <c r="B157" s="0" t="s">
+        <v>753</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="D157" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E157" s="0" t="s">
+      <c r="F157" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="F157" s="0" t="s">
+      <c r="G157" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="G157" s="0" t="s">
+      <c r="H157" s="1" t="s">
         <v>757</v>
-      </c>
-      <c r="H157" s="0" t="s">
-        <v>758</v>
       </c>
     </row>
     <row r="158">
       <c r="B158" s="0" t="s">
+        <v>758</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="F158" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="D158" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E158" s="0" t="s">
-        <v>658</v>
-      </c>
-      <c r="F158" s="0" t="s">
-        <v>760</v>
-      </c>
-      <c r="G158" s="0" t="s">
+      <c r="G158" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="H158" s="1" t="s">
         <v>660</v>
-      </c>
-      <c r="H158" s="0" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="159">
       <c r="B159" s="0" t="s">
+        <v>760</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="D159" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E159" s="0" t="s">
+      <c r="F159" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="F159" s="0" t="s">
+      <c r="G159" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="G159" s="0" t="s">
+      <c r="H159" s="1" t="s">
         <v>764</v>
-      </c>
-      <c r="H159" s="0" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="160">
       <c r="B160" s="0" t="s">
+        <v>765</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="D160" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E160" s="0" t="s">
+      <c r="F160" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="F160" s="0" t="s">
+      <c r="G160" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="G160" s="0" t="s">
+      <c r="H160" s="1" t="s">
         <v>769</v>
-      </c>
-      <c r="H160" s="0" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="161">
       <c r="B161" s="0" t="s">
+        <v>770</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="D161" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E161" s="0" t="s">
+      <c r="F161" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="F161" s="0" t="s">
+      <c r="G161" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="G161" s="0" t="s">
+      <c r="H161" s="1" t="s">
         <v>774</v>
-      </c>
-      <c r="H161" s="0" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="162">
       <c r="B162" s="0" t="s">
+        <v>775</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="D162" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E162" s="0" t="s">
+      <c r="F162" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="F162" s="0" t="s">
+      <c r="G162" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="G162" s="0" t="s">
+      <c r="H162" s="1" t="s">
         <v>779</v>
-      </c>
-      <c r="H162" s="0" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="163">
       <c r="B163" s="0" t="s">
+        <v>780</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="D163" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E163" s="0" t="s">
+      <c r="F163" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="F163" s="0" t="s">
+      <c r="G163" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="G163" s="0" t="s">
+      <c r="H163" s="1" t="s">
         <v>784</v>
-      </c>
-      <c r="H163" s="0" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="164">
       <c r="B164" s="0" t="s">
+        <v>785</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="D164" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E164" s="0" t="s">
+      <c r="F164" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="F164" s="0" t="s">
+      <c r="G164" s="1" t="s">
         <v>788</v>
       </c>
-      <c r="G164" s="0" t="s">
+      <c r="H164" s="1" t="s">
         <v>789</v>
-      </c>
-      <c r="H164" s="0" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="165">
       <c r="B165" s="0" t="s">
+        <v>790</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="D165" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E165" s="0" t="s">
+      <c r="F165" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="F165" s="0" t="s">
+      <c r="G165" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="G165" s="0" t="s">
+      <c r="H165" s="1" t="s">
         <v>794</v>
-      </c>
-      <c r="H165" s="0" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="166">
       <c r="B166" s="0" t="s">
+        <v>795</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="D166" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E166" s="0" t="s">
+      <c r="F166" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="F166" s="0" t="s">
+      <c r="G166" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="G166" s="0" t="s">
+      <c r="H166" s="1" t="s">
         <v>799</v>
-      </c>
-      <c r="H166" s="0" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="167">
       <c r="B167" s="0" t="s">
+        <v>800</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="D167" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E167" s="0" t="s">
+      <c r="F167" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="F167" s="0" t="s">
+      <c r="G167" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="G167" s="0" t="s">
+      <c r="H167" s="1" t="s">
         <v>804</v>
-      </c>
-      <c r="H167" s="0" t="s">
-        <v>805</v>
       </c>
     </row>
     <row r="168">
       <c r="B168" s="0" t="s">
+        <v>805</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="D168" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E168" s="0" t="s">
+      <c r="F168" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="F168" s="0" t="s">
+      <c r="G168" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="G168" s="0" t="s">
+      <c r="H168" s="1" t="s">
         <v>809</v>
-      </c>
-      <c r="H168" s="0" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="169">
       <c r="B169" s="0" t="s">
+        <v>810</v>
+      </c>
+      <c r="D169" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="D169" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E169" s="0" t="s">
+      <c r="F169" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="F169" s="0" t="s">
+      <c r="G169" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="G169" s="0" t="s">
+      <c r="H169" s="1" t="s">
         <v>814</v>
-      </c>
-      <c r="H169" s="0" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" s="0" t="s">
+        <v>815</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="D170" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E170" s="0" t="s">
+      <c r="F170" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="F170" s="0" t="s">
+      <c r="G170" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="G170" s="0" t="s">
+      <c r="H170" s="1" t="s">
         <v>819</v>
-      </c>
-      <c r="H170" s="0" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="171">
       <c r="B171" s="0" t="s">
+        <v>820</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="D171" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E171" s="0" t="s">
+      <c r="F171" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="F171" s="0" t="s">
+      <c r="G171" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="G171" s="0" t="s">
+      <c r="H171" s="1" t="s">
         <v>824</v>
-      </c>
-      <c r="H171" s="0" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="172">
       <c r="B172" s="0" t="s">
+        <v>825</v>
+      </c>
+      <c r="D172" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="D172" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E172" s="0" t="s">
+      <c r="F172" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="F172" s="0" t="s">
+      <c r="G172" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="G172" s="0" t="s">
+      <c r="H172" s="1" t="s">
         <v>829</v>
-      </c>
-      <c r="H172" s="0" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="173">
       <c r="B173" s="0" t="s">
+        <v>830</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>831</v>
       </c>
-      <c r="D173" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E173" s="0" t="s">
+      <c r="F173" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="F173" s="0" t="s">
+      <c r="G173" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="G173" s="0" t="s">
+      <c r="H173" s="1" t="s">
         <v>834</v>
-      </c>
-      <c r="H173" s="0" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="174">
       <c r="B174" s="0" t="s">
+        <v>835</v>
+      </c>
+      <c r="D174" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="D174" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E174" s="0" t="s">
+      <c r="F174" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="F174" s="0" t="s">
+      <c r="G174" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="G174" s="0" t="s">
+      <c r="H174" s="1" t="s">
         <v>839</v>
-      </c>
-      <c r="H174" s="0" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="175">
       <c r="B175" s="0" t="s">
+        <v>840</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="D175" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E175" s="0" t="s">
+      <c r="F175" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="F175" s="0" t="s">
+      <c r="G175" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="G175" s="0" t="s">
+      <c r="H175" s="1" t="s">
         <v>844</v>
-      </c>
-      <c r="H175" s="0" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="176">
       <c r="B176" s="0" t="s">
+        <v>845</v>
+      </c>
+      <c r="D176" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="D176" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E176" s="0" t="s">
+      <c r="F176" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="F176" s="0" t="s">
+      <c r="G176" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="G176" s="0" t="s">
+      <c r="H176" s="1" t="s">
         <v>849</v>
-      </c>
-      <c r="H176" s="0" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="177">
       <c r="B177" s="0" t="s">
+        <v>850</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="D177" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E177" s="0" t="s">
+      <c r="F177" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="F177" s="0" t="s">
+      <c r="G177" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="G177" s="0" t="s">
+      <c r="H177" s="1" t="s">
         <v>854</v>
-      </c>
-      <c r="H177" s="0" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="178">
       <c r="B178" s="0" t="s">
+        <v>855</v>
+      </c>
+      <c r="D178" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="D178" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E178" s="0" t="s">
+      <c r="F178" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="F178" s="0" t="s">
+      <c r="G178" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="G178" s="0" t="s">
+      <c r="H178" s="1" t="s">
         <v>859</v>
-      </c>
-      <c r="H178" s="0" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="179">
       <c r="B179" s="0" t="s">
+        <v>860</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="D179" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E179" s="0" t="s">
+      <c r="F179" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="F179" s="0" t="s">
+      <c r="G179" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="G179" s="0" t="s">
+      <c r="H179" s="1" t="s">
         <v>864</v>
-      </c>
-      <c r="H179" s="0" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="180">
       <c r="B180" s="0" t="s">
+        <v>865</v>
+      </c>
+      <c r="D180" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="D180" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E180" s="0" t="s">
+      <c r="F180" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="F180" s="0" t="s">
+      <c r="G180" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="G180" s="0" t="s">
+      <c r="H180" s="1" t="s">
         <v>869</v>
-      </c>
-      <c r="H180" s="0" t="s">
-        <v>870</v>
       </c>
     </row>
     <row r="181">
       <c r="B181" s="0" t="s">
+        <v>870</v>
+      </c>
+      <c r="D181" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="D181" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E181" s="0" t="s">
+      <c r="F181" s="1" t="s">
         <v>872</v>
       </c>
-      <c r="F181" s="0" t="s">
+      <c r="G181" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="G181" s="0" t="s">
+      <c r="H181" s="1" t="s">
         <v>874</v>
-      </c>
-      <c r="H181" s="0" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="182">
       <c r="B182" s="0" t="s">
+        <v>875</v>
+      </c>
+      <c r="D182" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="D182" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E182" s="0" t="s">
+      <c r="F182" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="F182" s="0" t="s">
+      <c r="G182" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="G182" s="0" t="s">
+      <c r="H182" s="1" t="s">
         <v>879</v>
-      </c>
-      <c r="H182" s="0" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="183">
       <c r="B183" s="0" t="s">
+        <v>880</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="D183" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E183" s="0" t="s">
+      <c r="F183" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="F183" s="0" t="s">
+      <c r="G183" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="G183" s="0" t="s">
+      <c r="H183" s="1" t="s">
         <v>884</v>
-      </c>
-      <c r="H183" s="0" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="184">
       <c r="B184" s="0" t="s">
+        <v>885</v>
+      </c>
+      <c r="D184" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="D184" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E184" s="0" t="s">
+      <c r="F184" s="1" t="s">
         <v>887</v>
       </c>
-      <c r="F184" s="0" t="s">
+      <c r="G184" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="G184" s="0" t="s">
+      <c r="H184" s="1" t="s">
         <v>889</v>
-      </c>
-      <c r="H184" s="0" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="185">
       <c r="B185" s="0" t="s">
+        <v>890</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="D185" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E185" s="0" t="s">
+      <c r="F185" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="F185" s="0" t="s">
+      <c r="G185" s="1" t="s">
         <v>893</v>
       </c>
-      <c r="G185" s="0" t="s">
+      <c r="H185" s="1" t="s">
         <v>894</v>
-      </c>
-      <c r="H185" s="0" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="186">
       <c r="B186" s="0" t="s">
+        <v>895</v>
+      </c>
+      <c r="D186" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="D186" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E186" s="0" t="s">
+      <c r="F186" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="F186" s="0" t="s">
+      <c r="G186" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="G186" s="0" t="s">
+      <c r="H186" s="1" t="s">
         <v>899</v>
-      </c>
-      <c r="H186" s="0" t="s">
-        <v>900</v>
       </c>
     </row>
     <row r="187">
       <c r="B187" s="0" t="s">
+        <v>900</v>
+      </c>
+      <c r="D187" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="D187" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E187" s="0" t="s">
+      <c r="F187" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="F187" s="0" t="s">
+      <c r="G187" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="G187" s="0" t="s">
+      <c r="H187" s="1" t="s">
         <v>904</v>
-      </c>
-      <c r="H187" s="0" t="s">
-        <v>905</v>
       </c>
     </row>
     <row r="188">
       <c r="B188" s="0" t="s">
+        <v>905</v>
+      </c>
+      <c r="D188" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="D188" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E188" s="0" t="s">
+      <c r="F188" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="F188" s="0" t="s">
+      <c r="G188" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="G188" s="0" t="s">
+      <c r="H188" s="1" t="s">
         <v>909</v>
-      </c>
-      <c r="H188" s="0" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="189">
       <c r="B189" s="0" t="s">
+        <v>910</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="D189" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E189" s="0" t="s">
+      <c r="F189" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="F189" s="0" t="s">
+      <c r="G189" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="G189" s="0" t="s">
+      <c r="H189" s="1" t="s">
         <v>914</v>
-      </c>
-      <c r="H189" s="0" t="s">
-        <v>915</v>
       </c>
     </row>
     <row r="190">
       <c r="B190" s="0" t="s">
+        <v>915</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>916</v>
       </c>
-      <c r="D190" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E190" s="0" t="s">
+      <c r="F190" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="F190" s="0" t="s">
+      <c r="G190" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="G190" s="0" t="s">
+      <c r="H190" s="1" t="s">
         <v>919</v>
-      </c>
-      <c r="H190" s="0" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="191">
       <c r="B191" s="0" t="s">
+        <v>920</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>921</v>
       </c>
-      <c r="D191" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E191" s="0" t="s">
+      <c r="F191" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="F191" s="0" t="s">
+      <c r="G191" s="1" t="s">
         <v>923</v>
       </c>
-      <c r="G191" s="0" t="s">
+      <c r="H191" s="1" t="s">
         <v>924</v>
-      </c>
-      <c r="H191" s="0" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="192">
       <c r="B192" s="0" t="s">
+        <v>925</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="D192" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E192" s="0" t="s">
+      <c r="F192" s="1" t="s">
         <v>927</v>
       </c>
-      <c r="F192" s="0" t="s">
+      <c r="G192" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="G192" s="0" t="s">
+      <c r="H192" s="1" t="s">
         <v>929</v>
-      </c>
-      <c r="H192" s="0" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="193">
       <c r="B193" s="0" t="s">
+        <v>930</v>
+      </c>
+      <c r="D193" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="D193" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E193" s="0" t="s">
+      <c r="F193" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="F193" s="0" t="s">
+      <c r="G193" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="G193" s="0" t="s">
+      <c r="H193" s="1" t="s">
         <v>934</v>
-      </c>
-      <c r="H193" s="0" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="194">
       <c r="B194" s="0" t="s">
+        <v>935</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>936</v>
       </c>
-      <c r="D194" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E194" s="0" t="s">
+      <c r="F194" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="F194" s="0" t="s">
+      <c r="G194" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="G194" s="0" t="s">
+      <c r="H194" s="1" t="s">
         <v>939</v>
-      </c>
-      <c r="H194" s="0" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="195">
       <c r="B195" s="0" t="s">
+        <v>940</v>
+      </c>
+      <c r="D195" s="1" t="s">
         <v>941</v>
       </c>
-      <c r="D195" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E195" s="0" t="s">
+      <c r="F195" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="F195" s="0" t="s">
+      <c r="G195" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="G195" s="0" t="s">
+      <c r="H195" s="1" t="s">
         <v>944</v>
-      </c>
-      <c r="H195" s="0" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="196">
       <c r="B196" s="0" t="s">
+        <v>945</v>
+      </c>
+      <c r="D196" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="D196" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E196" s="0" t="s">
+      <c r="F196" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="F196" s="0" t="s">
+      <c r="G196" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="G196" s="0" t="s">
+      <c r="H196" s="1" t="s">
         <v>949</v>
-      </c>
-      <c r="H196" s="0" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="197">
       <c r="B197" s="0" t="s">
+        <v>950</v>
+      </c>
+      <c r="D197" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="D197" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E197" s="0" t="s">
+      <c r="F197" s="1" t="s">
         <v>952</v>
       </c>
-      <c r="F197" s="0" t="s">
+      <c r="G197" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="G197" s="0" t="s">
+      <c r="H197" s="1" t="s">
         <v>954</v>
-      </c>
-      <c r="H197" s="0" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="198">
       <c r="B198" s="0" t="s">
+        <v>955</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="D198" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E198" s="0" t="s">
+      <c r="F198" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="F198" s="0" t="s">
+      <c r="G198" s="1" t="s">
         <v>958</v>
       </c>
-      <c r="G198" s="0" t="s">
+      <c r="H198" s="1" t="s">
         <v>959</v>
-      </c>
-      <c r="H198" s="0" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="199">
       <c r="B199" s="0" t="s">
+        <v>960</v>
+      </c>
+      <c r="D199" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="D199" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E199" s="0" t="s">
+      <c r="F199" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="F199" s="0" t="s">
+      <c r="G199" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="G199" s="0" t="s">
+      <c r="H199" s="1" t="s">
         <v>964</v>
-      </c>
-      <c r="H199" s="0" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="200">
       <c r="B200" s="0" t="s">
+        <v>965</v>
+      </c>
+      <c r="D200" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="D200" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E200" s="0" t="s">
+      <c r="F200" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="F200" s="0" t="s">
+      <c r="G200" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="G200" s="0" t="s">
+      <c r="H200" s="1" t="s">
         <v>969</v>
-      </c>
-      <c r="H200" s="0" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="201">
       <c r="B201" s="0" t="s">
+        <v>970</v>
+      </c>
+      <c r="D201" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="D201" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E201" s="0" t="s">
+      <c r="F201" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="F201" s="0" t="s">
+      <c r="G201" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="G201" s="0" t="s">
+      <c r="H201" s="1" t="s">
         <v>974</v>
-      </c>
-      <c r="H201" s="0" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="202">
       <c r="B202" s="0" t="s">
+        <v>975</v>
+      </c>
+      <c r="D202" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="D202" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E202" s="0" t="s">
+      <c r="F202" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="F202" s="0" t="s">
+      <c r="G202" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="G202" s="0" t="s">
+      <c r="H202" s="1" t="s">
         <v>979</v>
-      </c>
-      <c r="H202" s="0" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="203">
       <c r="B203" s="0" t="s">
+        <v>980</v>
+      </c>
+      <c r="D203" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="D203" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E203" s="0" t="s">
+      <c r="F203" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="F203" s="0" t="s">
+      <c r="G203" s="1" t="s">
         <v>983</v>
       </c>
-      <c r="G203" s="0" t="s">
+      <c r="H203" s="1" t="s">
         <v>984</v>
-      </c>
-      <c r="H203" s="0" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="204">
       <c r="B204" s="0" t="s">
+        <v>985</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="D204" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E204" s="0" t="s">
+      <c r="F204" s="1" t="s">
         <v>987</v>
       </c>
-      <c r="F204" s="0" t="s">
+      <c r="G204" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="G204" s="0" t="s">
+      <c r="H204" s="1" t="s">
         <v>989</v>
-      </c>
-      <c r="H204" s="0" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="205">
       <c r="B205" s="0" t="s">
+        <v>990</v>
+      </c>
+      <c r="D205" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="D205" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E205" s="0" t="s">
+      <c r="F205" s="1" t="s">
         <v>992</v>
       </c>
-      <c r="F205" s="0" t="s">
+      <c r="G205" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="G205" s="0" t="s">
+      <c r="H205" s="1" t="s">
         <v>994</v>
-      </c>
-      <c r="H205" s="0" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" s="0" t="s">
+        <v>995</v>
+      </c>
+      <c r="D206" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="D206" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E206" s="0" t="s">
+      <c r="F206" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="F206" s="0" t="s">
+      <c r="G206" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="G206" s="0" t="s">
+      <c r="H206" s="1" t="s">
         <v>999</v>
-      </c>
-      <c r="H206" s="0" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" s="0" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D207" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="D207" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E207" s="0" t="s">
+      <c r="F207" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="F207" s="0" t="s">
+      <c r="G207" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="G207" s="0" t="s">
+      <c r="H207" s="1" t="s">
         <v>1004</v>
-      </c>
-      <c r="H207" s="0" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" s="0" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D208" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="D208" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E208" s="0" t="s">
+      <c r="F208" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="F208" s="0" t="s">
+      <c r="G208" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="G208" s="0" t="s">
+      <c r="H208" s="1" t="s">
         <v>1009</v>
-      </c>
-      <c r="H208" s="0" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" s="0" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D209" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="D209" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E209" s="0" t="s">
+      <c r="F209" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="F209" s="0" t="s">
+      <c r="G209" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="G209" s="0" t="s">
+      <c r="H209" s="1" t="s">
         <v>1014</v>
-      </c>
-      <c r="H209" s="0" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" s="0" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="F210" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="G210" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="D210" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E210" s="0" t="s">
-        <v>872</v>
-      </c>
-      <c r="F210" s="0" t="s">
-        <v>873</v>
-      </c>
-      <c r="G210" s="0" t="s">
-        <v>1017</v>
-      </c>
-      <c r="H210" s="0" t="s">
-        <v>875</v>
+      <c r="H210" s="1" t="s">
+        <v>874</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" s="0" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D211" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="D211" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E211" s="0" t="s">
+      <c r="F211" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="F211" s="0" t="s">
+      <c r="G211" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="G211" s="0" t="s">
+      <c r="H211" s="1" t="s">
         <v>1021</v>
-      </c>
-      <c r="H211" s="0" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="212">
       <c r="B212" s="0" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D212" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="D212" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E212" s="0" t="s">
+      <c r="F212" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="F212" s="0" t="s">
+      <c r="G212" s="1" t="s">
         <v>1025</v>
       </c>
-      <c r="G212" s="0" t="s">
-        <v>1026</v>
-      </c>
-      <c r="H212" s="0" t="s">
-        <v>1024</v>
+      <c r="H212" s="1" t="s">
+        <v>1023</v>
       </c>
     </row>
     <row r="213">
       <c r="B213" s="0" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D213" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="D213" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E213" s="0" t="s">
+      <c r="F213" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="F213" s="0" t="s">
+      <c r="G213" s="1" t="s">
         <v>1029</v>
       </c>
-      <c r="G213" s="0" t="s">
+      <c r="H213" s="1" t="s">
         <v>1030</v>
-      </c>
-      <c r="H213" s="0" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" s="0" t="s">
+        <v>1031</v>
+      </c>
+      <c r="D214" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="D214" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E214" s="0" t="s">
+      <c r="F214" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="F214" s="0" t="s">
+      <c r="G214" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="G214" s="0" t="s">
+      <c r="H214" s="1" t="s">
         <v>1035</v>
-      </c>
-      <c r="H214" s="0" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="215">
       <c r="B215" s="0" t="s">
+        <v>1036</v>
+      </c>
+      <c r="D215" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="D215" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E215" s="0" t="s">
+      <c r="F215" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="F215" s="0" t="s">
+      <c r="G215" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="G215" s="0" t="s">
+      <c r="H215" s="1" t="s">
         <v>1040</v>
-      </c>
-      <c r="H215" s="0" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" s="0" t="s">
+        <v>1041</v>
+      </c>
+      <c r="D216" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="D216" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E216" s="0" t="s">
+      <c r="F216" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="F216" s="0" t="s">
+      <c r="G216" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="G216" s="0" t="s">
-        <v>1045</v>
-      </c>
-      <c r="H216" s="0" t="s">
-        <v>1043</v>
+      <c r="H216" s="1" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" s="0" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D217" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E217" s="0" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F217" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="F217" s="0" t="s">
+      <c r="G217" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="G217" s="0" t="s">
+      <c r="H217" s="1" t="s">
         <v>1035</v>
-      </c>
-      <c r="H217" s="0" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" s="0" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D218" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E218" s="0" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F218" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="F218" s="0" t="s">
+      <c r="G218" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="G218" s="0" t="s">
+      <c r="H218" s="1" t="s">
         <v>1040</v>
-      </c>
-      <c r="H218" s="0" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" s="0" t="s">
-        <v>1048</v>
-      </c>
-      <c r="D219" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E219" s="0" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="F219" s="0" t="s">
+      <c r="G219" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="G219" s="0" t="s">
-        <v>1045</v>
-      </c>
-      <c r="H219" s="0" t="s">
-        <v>1043</v>
+      <c r="H219" s="1" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="220">
       <c r="B220" s="0" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D220" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="D220" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E220" s="0" t="s">
+      <c r="F220" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="F220" s="0" t="s">
+      <c r="G220" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="G220" s="0" t="s">
-        <v>1052</v>
-      </c>
-      <c r="H220" s="0" t="s">
-        <v>1050</v>
+      <c r="H220" s="1" t="s">
+        <v>1049</v>
       </c>
     </row>
     <row r="221">
       <c r="B221" s="0" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D221" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E221" s="0" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F221" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="F221" s="0" t="s">
+      <c r="G221" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="G221" s="0" t="s">
+      <c r="H221" s="1" t="s">
         <v>1035</v>
-      </c>
-      <c r="H221" s="0" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" s="0" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D222" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E222" s="0" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F222" s="1" t="s">
         <v>1038</v>
       </c>
-      <c r="F222" s="0" t="s">
+      <c r="G222" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="G222" s="0" t="s">
+      <c r="H222" s="1" t="s">
         <v>1040</v>
-      </c>
-      <c r="H222" s="0" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" s="0" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D223" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E223" s="0" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F223" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="F223" s="0" t="s">
+      <c r="G223" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="G223" s="0" t="s">
-        <v>1045</v>
-      </c>
-      <c r="H223" s="0" t="s">
-        <v>1043</v>
+      <c r="H223" s="1" t="s">
+        <v>1042</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" s="0" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D224" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E224" s="0" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F224" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="F224" s="0" t="s">
+      <c r="G224" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="G224" s="0" t="s">
-        <v>1052</v>
-      </c>
-      <c r="H224" s="0" t="s">
-        <v>1050</v>
+      <c r="H224" s="1" t="s">
+        <v>1049</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" s="0" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D225" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="D225" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E225" s="0" t="s">
+      <c r="F225" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="F225" s="0" t="s">
+      <c r="G225" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="G225" s="0" t="s">
+      <c r="H225" s="1" t="s">
         <v>1060</v>
-      </c>
-      <c r="H225" s="0" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" s="0" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D226" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="D226" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E226" s="0" t="s">
+      <c r="F226" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="F226" s="0" t="s">
+      <c r="G226" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="G226" s="0" t="s">
+      <c r="H226" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="H226" s="0" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" s="0" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D227" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="D227" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E227" s="0" t="s">
+      <c r="F227" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="F227" s="0" t="s">
+      <c r="G227" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="G227" s="0" t="s">
+      <c r="H227" s="1" t="s">
         <v>1070</v>
-      </c>
-      <c r="H227" s="0" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" s="0" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D228" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="D228" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E228" s="0" t="s">
+      <c r="F228" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="F228" s="0" t="s">
+      <c r="G228" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="G228" s="0" t="s">
+      <c r="H228" s="1" t="s">
         <v>1075</v>
-      </c>
-      <c r="H228" s="0" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" s="0" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D229" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="D229" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E229" s="0" t="s">
+      <c r="F229" s="1" t="s">
         <v>1078</v>
       </c>
-      <c r="F229" s="0" t="s">
+      <c r="G229" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="G229" s="0" t="s">
+      <c r="H229" s="1" t="s">
         <v>1080</v>
-      </c>
-      <c r="H229" s="0" t="s">
-        <v>1081</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" s="0" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D230" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="D230" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E230" s="0" t="s">
+      <c r="F230" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="F230" s="0" t="s">
+      <c r="G230" s="1" t="s">
         <v>1084</v>
       </c>
-      <c r="G230" s="0" t="s">
+      <c r="H230" s="1" t="s">
         <v>1085</v>
-      </c>
-      <c r="H230" s="0" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" s="0" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D231" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="D231" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E231" s="0" t="s">
+      <c r="F231" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="F231" s="0" t="s">
+      <c r="G231" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="G231" s="0" t="s">
+      <c r="H231" s="1" t="s">
         <v>1090</v>
-      </c>
-      <c r="H231" s="0" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" s="0" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D232" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E232" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F232" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="F232" s="0" t="s">
+      <c r="G232" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="G232" s="0" t="s">
+      <c r="H232" s="1" t="s">
         <v>1060</v>
-      </c>
-      <c r="H232" s="0" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="233">
       <c r="B233" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D233" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E233" s="0" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F233" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="F233" s="0" t="s">
+      <c r="G233" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="G233" s="0" t="s">
+      <c r="H233" s="1" t="s">
         <v>1065</v>
-      </c>
-      <c r="H233" s="0" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="234">
       <c r="B234" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D234" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="D234" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E234" s="0" t="s">
+      <c r="F234" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="F234" s="0" t="s">
+      <c r="G234" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="G234" s="0" t="s">
+      <c r="H234" s="1" t="s">
         <v>1097</v>
-      </c>
-      <c r="H234" s="0" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" s="0" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D235" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E235" s="0" t="s">
+        <v>1098</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F235" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="F235" s="0" t="s">
+      <c r="G235" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="G235" s="0" t="s">
+      <c r="H235" s="1" t="s">
         <v>1090</v>
-      </c>
-      <c r="H235" s="0" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="236">
       <c r="B236" s="0" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D236" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="D236" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E236" s="0" t="s">
+      <c r="F236" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="F236" s="0" t="s">
+      <c r="G236" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="G236" s="0" t="s">
+      <c r="H236" s="1" t="s">
         <v>1103</v>
-      </c>
-      <c r="H236" s="0" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="237">
       <c r="B237" s="0" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D237" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E237" s="0" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F237" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="F237" s="0" t="s">
+      <c r="G237" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="G237" s="0" t="s">
+      <c r="H237" s="1" t="s">
         <v>1103</v>
-      </c>
-      <c r="H237" s="0" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" s="0" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D238" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="D238" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E238" s="0" t="s">
+      <c r="F238" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="F238" s="0" t="s">
+      <c r="G238" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="G238" s="0" t="s">
+      <c r="H238" s="1" t="s">
         <v>1109</v>
-      </c>
-      <c r="H238" s="0" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="239">
       <c r="B239" s="0" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D239" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E239" s="0" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F239" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="F239" s="0" t="s">
+      <c r="G239" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="G239" s="0" t="s">
+      <c r="H239" s="1" t="s">
         <v>1103</v>
-      </c>
-      <c r="H239" s="0" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="240">
       <c r="B240" s="0" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D240" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="D240" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E240" s="0" t="s">
+      <c r="F240" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="F240" s="0" t="s">
+      <c r="G240" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="G240" s="0" t="s">
+      <c r="H240" s="1" t="s">
         <v>1115</v>
-      </c>
-      <c r="H240" s="0" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" s="0" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D241" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="D241" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E241" s="0" t="s">
+      <c r="F241" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="F241" s="0" t="s">
+      <c r="G241" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="G241" s="0" t="s">
+      <c r="H241" s="1" t="s">
         <v>1120</v>
-      </c>
-      <c r="H241" s="0" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="242">
       <c r="B242" s="0" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D242" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="D242" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E242" s="0" t="s">
+      <c r="F242" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="F242" s="0" t="s">
+      <c r="G242" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="G242" s="0" t="s">
+      <c r="H242" s="1" t="s">
         <v>1125</v>
-      </c>
-      <c r="H242" s="0" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="243">
       <c r="B243" s="0" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D243" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E243" s="0" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F243" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="F243" s="0" t="s">
+      <c r="G243" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="G243" s="0" t="s">
+      <c r="H243" s="1" t="s">
         <v>1125</v>
-      </c>
-      <c r="H243" s="0" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="244">
       <c r="B244" s="0" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D244" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="D244" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E244" s="0" t="s">
+      <c r="F244" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="F244" s="0" t="s">
+      <c r="G244" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="G244" s="0" t="s">
+      <c r="H244" s="1" t="s">
         <v>1131</v>
-      </c>
-      <c r="H244" s="0" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="245">
       <c r="B245" s="0" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D245" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E245" s="0" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F245" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="F245" s="0" t="s">
+      <c r="G245" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="G245" s="0" t="s">
+      <c r="H245" s="1" t="s">
         <v>1125</v>
-      </c>
-      <c r="H245" s="0" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" s="0" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D246" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E246" s="0" t="s">
+        <v>1133</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F246" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="F246" s="0" t="s">
+      <c r="G246" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="G246" s="0" t="s">
+      <c r="H246" s="1" t="s">
         <v>1125</v>
-      </c>
-      <c r="H246" s="0" t="s">
-        <v>1126</v>
       </c>
     </row>
     <row r="247">
       <c r="B247" s="0" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D247" s="1" t="s">
         <v>1135</v>
       </c>
-      <c r="D247" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E247" s="0" t="s">
+      <c r="F247" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="F247" s="0" t="s">
+      <c r="G247" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="G247" s="0" t="s">
+      <c r="H247" s="1" t="s">
         <v>1138</v>
-      </c>
-      <c r="H247" s="0" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="248">
       <c r="B248" s="0" t="s">
-        <v>1140</v>
-      </c>
-      <c r="D248" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E248" s="0" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F248" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="F248" s="0" t="s">
+      <c r="G248" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="G248" s="0" t="s">
+      <c r="H248" s="1" t="s">
         <v>1115</v>
-      </c>
-      <c r="H248" s="0" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="249">
       <c r="B249" s="0" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D249" s="1" t="s">
         <v>1141</v>
       </c>
-      <c r="D249" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E249" s="0" t="s">
+      <c r="F249" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="F249" s="0" t="s">
+      <c r="G249" s="1" t="s">
         <v>1143</v>
       </c>
-      <c r="G249" s="0" t="s">
+      <c r="H249" s="1" t="s">
         <v>1144</v>
-      </c>
-      <c r="H249" s="0" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="250">
       <c r="B250" s="0" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D250" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E250" s="0" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F250" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="F250" s="0" t="s">
+      <c r="G250" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="G250" s="0" t="s">
+      <c r="H250" s="1" t="s">
         <v>1115</v>
-      </c>
-      <c r="H250" s="0" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" s="0" t="s">
+        <v>1146</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F251" s="1" t="s">
         <v>1147</v>
       </c>
-      <c r="D251" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E251" s="0" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F251" s="0" t="s">
-        <v>1148</v>
-      </c>
-      <c r="G251" s="0" t="s">
+      <c r="G251" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H251" s="1" t="s">
         <v>1144</v>
-      </c>
-      <c r="H251" s="0" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="252">
       <c r="B252" s="0" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F252" s="1" t="s">
         <v>1149</v>
       </c>
-      <c r="D252" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E252" s="0" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F252" s="0" t="s">
+      <c r="G252" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="G252" s="0" t="s">
-        <v>1151</v>
-      </c>
-      <c r="H252" s="0" t="s">
-        <v>1116</v>
+      <c r="H252" s="1" t="s">
+        <v>1115</v>
       </c>
     </row>
     <row r="253">
       <c r="B253" s="0" t="s">
-        <v>1152</v>
-      </c>
-      <c r="D253" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E253" s="0" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F253" s="0" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="G253" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="G253" s="0" t="s">
-        <v>1151</v>
-      </c>
-      <c r="H253" s="0" t="s">
-        <v>1116</v>
+      <c r="H253" s="1" t="s">
+        <v>1115</v>
       </c>
     </row>
     <row r="254">
       <c r="B254" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D254" s="1" t="s">
         <v>1153</v>
       </c>
-      <c r="D254" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E254" s="0" t="s">
+      <c r="F254" s="1" t="s">
         <v>1154</v>
       </c>
-      <c r="F254" s="0" t="s">
+      <c r="G254" s="1" t="s">
         <v>1155</v>
       </c>
-      <c r="G254" s="0" t="s">
+      <c r="H254" s="1" t="s">
         <v>1156</v>
-      </c>
-      <c r="H254" s="0" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="255">
       <c r="B255" s="0" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D255" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="D255" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E255" s="0" t="s">
+      <c r="F255" s="1" t="s">
         <v>1159</v>
       </c>
-      <c r="F255" s="0" t="s">
+      <c r="G255" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="G255" s="0" t="s">
+      <c r="H255" s="1" t="s">
         <v>1161</v>
-      </c>
-      <c r="H255" s="0" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="256">
       <c r="B256" s="0" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D256" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="D256" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E256" s="0" t="s">
+      <c r="F256" s="1" t="s">
         <v>1164</v>
       </c>
-      <c r="F256" s="0" t="s">
+      <c r="G256" s="1" t="s">
         <v>1165</v>
       </c>
-      <c r="G256" s="0" t="s">
+      <c r="H256" s="1" t="s">
         <v>1166</v>
-      </c>
-      <c r="H256" s="0" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="257">
       <c r="B257" s="0" t="s">
+        <v>1167</v>
+      </c>
+      <c r="D257" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="D257" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E257" s="0" t="s">
+      <c r="F257" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="F257" s="0" t="s">
+      <c r="G257" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="G257" s="0" t="s">
+      <c r="H257" s="1" t="s">
         <v>1171</v>
-      </c>
-      <c r="H257" s="0" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="258">
       <c r="B258" s="0" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D258" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="D258" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E258" s="0" t="s">
+      <c r="F258" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="F258" s="0" t="s">
+      <c r="G258" s="1" t="s">
         <v>1175</v>
       </c>
-      <c r="G258" s="0" t="s">
+      <c r="H258" s="1" t="s">
         <v>1176</v>
-      </c>
-      <c r="H258" s="0" t="s">
-        <v>1177</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" s="0" t="s">
+        <v>1177</v>
+      </c>
+      <c r="D259" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="D259" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E259" s="0" t="s">
+      <c r="F259" s="1" t="s">
         <v>1179</v>
       </c>
-      <c r="F259" s="0" t="s">
+      <c r="G259" s="1" t="s">
         <v>1180</v>
       </c>
-      <c r="G259" s="0" t="s">
+      <c r="H259" s="1" t="s">
         <v>1181</v>
-      </c>
-      <c r="H259" s="0" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" s="0" t="s">
+        <v>1182</v>
+      </c>
+      <c r="D260" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="D260" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E260" s="0" t="s">
+      <c r="F260" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="F260" s="0" t="s">
+      <c r="G260" s="1" t="s">
         <v>1185</v>
       </c>
-      <c r="G260" s="0" t="s">
+      <c r="H260" s="1" t="s">
         <v>1186</v>
-      </c>
-      <c r="H260" s="0" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" s="0" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D261" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="D261" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E261" s="0" t="s">
+      <c r="F261" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="F261" s="0" t="s">
+      <c r="G261" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="G261" s="0" t="s">
+      <c r="H261" s="1" t="s">
         <v>1191</v>
-      </c>
-      <c r="H261" s="0" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" s="0" t="s">
+        <v>1192</v>
+      </c>
+      <c r="D262" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="D262" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E262" s="0" t="s">
+      <c r="F262" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="F262" s="0" t="s">
+      <c r="G262" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="G262" s="0" t="s">
+      <c r="H262" s="1" t="s">
         <v>1196</v>
-      </c>
-      <c r="H262" s="0" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="0" t="s">
+        <v>1197</v>
+      </c>
+      <c r="D263" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="D263" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E263" s="0" t="s">
+      <c r="F263" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="F263" s="0" t="s">
+      <c r="G263" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="G263" s="0" t="s">
+      <c r="H263" s="1" t="s">
         <v>1201</v>
-      </c>
-      <c r="H263" s="0" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="0" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D264" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="D264" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E264" s="0" t="s">
+      <c r="F264" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="F264" s="0" t="s">
+      <c r="G264" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="G264" s="0" t="s">
+      <c r="H264" s="1" t="s">
         <v>1206</v>
-      </c>
-      <c r="H264" s="0" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" s="0" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D265" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="D265" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E265" s="0" t="s">
+      <c r="F265" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="F265" s="0" t="s">
+      <c r="G265" s="1" t="s">
         <v>1210</v>
       </c>
-      <c r="G265" s="0" t="s">
+      <c r="H265" s="1" t="s">
         <v>1211</v>
-      </c>
-      <c r="H265" s="0" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" s="0" t="s">
+        <v>1212</v>
+      </c>
+      <c r="D266" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="D266" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E266" s="0" t="s">
+      <c r="F266" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="F266" s="0" t="s">
+      <c r="G266" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="G266" s="0" t="s">
+      <c r="H266" s="1" t="s">
         <v>1216</v>
-      </c>
-      <c r="H266" s="0" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="267">
       <c r="B267" s="0" t="s">
+        <v>1217</v>
+      </c>
+      <c r="D267" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="D267" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E267" s="0" t="s">
+      <c r="F267" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="F267" s="0" t="s">
+      <c r="G267" s="1" t="s">
         <v>1220</v>
       </c>
-      <c r="G267" s="0" t="s">
-        <v>1221</v>
-      </c>
-      <c r="H267" s="0" t="s">
-        <v>1219</v>
+      <c r="H267" s="1" t="s">
+        <v>1218</v>
       </c>
     </row>
     <row r="268">
       <c r="B268" s="0" t="s">
+        <v>1221</v>
+      </c>
+      <c r="D268" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="D268" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E268" s="0" t="s">
+      <c r="F268" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="F268" s="0" t="s">
+      <c r="G268" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="G268" s="0" t="s">
-        <v>1225</v>
-      </c>
-      <c r="H268" s="0" t="s">
-        <v>1223</v>
+      <c r="H268" s="1" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" s="0" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D269" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="D269" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E269" s="0" t="s">
+      <c r="F269" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="F269" s="0" t="s">
+      <c r="G269" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="G269" s="0" t="s">
+      <c r="H269" s="1" t="s">
         <v>1229</v>
-      </c>
-      <c r="H269" s="0" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" s="0" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D270" s="1" t="s">
         <v>1231</v>
       </c>
-      <c r="D270" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E270" s="0" t="s">
+      <c r="F270" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="F270" s="0" t="s">
+      <c r="G270" s="1" t="s">
         <v>1233</v>
       </c>
-      <c r="G270" s="0" t="s">
+      <c r="H270" s="1" t="s">
         <v>1234</v>
-      </c>
-      <c r="H270" s="0" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="271">
       <c r="B271" s="0" t="s">
+        <v>1235</v>
+      </c>
+      <c r="D271" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="D271" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E271" s="0" t="s">
+      <c r="F271" s="1" t="s">
         <v>1237</v>
       </c>
-      <c r="F271" s="0" t="s">
+      <c r="G271" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="G271" s="0" t="s">
+      <c r="H271" s="1" t="s">
         <v>1239</v>
-      </c>
-      <c r="H271" s="0" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="272">
       <c r="B272" s="0" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D272" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="D272" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E272" s="0" t="s">
+      <c r="F272" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="F272" s="0" t="s">
+      <c r="G272" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="G272" s="0" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H272" s="0" t="s">
-        <v>1242</v>
+      <c r="H272" s="1" t="s">
+        <v>1241</v>
       </c>
     </row>
     <row r="273">
       <c r="B273" s="0" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D273" s="1" t="s">
         <v>1245</v>
       </c>
-      <c r="D273" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E273" s="0" t="s">
+      <c r="F273" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="F273" s="0" t="s">
+      <c r="G273" s="1" t="s">
         <v>1247</v>
       </c>
-      <c r="G273" s="0" t="s">
-        <v>1248</v>
-      </c>
-      <c r="H273" s="0" t="s">
-        <v>1246</v>
+      <c r="H273" s="1" t="s">
+        <v>1245</v>
       </c>
     </row>
     <row r="274">
       <c r="B274" s="0" t="s">
+        <v>1248</v>
+      </c>
+      <c r="D274" s="1" t="s">
         <v>1249</v>
       </c>
-      <c r="D274" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E274" s="0" t="s">
+      <c r="F274" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="F274" s="0" t="s">
+      <c r="G274" s="1" t="s">
         <v>1251</v>
       </c>
-      <c r="G274" s="0" t="s">
+      <c r="H274" s="1" t="s">
         <v>1252</v>
-      </c>
-      <c r="H274" s="0" t="s">
-        <v>1253</v>
       </c>
     </row>
     <row r="275">
       <c r="B275" s="0" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D275" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E275" s="0" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F275" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="F275" s="0" t="s">
+      <c r="G275" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="G275" s="0" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H275" s="0" t="s">
-        <v>1242</v>
+      <c r="H275" s="1" t="s">
+        <v>1241</v>
       </c>
     </row>
     <row r="276">
       <c r="B276" s="0" t="s">
-        <v>1255</v>
-      </c>
-      <c r="D276" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E276" s="0" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F276" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="F276" s="0" t="s">
+      <c r="G276" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="G276" s="0" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H276" s="0" t="s">
-        <v>1242</v>
+      <c r="H276" s="1" t="s">
+        <v>1241</v>
       </c>
     </row>
     <row r="277">
       <c r="B277" s="0" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D277" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E277" s="0" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F277" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="F277" s="0" t="s">
+      <c r="G277" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="G277" s="0" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H277" s="0" t="s">
-        <v>1242</v>
+      <c r="H277" s="1" t="s">
+        <v>1241</v>
       </c>
     </row>
     <row r="278">
       <c r="B278" s="0" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D278" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="D278" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E278" s="0" t="s">
+      <c r="F278" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="F278" s="0" t="s">
+      <c r="G278" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="G278" s="0" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H278" s="0" t="s">
-        <v>1258</v>
+      <c r="H278" s="1" t="s">
+        <v>1257</v>
       </c>
     </row>
     <row r="279">
       <c r="B279" s="0" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D279" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="D279" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E279" s="0" t="s">
+      <c r="F279" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="F279" s="0" t="s">
+      <c r="G279" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="G279" s="0" t="s">
+      <c r="H279" s="1" t="s">
         <v>1264</v>
-      </c>
-      <c r="H279" s="0" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="280">
       <c r="B280" s="0" t="s">
-        <v>1266</v>
-      </c>
-      <c r="D280" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E280" s="0" t="s">
+        <v>1265</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F280" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="F280" s="0" t="s">
+      <c r="G280" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="G280" s="0" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H280" s="0" t="s">
-        <v>1258</v>
+      <c r="H280" s="1" t="s">
+        <v>1257</v>
       </c>
     </row>
     <row r="281">
       <c r="B281" s="0" t="s">
+        <v>1266</v>
+      </c>
+      <c r="D281" s="1" t="s">
         <v>1267</v>
       </c>
-      <c r="D281" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E281" s="0" t="s">
+      <c r="F281" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="F281" s="0" t="s">
+      <c r="G281" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="G281" s="0" t="s">
+      <c r="H281" s="1" t="s">
         <v>1270</v>
-      </c>
-      <c r="H281" s="0" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="282">
       <c r="B282" s="0" t="s">
-        <v>1272</v>
-      </c>
-      <c r="D282" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E282" s="0" t="s">
+        <v>1271</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F282" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="F282" s="0" t="s">
+      <c r="G282" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="G282" s="0" t="s">
+      <c r="H282" s="1" t="s">
         <v>1270</v>
-      </c>
-      <c r="H282" s="0" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="283">
       <c r="B283" s="0" t="s">
-        <v>1273</v>
-      </c>
-      <c r="D283" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E283" s="0" t="s">
+        <v>1272</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F283" s="1" t="s">
         <v>1268</v>
       </c>
-      <c r="F283" s="0" t="s">
+      <c r="G283" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="G283" s="0" t="s">
+      <c r="H283" s="1" t="s">
         <v>1270</v>
-      </c>
-      <c r="H283" s="0" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="284">
       <c r="B284" s="0" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D284" s="1" t="s">
         <v>1274</v>
       </c>
-      <c r="D284" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E284" s="0" t="s">
+      <c r="F284" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="F284" s="0" t="s">
+      <c r="G284" s="1" t="s">
         <v>1276</v>
       </c>
-      <c r="G284" s="0" t="s">
+      <c r="H284" s="1" t="s">
         <v>1277</v>
-      </c>
-      <c r="H284" s="0" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="285">
       <c r="B285" s="0" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D285" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="D285" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E285" s="0" t="s">
+      <c r="F285" s="1" t="s">
         <v>1280</v>
       </c>
-      <c r="F285" s="0" t="s">
+      <c r="G285" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="G285" s="0" t="s">
-        <v>1282</v>
-      </c>
-      <c r="H285" s="0" t="s">
-        <v>1280</v>
+      <c r="H285" s="1" t="s">
+        <v>1279</v>
       </c>
     </row>
     <row r="286">
       <c r="B286" s="0" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D286" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="D286" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E286" s="0" t="s">
+      <c r="F286" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="F286" s="0" t="s">
+      <c r="G286" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="G286" s="0" t="s">
+      <c r="H286" s="1" t="s">
         <v>1286</v>
-      </c>
-      <c r="H286" s="0" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="287">
       <c r="B287" s="0" t="s">
+        <v>1287</v>
+      </c>
+      <c r="D287" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="D287" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E287" s="0" t="s">
+      <c r="F287" s="1" t="s">
         <v>1289</v>
       </c>
-      <c r="F287" s="0" t="s">
+      <c r="G287" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="G287" s="0" t="s">
+      <c r="H287" s="1" t="s">
         <v>1291</v>
-      </c>
-      <c r="H287" s="0" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="288">
       <c r="B288" s="0" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D288" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="D288" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E288" s="0" t="s">
+      <c r="F288" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="F288" s="0" t="s">
+      <c r="G288" s="1" t="s">
         <v>1295</v>
       </c>
-      <c r="G288" s="0" t="s">
+      <c r="H288" s="1" t="s">
         <v>1296</v>
-      </c>
-      <c r="H288" s="0" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="289">
       <c r="B289" s="0" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D289" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="D289" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E289" s="0" t="s">
+      <c r="F289" s="1" t="s">
         <v>1299</v>
       </c>
-      <c r="F289" s="0" t="s">
+      <c r="G289" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="G289" s="0" t="s">
+      <c r="H289" s="1" t="s">
         <v>1301</v>
-      </c>
-      <c r="H289" s="0" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="290">
       <c r="B290" s="0" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D290" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E290" s="0" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F290" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="F290" s="0" t="s">
+      <c r="G290" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="G290" s="0" t="s">
+      <c r="H290" s="1" t="s">
         <v>1264</v>
-      </c>
-      <c r="H290" s="0" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="291">
       <c r="B291" s="0" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D291" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E291" s="0" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F291" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="F291" s="0" t="s">
+      <c r="G291" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="G291" s="0" t="s">
+      <c r="H291" s="1" t="s">
         <v>1264</v>
-      </c>
-      <c r="H291" s="0" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="292">
       <c r="B292" s="0" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D292" s="1" t="s">
         <v>1305</v>
       </c>
-      <c r="D292" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E292" s="0" t="s">
+      <c r="F292" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="F292" s="0" t="s">
+      <c r="G292" s="1" t="s">
         <v>1307</v>
       </c>
-      <c r="G292" s="0" t="s">
+      <c r="H292" s="1" t="s">
         <v>1308</v>
-      </c>
-      <c r="H292" s="0" t="s">
-        <v>1309</v>
       </c>
     </row>
     <row r="293">
       <c r="B293" s="0" t="s">
+        <v>1309</v>
+      </c>
+      <c r="D293" s="1" t="s">
         <v>1310</v>
       </c>
-      <c r="D293" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E293" s="0" t="s">
+      <c r="F293" s="1" t="s">
         <v>1311</v>
       </c>
-      <c r="F293" s="0" t="s">
+      <c r="G293" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="G293" s="0" t="s">
+      <c r="H293" s="1" t="s">
         <v>1313</v>
-      </c>
-      <c r="H293" s="0" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" s="0" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D294" s="1" t="s">
         <v>1315</v>
       </c>
-      <c r="D294" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E294" s="0" t="s">
+      <c r="F294" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="F294" s="0" t="s">
+      <c r="G294" s="1" t="s">
         <v>1317</v>
       </c>
-      <c r="G294" s="0" t="s">
-        <v>1318</v>
-      </c>
-      <c r="H294" s="0" t="s">
-        <v>1316</v>
+      <c r="H294" s="1" t="s">
+        <v>1315</v>
       </c>
     </row>
     <row r="295">
       <c r="B295" s="0" t="s">
+        <v>1318</v>
+      </c>
+      <c r="D295" s="1" t="s">
         <v>1319</v>
       </c>
-      <c r="D295" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E295" s="0" t="s">
+      <c r="F295" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="F295" s="0" t="s">
+      <c r="G295" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="G295" s="0" t="s">
+      <c r="H295" s="1" t="s">
         <v>1322</v>
-      </c>
-      <c r="H295" s="0" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="296">
       <c r="B296" s="0" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D296" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="D296" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E296" s="0" t="s">
+      <c r="F296" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="F296" s="0" t="s">
+      <c r="G296" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="G296" s="0" t="s">
+      <c r="H296" s="1" t="s">
         <v>1327</v>
-      </c>
-      <c r="H296" s="0" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="297">
       <c r="B297" s="0" t="s">
+        <v>1328</v>
+      </c>
+      <c r="D297" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="D297" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E297" s="0" t="s">
+      <c r="F297" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="F297" s="0" t="s">
+      <c r="G297" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="G297" s="0" t="s">
+      <c r="H297" s="1" t="s">
         <v>1332</v>
-      </c>
-      <c r="H297" s="0" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="298">
       <c r="B298" s="0" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D298" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="D298" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E298" s="0" t="s">
+      <c r="F298" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="F298" s="0" t="s">
+      <c r="G298" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="G298" s="0" t="s">
+      <c r="H298" s="1" t="s">
         <v>1337</v>
-      </c>
-      <c r="H298" s="0" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="299">
       <c r="B299" s="0" t="s">
+        <v>1338</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>1339</v>
       </c>
-      <c r="D299" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E299" s="0" t="s">
+      <c r="F299" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="F299" s="0" t="s">
+      <c r="G299" s="1" t="s">
         <v>1341</v>
       </c>
-      <c r="G299" s="0" t="s">
+      <c r="H299" s="1" t="s">
         <v>1342</v>
-      </c>
-      <c r="H299" s="0" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="300">
       <c r="B300" s="0" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D300" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="D300" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E300" s="0" t="s">
+      <c r="F300" s="1" t="s">
         <v>1345</v>
       </c>
-      <c r="F300" s="0" t="s">
+      <c r="G300" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="G300" s="0" t="s">
+      <c r="H300" s="1" t="s">
         <v>1347</v>
-      </c>
-      <c r="H300" s="0" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="301">
       <c r="B301" s="0" t="s">
+        <v>1348</v>
+      </c>
+      <c r="D301" s="1" t="s">
         <v>1349</v>
       </c>
-      <c r="D301" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E301" s="0" t="s">
+      <c r="F301" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="F301" s="0" t="s">
+      <c r="G301" s="1" t="s">
         <v>1351</v>
       </c>
-      <c r="G301" s="0" t="s">
+      <c r="H301" s="1" t="s">
         <v>1352</v>
-      </c>
-      <c r="H301" s="0" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="302">
       <c r="B302" s="0" t="s">
+        <v>1353</v>
+      </c>
+      <c r="D302" s="1" t="s">
         <v>1354</v>
       </c>
-      <c r="D302" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E302" s="0" t="s">
+      <c r="F302" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="F302" s="0" t="s">
+      <c r="G302" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="G302" s="0" t="s">
+      <c r="H302" s="1" t="s">
         <v>1357</v>
-      </c>
-      <c r="H302" s="0" t="s">
-        <v>1358</v>
       </c>
     </row>
     <row r="303">
       <c r="B303" s="0" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D303" s="1" t="s">
         <v>1359</v>
       </c>
-      <c r="D303" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E303" s="0" t="s">
+      <c r="F303" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="F303" s="0" t="s">
+      <c r="G303" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="G303" s="0" t="s">
+      <c r="H303" s="1" t="s">
         <v>1362</v>
-      </c>
-      <c r="H303" s="0" t="s">
-        <v>1363</v>
       </c>
     </row>
     <row r="304">
       <c r="B304" s="0" t="s">
+        <v>1363</v>
+      </c>
+      <c r="D304" s="1" t="s">
         <v>1364</v>
       </c>
-      <c r="D304" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E304" s="0" t="s">
+      <c r="F304" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="F304" s="0" t="s">
+      <c r="G304" s="1" t="s">
         <v>1366</v>
       </c>
-      <c r="G304" s="0" t="s">
+      <c r="H304" s="1" t="s">
         <v>1367</v>
-      </c>
-      <c r="H304" s="0" t="s">
-        <v>1368</v>
       </c>
     </row>
     <row r="305">
       <c r="B305" s="0" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D305" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="D305" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E305" s="0" t="s">
+      <c r="F305" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="F305" s="0" t="s">
+      <c r="G305" s="1" t="s">
         <v>1371</v>
       </c>
-      <c r="G305" s="0" t="s">
+      <c r="H305" s="1" t="s">
         <v>1372</v>
-      </c>
-      <c r="H305" s="0" t="s">
-        <v>1373</v>
       </c>
     </row>
     <row r="306">
       <c r="B306" s="0" t="s">
+        <v>1373</v>
+      </c>
+      <c r="D306" s="1" t="s">
         <v>1374</v>
       </c>
-      <c r="D306" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E306" s="0" t="s">
+      <c r="F306" s="1" t="s">
         <v>1375</v>
       </c>
-      <c r="F306" s="0" t="s">
+      <c r="G306" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="G306" s="0" t="s">
+      <c r="H306" s="1" t="s">
         <v>1377</v>
-      </c>
-      <c r="H306" s="0" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="307">
       <c r="B307" s="0" t="s">
+        <v>1378</v>
+      </c>
+      <c r="D307" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="D307" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E307" s="0" t="s">
+      <c r="F307" s="1" t="s">
         <v>1380</v>
       </c>
-      <c r="F307" s="0" t="s">
+      <c r="G307" s="1" t="s">
         <v>1381</v>
       </c>
-      <c r="G307" s="0" t="s">
+      <c r="H307" s="1" t="s">
         <v>1382</v>
-      </c>
-      <c r="H307" s="0" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="308">
       <c r="B308" s="0" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D308" s="1" t="s">
         <v>1384</v>
       </c>
-      <c r="D308" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E308" s="0" t="s">
+      <c r="F308" s="1" t="s">
         <v>1385</v>
       </c>
-      <c r="F308" s="0" t="s">
+      <c r="G308" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="G308" s="0" t="s">
+      <c r="H308" s="1" t="s">
         <v>1387</v>
-      </c>
-      <c r="H308" s="0" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="309">
       <c r="B309" s="0" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D309" s="1" t="s">
         <v>1389</v>
       </c>
-      <c r="D309" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E309" s="0" t="s">
+      <c r="F309" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G309" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="F309" s="0" t="s">
-        <v>1331</v>
-      </c>
-      <c r="G309" s="0" t="s">
+      <c r="H309" s="1" t="s">
         <v>1391</v>
-      </c>
-      <c r="H309" s="0" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="310">
       <c r="B310" s="0" t="s">
+        <v>1392</v>
+      </c>
+      <c r="D310" s="1" t="s">
         <v>1393</v>
       </c>
-      <c r="D310" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E310" s="0" t="s">
+      <c r="F310" s="1" t="s">
         <v>1394</v>
       </c>
-      <c r="F310" s="0" t="s">
+      <c r="G310" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="G310" s="0" t="s">
+      <c r="H310" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="H310" s="0" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="311">
       <c r="B311" s="0" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D311" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="D311" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E311" s="0" t="s">
+      <c r="F311" s="1" t="s">
         <v>1399</v>
       </c>
-      <c r="F311" s="0" t="s">
+      <c r="G311" s="1" t="s">
         <v>1400</v>
       </c>
-      <c r="G311" s="0" t="s">
+      <c r="H311" s="1" t="s">
         <v>1401</v>
-      </c>
-      <c r="H311" s="0" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="312">
       <c r="B312" s="0" t="s">
+        <v>1402</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="D312" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E312" s="0" t="s">
+      <c r="F312" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="F312" s="0" t="s">
+      <c r="G312" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="G312" s="0" t="s">
+      <c r="H312" s="1" t="s">
         <v>1406</v>
-      </c>
-      <c r="H312" s="0" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="313">
       <c r="B313" s="0" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D313" s="1" t="s">
         <v>1408</v>
       </c>
-      <c r="D313" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E313" s="0" t="s">
+      <c r="F313" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="F313" s="0" t="s">
+      <c r="G313" s="1" t="s">
         <v>1410</v>
       </c>
-      <c r="G313" s="0" t="s">
+      <c r="H313" s="1" t="s">
         <v>1411</v>
-      </c>
-      <c r="H313" s="0" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="314">
       <c r="B314" s="0" t="s">
+        <v>1412</v>
+      </c>
+      <c r="D314" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="D314" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E314" s="0" t="s">
+      <c r="F314" s="1" t="s">
         <v>1414</v>
       </c>
-      <c r="F314" s="0" t="s">
+      <c r="G314" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="G314" s="0" t="s">
+      <c r="H314" s="1" t="s">
         <v>1416</v>
-      </c>
-      <c r="H314" s="0" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="315">
       <c r="B315" s="0" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D315" s="1" t="s">
         <v>1418</v>
       </c>
-      <c r="D315" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E315" s="0" t="s">
+      <c r="F315" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="F315" s="0" t="s">
+      <c r="G315" s="1" t="s">
         <v>1420</v>
       </c>
-      <c r="G315" s="0" t="s">
+      <c r="H315" s="1" t="s">
         <v>1421</v>
-      </c>
-      <c r="H315" s="0" t="s">
-        <v>1422</v>
       </c>
     </row>
     <row r="316">
       <c r="B316" s="0" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D316" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="D316" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E316" s="0" t="s">
+      <c r="F316" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="F316" s="0" t="s">
+      <c r="G316" s="1" t="s">
         <v>1425</v>
       </c>
-      <c r="G316" s="0" t="s">
+      <c r="H316" s="1" t="s">
         <v>1426</v>
-      </c>
-      <c r="H316" s="0" t="s">
-        <v>1427</v>
       </c>
     </row>
     <row r="317">
       <c r="B317" s="0" t="s">
+        <v>1427</v>
+      </c>
+      <c r="D317" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="D317" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E317" s="0" t="s">
+      <c r="F317" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="F317" s="0" t="s">
+      <c r="G317" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="G317" s="0" t="s">
+      <c r="H317" s="1" t="s">
         <v>1431</v>
-      </c>
-      <c r="H317" s="0" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="318">
       <c r="B318" s="0" t="s">
+        <v>1432</v>
+      </c>
+      <c r="D318" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="D318" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E318" s="0" t="s">
+      <c r="F318" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="F318" s="0" t="s">
+      <c r="G318" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="G318" s="0" t="s">
+      <c r="H318" s="1" t="s">
         <v>1436</v>
-      </c>
-      <c r="H318" s="0" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="319">
       <c r="B319" s="0" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D319" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="D319" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="E319" s="0" t="s">
+      <c r="F319" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="F319" s="0" t="s">
+      <c r="G319" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="G319" s="0" t="s">
+      <c r="H319" s="1" t="s">
         <v>1441</v>
-      </c>
-      <c r="H319" s="0" t="s">
-        <v>1442</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Localization/翻译文本/FlowyGraphLocalizationExport.xlsx
+++ b/Assets/Localization/翻译文本/FlowyGraphLocalizationExport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1442" uniqueCount="1442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="1457">
   <si>
     <t>#var</t>
   </si>
@@ -23,12 +23,12 @@
     <t>lTips1</t>
   </si>
   <si>
+    <t>lTips2</t>
+  </si>
+  <si>
     <t>zh-CN</t>
   </si>
   <si>
-    <t>lTips2</t>
-  </si>
-  <si>
     <t>en</t>
   </si>
   <si>
@@ -2984,6 +2984,24 @@
     <t>死者肉墊直接接觸了非常低溫的東西。</t>
   </si>
   <si>
+    <t>第一天_白猫_节点图_打招呼.3.0</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t>到底是怎么回事呢？</t>
+  </si>
+  <si>
+    <t>What's going on?</t>
+  </si>
+  <si>
+    <t>いったいどうしたのでしょうか？</t>
+  </si>
+  <si>
+    <t>到底是怎麼回事呢？</t>
+  </si>
+  <si>
     <t>第一天_警察_节点图_与警察交谈.7.0</t>
   </si>
   <si>
@@ -3996,6 +4014,33 @@
   </si>
   <si>
     <t>忙活了一上午，你終於把這裡的事情弄清楚了。</t>
+  </si>
+  <si>
+    <t>第一天_警察_节点图_打招呼.3.0</t>
+  </si>
+  <si>
+    <t>#Player#, 你来了！</t>
+  </si>
+  <si>
+    <t>#Player#, you're here!</t>
+  </si>
+  <si>
+    <t>#Player#、来たね！</t>
+  </si>
+  <si>
+    <t>#Player#，你來了！</t>
+  </si>
+  <si>
+    <t>第一天_警察_节点图_离开触发.3.0</t>
+  </si>
+  <si>
+    <t>加油！</t>
+  </si>
+  <si>
+    <t>Go for it!</t>
+  </si>
+  <si>
+    <t>頑張って！</t>
   </si>
   <si>
     <t>第一天_路人A_节点图_与路人A交谈.6.0</t>
@@ -4371,11 +4416,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0"/>
-    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4386,18 +4428,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H319"/>
+  <dimension ref="A1:H322"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1" style="1"/>
-    <col min="5" max="5" width="50" customWidth="1" style="1"/>
-    <col min="6" max="6" width="50" customWidth="1" style="1"/>
-    <col min="7" max="7" width="50" customWidth="1" style="1"/>
-    <col min="8" max="8" width="50" customWidth="1" style="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
@@ -4409,19 +4441,19 @@
       <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4435,19 +4467,19 @@
       <c r="C2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="0" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4455,16 +4487,16 @@
       <c r="B3" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="0" t="s">
         <v>11</v>
       </c>
     </row>
@@ -4472,16 +4504,16 @@
       <c r="B4" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="0" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4489,16 +4521,16 @@
       <c r="B5" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="0" t="s">
         <v>23</v>
       </c>
     </row>
@@ -4506,16 +4538,16 @@
       <c r="B6" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="0" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4523,16 +4555,16 @@
       <c r="B7" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="0" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4540,16 +4572,16 @@
       <c r="B8" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="0" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="0" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="0" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="0" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4557,16 +4589,16 @@
       <c r="B9" s="0" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="0" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="0" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="0" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="0" t="s">
         <v>43</v>
       </c>
     </row>
@@ -4574,16 +4606,16 @@
       <c r="B10" s="0" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="0" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="0" t="s">
         <v>48</v>
       </c>
     </row>
@@ -4591,16 +4623,16 @@
       <c r="B11" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="0" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="0" t="s">
         <v>51</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="0" t="s">
         <v>52</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="0" t="s">
         <v>53</v>
       </c>
     </row>
@@ -4608,16 +4640,16 @@
       <c r="B12" s="0" t="s">
         <v>54</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="0" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="0" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="0" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="0" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4625,16 +4657,16 @@
       <c r="B13" s="0" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="0" t="s">
         <v>60</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="0" t="s">
         <v>61</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="0" t="s">
         <v>63</v>
       </c>
     </row>
@@ -4642,16 +4674,16 @@
       <c r="B14" s="0" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="0" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="0" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="0" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="0" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4659,16 +4691,16 @@
       <c r="B15" s="0" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="0" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="0" t="s">
         <v>71</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="0" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="0" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4676,16 +4708,16 @@
       <c r="B16" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="0" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="0" t="s">
         <v>76</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="0" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4693,16 +4725,16 @@
       <c r="B17" s="0" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="0" t="s">
         <v>79</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="0" t="s">
         <v>80</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="0" t="s">
         <v>81</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="0" t="s">
         <v>82</v>
       </c>
     </row>
@@ -4710,16 +4742,16 @@
       <c r="B18" s="0" t="s">
         <v>83</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="0" t="s">
         <v>84</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="0" t="s">
         <v>85</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="0" t="s">
         <v>86</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="0" t="s">
         <v>87</v>
       </c>
     </row>
@@ -4727,16 +4759,16 @@
       <c r="B19" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="0" t="s">
         <v>89</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="0" t="s">
         <v>90</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="0" t="s">
         <v>91</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="0" t="s">
         <v>92</v>
       </c>
     </row>
@@ -4744,16 +4776,16 @@
       <c r="B20" s="0" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="0" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="0" t="s">
         <v>95</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="0" t="s">
         <v>96</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="0" t="s">
         <v>94</v>
       </c>
     </row>
@@ -4761,16 +4793,16 @@
       <c r="B21" s="0" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="0" t="s">
         <v>98</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="0" t="s">
         <v>100</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="0" t="s">
         <v>101</v>
       </c>
     </row>
@@ -4778,16 +4810,16 @@
       <c r="B22" s="0" t="s">
         <v>102</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="0" t="s">
         <v>103</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="0" t="s">
         <v>104</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="0" t="s">
         <v>105</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="0" t="s">
         <v>106</v>
       </c>
     </row>
@@ -4795,16 +4827,16 @@
       <c r="B23" s="0" t="s">
         <v>107</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="0" t="s">
         <v>109</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="0" t="s">
         <v>111</v>
       </c>
     </row>
@@ -4812,16 +4844,16 @@
       <c r="B24" s="0" t="s">
         <v>112</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="0" t="s">
         <v>113</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="0" t="s">
         <v>115</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="0" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4829,16 +4861,16 @@
       <c r="B25" s="0" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="0" t="s">
         <v>118</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="0" t="s">
         <v>119</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="0" t="s">
         <v>120</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="0" t="s">
         <v>121</v>
       </c>
     </row>
@@ -4846,16 +4878,16 @@
       <c r="B26" s="0" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="0" t="s">
         <v>124</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="0" t="s">
         <v>125</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="0" t="s">
         <v>126</v>
       </c>
     </row>
@@ -4863,16 +4895,16 @@
       <c r="B27" s="0" t="s">
         <v>127</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="0" t="s">
         <v>128</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="0" t="s">
         <v>129</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="0" t="s">
         <v>130</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="0" t="s">
         <v>131</v>
       </c>
     </row>
@@ -4880,16 +4912,16 @@
       <c r="B28" s="0" t="s">
         <v>132</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="0" t="s">
         <v>133</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="0" t="s">
         <v>134</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="0" t="s">
         <v>135</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="0" t="s">
         <v>136</v>
       </c>
     </row>
@@ -4897,16 +4929,16 @@
       <c r="B29" s="0" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="0" t="s">
         <v>138</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="0" t="s">
         <v>139</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="0" t="s">
         <v>140</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="0" t="s">
         <v>141</v>
       </c>
     </row>
@@ -4914,16 +4946,16 @@
       <c r="B30" s="0" t="s">
         <v>142</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="0" t="s">
         <v>143</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="0" t="s">
         <v>144</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="0" t="s">
         <v>145</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="0" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4931,16 +4963,16 @@
       <c r="B31" s="0" t="s">
         <v>147</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="E31" s="0" t="s">
         <v>148</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="0" t="s">
         <v>149</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="0" t="s">
         <v>150</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="0" t="s">
         <v>151</v>
       </c>
     </row>
@@ -4948,16 +4980,16 @@
       <c r="B32" s="0" t="s">
         <v>152</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="0" t="s">
         <v>153</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="0" t="s">
         <v>155</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="0" t="s">
         <v>156</v>
       </c>
     </row>
@@ -4965,16 +4997,16 @@
       <c r="B33" s="0" t="s">
         <v>157</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="0" t="s">
         <v>159</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="0" t="s">
         <v>158</v>
       </c>
     </row>
@@ -4982,16 +5014,16 @@
       <c r="B34" s="0" t="s">
         <v>160</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="0" t="s">
         <v>161</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="0" t="s">
         <v>163</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="0" t="s">
         <v>161</v>
       </c>
     </row>
@@ -4999,16 +5031,16 @@
       <c r="B35" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="0" t="s">
         <v>165</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="0" t="s">
         <v>167</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="0" t="s">
         <v>168</v>
       </c>
     </row>
@@ -5016,16 +5048,16 @@
       <c r="B36" s="0" t="s">
         <v>169</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="0" t="s">
         <v>170</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="0" t="s">
         <v>171</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="0" t="s">
         <v>173</v>
       </c>
     </row>
@@ -5033,16 +5065,16 @@
       <c r="B37" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="E37" s="0" t="s">
         <v>175</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="0" t="s">
         <v>176</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="0" t="s">
         <v>177</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="0" t="s">
         <v>175</v>
       </c>
     </row>
@@ -5050,16 +5082,16 @@
       <c r="B38" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="E38" s="0" t="s">
         <v>179</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="0" t="s">
         <v>181</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="0" t="s">
         <v>182</v>
       </c>
     </row>
@@ -5067,16 +5099,16 @@
       <c r="B39" s="0" t="s">
         <v>183</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="E39" s="0" t="s">
         <v>184</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="0" t="s">
         <v>185</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="0" t="s">
         <v>186</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="0" t="s">
         <v>187</v>
       </c>
     </row>
@@ -5084,16 +5116,16 @@
       <c r="B40" s="0" t="s">
         <v>188</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="E40" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="0" t="s">
         <v>190</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="0" t="s">
         <v>191</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="0" t="s">
         <v>189</v>
       </c>
     </row>
@@ -5101,16 +5133,16 @@
       <c r="B41" s="0" t="s">
         <v>192</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="E41" s="0" t="s">
         <v>193</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="0" t="s">
         <v>194</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="0" t="s">
         <v>195</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="0" t="s">
         <v>196</v>
       </c>
     </row>
@@ -5118,16 +5150,16 @@
       <c r="B42" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="E42" s="0" t="s">
         <v>198</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="0" t="s">
         <v>199</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="0" t="s">
         <v>200</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="0" t="s">
         <v>201</v>
       </c>
     </row>
@@ -5135,16 +5167,16 @@
       <c r="B43" s="0" t="s">
         <v>202</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="0" t="s">
         <v>203</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="0" t="s">
         <v>204</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="0" t="s">
         <v>205</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="0" t="s">
         <v>206</v>
       </c>
     </row>
@@ -5152,16 +5184,16 @@
       <c r="B44" s="0" t="s">
         <v>207</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="E44" s="0" t="s">
         <v>208</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="0" t="s">
         <v>210</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="0" t="s">
         <v>211</v>
       </c>
     </row>
@@ -5169,16 +5201,16 @@
       <c r="B45" s="0" t="s">
         <v>212</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="E45" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="0" t="s">
         <v>214</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="0" t="s">
         <v>215</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" s="0" t="s">
         <v>213</v>
       </c>
     </row>
@@ -5186,16 +5218,16 @@
       <c r="B46" s="0" t="s">
         <v>216</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="E46" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="0" t="s">
         <v>218</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="0" t="s">
         <v>219</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" s="0" t="s">
         <v>220</v>
       </c>
     </row>
@@ -5203,16 +5235,16 @@
       <c r="B47" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="E47" s="0" t="s">
         <v>222</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="0" t="s">
         <v>223</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="0" t="s">
         <v>224</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="0" t="s">
         <v>225</v>
       </c>
     </row>
@@ -5220,16 +5252,16 @@
       <c r="B48" s="0" t="s">
         <v>226</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="E48" s="0" t="s">
         <v>227</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="0" t="s">
         <v>228</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="0" t="s">
         <v>229</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="0" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5237,16 +5269,16 @@
       <c r="B49" s="0" t="s">
         <v>231</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="E49" s="0" t="s">
         <v>232</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="0" t="s">
         <v>233</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="0" t="s">
         <v>234</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="0" t="s">
         <v>235</v>
       </c>
     </row>
@@ -5254,16 +5286,16 @@
       <c r="B50" s="0" t="s">
         <v>236</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="0" t="s">
         <v>237</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="0" t="s">
         <v>238</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="0" t="s">
         <v>239</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="0" t="s">
         <v>240</v>
       </c>
     </row>
@@ -5271,16 +5303,16 @@
       <c r="B51" s="0" t="s">
         <v>241</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="E51" s="0" t="s">
         <v>242</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="0" t="s">
         <v>243</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="0" t="s">
         <v>244</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="0" t="s">
         <v>245</v>
       </c>
     </row>
@@ -5288,16 +5320,16 @@
       <c r="B52" s="0" t="s">
         <v>246</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="E52" s="0" t="s">
         <v>247</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="0" t="s">
         <v>248</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="0" t="s">
         <v>249</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="H52" s="0" t="s">
         <v>250</v>
       </c>
     </row>
@@ -5305,16 +5337,16 @@
       <c r="B53" s="0" t="s">
         <v>251</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="E53" s="0" t="s">
         <v>252</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="0" t="s">
         <v>253</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="0" t="s">
         <v>254</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H53" s="0" t="s">
         <v>255</v>
       </c>
     </row>
@@ -5322,16 +5354,16 @@
       <c r="B54" s="0" t="s">
         <v>256</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="E54" s="0" t="s">
         <v>257</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="0" t="s">
         <v>258</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="0" t="s">
         <v>259</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H54" s="0" t="s">
         <v>260</v>
       </c>
     </row>
@@ -5339,16 +5371,16 @@
       <c r="B55" s="0" t="s">
         <v>261</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="E55" s="0" t="s">
         <v>262</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="0" t="s">
         <v>263</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="0" t="s">
         <v>264</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" s="0" t="s">
         <v>265</v>
       </c>
     </row>
@@ -5356,16 +5388,16 @@
       <c r="B56" s="0" t="s">
         <v>266</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="E56" s="0" t="s">
         <v>267</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="0" t="s">
         <v>268</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="0" t="s">
         <v>269</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="0" t="s">
         <v>270</v>
       </c>
     </row>
@@ -5373,16 +5405,16 @@
       <c r="B57" s="0" t="s">
         <v>271</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="E57" s="0" t="s">
         <v>272</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="0" t="s">
         <v>273</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="0" t="s">
         <v>274</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="0" t="s">
         <v>275</v>
       </c>
     </row>
@@ -5390,16 +5422,16 @@
       <c r="B58" s="0" t="s">
         <v>276</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="E58" s="0" t="s">
         <v>277</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="0" t="s">
         <v>278</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="0" t="s">
         <v>279</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="H58" s="0" t="s">
         <v>280</v>
       </c>
     </row>
@@ -5407,16 +5439,16 @@
       <c r="B59" s="0" t="s">
         <v>281</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="E59" s="0" t="s">
         <v>282</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="0" t="s">
         <v>283</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="0" t="s">
         <v>284</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="0" t="s">
         <v>285</v>
       </c>
     </row>
@@ -5424,16 +5456,16 @@
       <c r="B60" s="0" t="s">
         <v>286</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="E60" s="0" t="s">
         <v>287</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="0" t="s">
         <v>288</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="0" t="s">
         <v>289</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" s="0" t="s">
         <v>290</v>
       </c>
     </row>
@@ -5441,16 +5473,16 @@
       <c r="B61" s="0" t="s">
         <v>291</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="E61" s="0" t="s">
         <v>292</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="0" t="s">
         <v>293</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="G61" s="0" t="s">
         <v>294</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="H61" s="0" t="s">
         <v>295</v>
       </c>
     </row>
@@ -5458,16 +5490,16 @@
       <c r="B62" s="0" t="s">
         <v>296</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="E62" s="0" t="s">
         <v>297</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="0" t="s">
         <v>298</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="G62" s="0" t="s">
         <v>299</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H62" s="0" t="s">
         <v>300</v>
       </c>
     </row>
@@ -5475,16 +5507,16 @@
       <c r="B63" s="0" t="s">
         <v>301</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="E63" s="0" t="s">
         <v>302</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="0" t="s">
         <v>303</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="G63" s="0" t="s">
         <v>304</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H63" s="0" t="s">
         <v>305</v>
       </c>
     </row>
@@ -5492,16 +5524,16 @@
       <c r="B64" s="0" t="s">
         <v>306</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="E64" s="0" t="s">
         <v>307</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="0" t="s">
         <v>308</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="G64" s="0" t="s">
         <v>309</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="H64" s="0" t="s">
         <v>310</v>
       </c>
     </row>
@@ -5509,16 +5541,16 @@
       <c r="B65" s="0" t="s">
         <v>311</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="E65" s="0" t="s">
         <v>312</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="0" t="s">
         <v>313</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G65" s="0" t="s">
         <v>314</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="0" t="s">
         <v>315</v>
       </c>
     </row>
@@ -5526,16 +5558,16 @@
       <c r="B66" s="0" t="s">
         <v>316</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="E66" s="0" t="s">
         <v>317</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="0" t="s">
         <v>318</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="G66" s="0" t="s">
         <v>319</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="H66" s="0" t="s">
         <v>320</v>
       </c>
     </row>
@@ -5543,16 +5575,16 @@
       <c r="B67" s="0" t="s">
         <v>321</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="E67" s="0" t="s">
         <v>322</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="0" t="s">
         <v>323</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="G67" s="0" t="s">
         <v>324</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="0" t="s">
         <v>325</v>
       </c>
     </row>
@@ -5560,16 +5592,16 @@
       <c r="B68" s="0" t="s">
         <v>326</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="0" t="s">
         <v>327</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="0" t="s">
         <v>328</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="G68" s="0" t="s">
         <v>329</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" s="0" t="s">
         <v>330</v>
       </c>
     </row>
@@ -5577,16 +5609,16 @@
       <c r="B69" s="0" t="s">
         <v>331</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="E69" s="0" t="s">
         <v>332</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="0" t="s">
         <v>333</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="G69" s="0" t="s">
         <v>334</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="H69" s="0" t="s">
         <v>335</v>
       </c>
     </row>
@@ -5594,16 +5626,16 @@
       <c r="B70" s="0" t="s">
         <v>336</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="E70" s="0" t="s">
         <v>337</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="0" t="s">
         <v>338</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="G70" s="0" t="s">
         <v>339</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="H70" s="0" t="s">
         <v>340</v>
       </c>
     </row>
@@ -5611,16 +5643,16 @@
       <c r="B71" s="0" t="s">
         <v>341</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="E71" s="0" t="s">
         <v>342</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="0" t="s">
         <v>343</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="G71" s="0" t="s">
         <v>344</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H71" s="0" t="s">
         <v>345</v>
       </c>
     </row>
@@ -5628,16 +5660,16 @@
       <c r="B72" s="0" t="s">
         <v>346</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="E72" s="0" t="s">
         <v>347</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="0" t="s">
         <v>348</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="G72" s="0" t="s">
         <v>349</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="H72" s="0" t="s">
         <v>350</v>
       </c>
     </row>
@@ -5645,16 +5677,16 @@
       <c r="B73" s="0" t="s">
         <v>351</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="E73" s="0" t="s">
         <v>352</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="0" t="s">
         <v>353</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="G73" s="0" t="s">
         <v>354</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="0" t="s">
         <v>355</v>
       </c>
     </row>
@@ -5662,16 +5694,16 @@
       <c r="B74" s="0" t="s">
         <v>356</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="E74" s="0" t="s">
         <v>357</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="0" t="s">
         <v>358</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="G74" s="0" t="s">
         <v>359</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H74" s="0" t="s">
         <v>360</v>
       </c>
     </row>
@@ -5679,16 +5711,16 @@
       <c r="B75" s="0" t="s">
         <v>361</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="E75" s="0" t="s">
         <v>362</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="0" t="s">
         <v>363</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G75" s="0" t="s">
         <v>364</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H75" s="0" t="s">
         <v>365</v>
       </c>
     </row>
@@ -5696,16 +5728,16 @@
       <c r="B76" s="0" t="s">
         <v>366</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="E76" s="0" t="s">
         <v>367</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="0" t="s">
         <v>368</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="G76" s="0" t="s">
         <v>369</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="H76" s="0" t="s">
         <v>370</v>
       </c>
     </row>
@@ -5713,16 +5745,16 @@
       <c r="B77" s="0" t="s">
         <v>371</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="E77" s="0" t="s">
         <v>372</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="0" t="s">
         <v>373</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G77" s="0" t="s">
         <v>374</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="H77" s="0" t="s">
         <v>375</v>
       </c>
     </row>
@@ -5730,16 +5762,16 @@
       <c r="B78" s="0" t="s">
         <v>376</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="E78" s="0" t="s">
         <v>377</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="0" t="s">
         <v>378</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="G78" s="0" t="s">
         <v>379</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="H78" s="0" t="s">
         <v>380</v>
       </c>
     </row>
@@ -5747,16 +5779,16 @@
       <c r="B79" s="0" t="s">
         <v>381</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="E79" s="0" t="s">
         <v>382</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F79" s="0" t="s">
         <v>383</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="G79" s="0" t="s">
         <v>384</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="H79" s="0" t="s">
         <v>385</v>
       </c>
     </row>
@@ -5764,16 +5796,16 @@
       <c r="B80" s="0" t="s">
         <v>386</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="E80" s="0" t="s">
         <v>387</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" s="0" t="s">
         <v>388</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="G80" s="0" t="s">
         <v>389</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="H80" s="0" t="s">
         <v>390</v>
       </c>
     </row>
@@ -5781,16 +5813,16 @@
       <c r="B81" s="0" t="s">
         <v>391</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="E81" s="0" t="s">
         <v>392</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" s="0" t="s">
         <v>393</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="G81" s="0" t="s">
         <v>394</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H81" s="0" t="s">
         <v>395</v>
       </c>
     </row>
@@ -5798,16 +5830,16 @@
       <c r="B82" s="0" t="s">
         <v>396</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="E82" s="0" t="s">
         <v>397</v>
       </c>
-      <c r="F82" s="1" t="s">
+      <c r="F82" s="0" t="s">
         <v>398</v>
       </c>
-      <c r="G82" s="1" t="s">
+      <c r="G82" s="0" t="s">
         <v>399</v>
       </c>
-      <c r="H82" s="1" t="s">
+      <c r="H82" s="0" t="s">
         <v>400</v>
       </c>
     </row>
@@ -5815,16 +5847,16 @@
       <c r="B83" s="0" t="s">
         <v>401</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="E83" s="0" t="s">
         <v>402</v>
       </c>
-      <c r="F83" s="1" t="s">
+      <c r="F83" s="0" t="s">
         <v>403</v>
       </c>
-      <c r="G83" s="1" t="s">
+      <c r="G83" s="0" t="s">
         <v>404</v>
       </c>
-      <c r="H83" s="1" t="s">
+      <c r="H83" s="0" t="s">
         <v>405</v>
       </c>
     </row>
@@ -5832,16 +5864,16 @@
       <c r="B84" s="0" t="s">
         <v>406</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="E84" s="0" t="s">
         <v>407</v>
       </c>
-      <c r="F84" s="1" t="s">
+      <c r="F84" s="0" t="s">
         <v>408</v>
       </c>
-      <c r="G84" s="1" t="s">
+      <c r="G84" s="0" t="s">
         <v>409</v>
       </c>
-      <c r="H84" s="1" t="s">
+      <c r="H84" s="0" t="s">
         <v>410</v>
       </c>
     </row>
@@ -5849,16 +5881,16 @@
       <c r="B85" s="0" t="s">
         <v>411</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="E85" s="0" t="s">
         <v>412</v>
       </c>
-      <c r="F85" s="1" t="s">
+      <c r="F85" s="0" t="s">
         <v>413</v>
       </c>
-      <c r="G85" s="1" t="s">
+      <c r="G85" s="0" t="s">
         <v>414</v>
       </c>
-      <c r="H85" s="1" t="s">
+      <c r="H85" s="0" t="s">
         <v>415</v>
       </c>
     </row>
@@ -5866,16 +5898,16 @@
       <c r="B86" s="0" t="s">
         <v>416</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="E86" s="0" t="s">
         <v>417</v>
       </c>
-      <c r="F86" s="1" t="s">
+      <c r="F86" s="0" t="s">
         <v>418</v>
       </c>
-      <c r="G86" s="1" t="s">
+      <c r="G86" s="0" t="s">
         <v>419</v>
       </c>
-      <c r="H86" s="1" t="s">
+      <c r="H86" s="0" t="s">
         <v>420</v>
       </c>
     </row>
@@ -5883,16 +5915,16 @@
       <c r="B87" s="0" t="s">
         <v>421</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="E87" s="0" t="s">
         <v>422</v>
       </c>
-      <c r="F87" s="1" t="s">
+      <c r="F87" s="0" t="s">
         <v>423</v>
       </c>
-      <c r="G87" s="1" t="s">
+      <c r="G87" s="0" t="s">
         <v>424</v>
       </c>
-      <c r="H87" s="1" t="s">
+      <c r="H87" s="0" t="s">
         <v>425</v>
       </c>
     </row>
@@ -5900,16 +5932,16 @@
       <c r="B88" s="0" t="s">
         <v>426</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="E88" s="0" t="s">
         <v>427</v>
       </c>
-      <c r="F88" s="1" t="s">
+      <c r="F88" s="0" t="s">
         <v>428</v>
       </c>
-      <c r="G88" s="1" t="s">
+      <c r="G88" s="0" t="s">
         <v>429</v>
       </c>
-      <c r="H88" s="1" t="s">
+      <c r="H88" s="0" t="s">
         <v>430</v>
       </c>
     </row>
@@ -5917,16 +5949,16 @@
       <c r="B89" s="0" t="s">
         <v>431</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="E89" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="F89" s="1" t="s">
+      <c r="F89" s="0" t="s">
         <v>432</v>
       </c>
-      <c r="G89" s="1" t="s">
+      <c r="G89" s="0" t="s">
         <v>433</v>
       </c>
-      <c r="H89" s="1" t="s">
+      <c r="H89" s="0" t="s">
         <v>11</v>
       </c>
     </row>
@@ -5934,16 +5966,16 @@
       <c r="B90" s="0" t="s">
         <v>434</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="E90" s="0" t="s">
         <v>435</v>
       </c>
-      <c r="F90" s="1" t="s">
+      <c r="F90" s="0" t="s">
         <v>436</v>
       </c>
-      <c r="G90" s="1" t="s">
+      <c r="G90" s="0" t="s">
         <v>437</v>
       </c>
-      <c r="H90" s="1" t="s">
+      <c r="H90" s="0" t="s">
         <v>438</v>
       </c>
     </row>
@@ -5951,16 +5983,16 @@
       <c r="B91" s="0" t="s">
         <v>439</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="E91" s="0" t="s">
         <v>440</v>
       </c>
-      <c r="F91" s="1" t="s">
+      <c r="F91" s="0" t="s">
         <v>263</v>
       </c>
-      <c r="G91" s="1" t="s">
+      <c r="G91" s="0" t="s">
         <v>441</v>
       </c>
-      <c r="H91" s="1" t="s">
+      <c r="H91" s="0" t="s">
         <v>442</v>
       </c>
     </row>
@@ -5968,16 +6000,16 @@
       <c r="B92" s="0" t="s">
         <v>443</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="E92" s="0" t="s">
         <v>444</v>
       </c>
-      <c r="F92" s="1" t="s">
+      <c r="F92" s="0" t="s">
         <v>445</v>
       </c>
-      <c r="G92" s="1" t="s">
+      <c r="G92" s="0" t="s">
         <v>446</v>
       </c>
-      <c r="H92" s="1" t="s">
+      <c r="H92" s="0" t="s">
         <v>447</v>
       </c>
     </row>
@@ -5985,16 +6017,16 @@
       <c r="B93" s="0" t="s">
         <v>448</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="E93" s="0" t="s">
         <v>449</v>
       </c>
-      <c r="F93" s="1" t="s">
+      <c r="F93" s="0" t="s">
         <v>450</v>
       </c>
-      <c r="G93" s="1" t="s">
+      <c r="G93" s="0" t="s">
         <v>449</v>
       </c>
-      <c r="H93" s="1" t="s">
+      <c r="H93" s="0" t="s">
         <v>449</v>
       </c>
     </row>
@@ -6002,16 +6034,16 @@
       <c r="B94" s="0" t="s">
         <v>451</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="E94" s="0" t="s">
         <v>452</v>
       </c>
-      <c r="F94" s="1" t="s">
+      <c r="F94" s="0" t="s">
         <v>453</v>
       </c>
-      <c r="G94" s="1" t="s">
+      <c r="G94" s="0" t="s">
         <v>454</v>
       </c>
-      <c r="H94" s="1" t="s">
+      <c r="H94" s="0" t="s">
         <v>452</v>
       </c>
     </row>
@@ -6019,16 +6051,16 @@
       <c r="B95" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="E95" s="0" t="s">
         <v>456</v>
       </c>
-      <c r="F95" s="1" t="s">
+      <c r="F95" s="0" t="s">
         <v>457</v>
       </c>
-      <c r="G95" s="1" t="s">
+      <c r="G95" s="0" t="s">
         <v>458</v>
       </c>
-      <c r="H95" s="1" t="s">
+      <c r="H95" s="0" t="s">
         <v>459</v>
       </c>
     </row>
@@ -6036,16 +6068,16 @@
       <c r="B96" s="0" t="s">
         <v>460</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="E96" s="0" t="s">
         <v>461</v>
       </c>
-      <c r="F96" s="1" t="s">
+      <c r="F96" s="0" t="s">
         <v>462</v>
       </c>
-      <c r="G96" s="1" t="s">
+      <c r="G96" s="0" t="s">
         <v>463</v>
       </c>
-      <c r="H96" s="1" t="s">
+      <c r="H96" s="0" t="s">
         <v>464</v>
       </c>
     </row>
@@ -6053,16 +6085,16 @@
       <c r="B97" s="0" t="s">
         <v>465</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="E97" s="0" t="s">
         <v>466</v>
       </c>
-      <c r="F97" s="1" t="s">
+      <c r="F97" s="0" t="s">
         <v>467</v>
       </c>
-      <c r="G97" s="1" t="s">
+      <c r="G97" s="0" t="s">
         <v>468</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="H97" s="0" t="s">
         <v>469</v>
       </c>
     </row>
@@ -6070,16 +6102,16 @@
       <c r="B98" s="0" t="s">
         <v>470</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="E98" s="0" t="s">
         <v>471</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F98" s="0" t="s">
         <v>472</v>
       </c>
-      <c r="G98" s="1" t="s">
+      <c r="G98" s="0" t="s">
         <v>473</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H98" s="0" t="s">
         <v>474</v>
       </c>
     </row>
@@ -6087,16 +6119,16 @@
       <c r="B99" s="0" t="s">
         <v>475</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="E99" s="0" t="s">
         <v>476</v>
       </c>
-      <c r="F99" s="1" t="s">
+      <c r="F99" s="0" t="s">
         <v>477</v>
       </c>
-      <c r="G99" s="1" t="s">
+      <c r="G99" s="0" t="s">
         <v>478</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="H99" s="0" t="s">
         <v>479</v>
       </c>
     </row>
@@ -6104,16 +6136,16 @@
       <c r="B100" s="0" t="s">
         <v>480</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="E100" s="0" t="s">
         <v>481</v>
       </c>
-      <c r="F100" s="1" t="s">
+      <c r="F100" s="0" t="s">
         <v>482</v>
       </c>
-      <c r="G100" s="1" t="s">
+      <c r="G100" s="0" t="s">
         <v>483</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="H100" s="0" t="s">
         <v>484</v>
       </c>
     </row>
@@ -6121,16 +6153,16 @@
       <c r="B101" s="0" t="s">
         <v>485</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="E101" s="0" t="s">
         <v>486</v>
       </c>
-      <c r="F101" s="1" t="s">
+      <c r="F101" s="0" t="s">
         <v>487</v>
       </c>
-      <c r="G101" s="1" t="s">
+      <c r="G101" s="0" t="s">
         <v>488</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H101" s="0" t="s">
         <v>489</v>
       </c>
     </row>
@@ -6138,16 +6170,16 @@
       <c r="B102" s="0" t="s">
         <v>490</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="E102" s="0" t="s">
         <v>491</v>
       </c>
-      <c r="F102" s="1" t="s">
+      <c r="F102" s="0" t="s">
         <v>492</v>
       </c>
-      <c r="G102" s="1" t="s">
+      <c r="G102" s="0" t="s">
         <v>493</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="H102" s="0" t="s">
         <v>494</v>
       </c>
     </row>
@@ -6155,16 +6187,16 @@
       <c r="B103" s="0" t="s">
         <v>495</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="E103" s="0" t="s">
         <v>496</v>
       </c>
-      <c r="F103" s="1" t="s">
+      <c r="F103" s="0" t="s">
         <v>497</v>
       </c>
-      <c r="G103" s="1" t="s">
+      <c r="G103" s="0" t="s">
         <v>498</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="H103" s="0" t="s">
         <v>499</v>
       </c>
     </row>
@@ -6172,16 +6204,16 @@
       <c r="B104" s="0" t="s">
         <v>500</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="E104" s="0" t="s">
         <v>501</v>
       </c>
-      <c r="F104" s="1" t="s">
+      <c r="F104" s="0" t="s">
         <v>502</v>
       </c>
-      <c r="G104" s="1" t="s">
+      <c r="G104" s="0" t="s">
         <v>503</v>
       </c>
-      <c r="H104" s="1" t="s">
+      <c r="H104" s="0" t="s">
         <v>504</v>
       </c>
     </row>
@@ -6189,16 +6221,16 @@
       <c r="B105" s="0" t="s">
         <v>505</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="E105" s="0" t="s">
         <v>506</v>
       </c>
-      <c r="F105" s="1" t="s">
+      <c r="F105" s="0" t="s">
         <v>507</v>
       </c>
-      <c r="G105" s="1" t="s">
+      <c r="G105" s="0" t="s">
         <v>508</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="H105" s="0" t="s">
         <v>509</v>
       </c>
     </row>
@@ -6206,16 +6238,16 @@
       <c r="B106" s="0" t="s">
         <v>510</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="E106" s="0" t="s">
         <v>511</v>
       </c>
-      <c r="F106" s="1" t="s">
+      <c r="F106" s="0" t="s">
         <v>512</v>
       </c>
-      <c r="G106" s="1" t="s">
+      <c r="G106" s="0" t="s">
         <v>513</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="H106" s="0" t="s">
         <v>514</v>
       </c>
     </row>
@@ -6223,16 +6255,16 @@
       <c r="B107" s="0" t="s">
         <v>515</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="E107" s="0" t="s">
         <v>516</v>
       </c>
-      <c r="F107" s="1" t="s">
+      <c r="F107" s="0" t="s">
         <v>517</v>
       </c>
-      <c r="G107" s="1" t="s">
+      <c r="G107" s="0" t="s">
         <v>518</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="H107" s="0" t="s">
         <v>519</v>
       </c>
     </row>
@@ -6240,16 +6272,16 @@
       <c r="B108" s="0" t="s">
         <v>520</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="E108" s="0" t="s">
         <v>521</v>
       </c>
-      <c r="F108" s="1" t="s">
+      <c r="F108" s="0" t="s">
         <v>522</v>
       </c>
-      <c r="G108" s="1" t="s">
+      <c r="G108" s="0" t="s">
         <v>523</v>
       </c>
-      <c r="H108" s="1" t="s">
+      <c r="H108" s="0" t="s">
         <v>524</v>
       </c>
     </row>
@@ -6257,16 +6289,16 @@
       <c r="B109" s="0" t="s">
         <v>525</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="E109" s="0" t="s">
         <v>526</v>
       </c>
-      <c r="F109" s="1" t="s">
+      <c r="F109" s="0" t="s">
         <v>527</v>
       </c>
-      <c r="G109" s="1" t="s">
+      <c r="G109" s="0" t="s">
         <v>528</v>
       </c>
-      <c r="H109" s="1" t="s">
+      <c r="H109" s="0" t="s">
         <v>529</v>
       </c>
     </row>
@@ -6274,16 +6306,16 @@
       <c r="B110" s="0" t="s">
         <v>530</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="E110" s="0" t="s">
         <v>531</v>
       </c>
-      <c r="F110" s="1" t="s">
+      <c r="F110" s="0" t="s">
         <v>532</v>
       </c>
-      <c r="G110" s="1" t="s">
+      <c r="G110" s="0" t="s">
         <v>533</v>
       </c>
-      <c r="H110" s="1" t="s">
+      <c r="H110" s="0" t="s">
         <v>534</v>
       </c>
     </row>
@@ -6291,16 +6323,16 @@
       <c r="B111" s="0" t="s">
         <v>535</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="E111" s="0" t="s">
         <v>536</v>
       </c>
-      <c r="F111" s="1" t="s">
+      <c r="F111" s="0" t="s">
         <v>537</v>
       </c>
-      <c r="G111" s="1" t="s">
+      <c r="G111" s="0" t="s">
         <v>538</v>
       </c>
-      <c r="H111" s="1" t="s">
+      <c r="H111" s="0" t="s">
         <v>539</v>
       </c>
     </row>
@@ -6308,16 +6340,16 @@
       <c r="B112" s="0" t="s">
         <v>540</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="E112" s="0" t="s">
         <v>541</v>
       </c>
-      <c r="F112" s="1" t="s">
+      <c r="F112" s="0" t="s">
         <v>542</v>
       </c>
-      <c r="G112" s="1" t="s">
+      <c r="G112" s="0" t="s">
         <v>543</v>
       </c>
-      <c r="H112" s="1" t="s">
+      <c r="H112" s="0" t="s">
         <v>544</v>
       </c>
     </row>
@@ -6325,16 +6357,16 @@
       <c r="B113" s="0" t="s">
         <v>545</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="E113" s="0" t="s">
         <v>546</v>
       </c>
-      <c r="F113" s="1" t="s">
+      <c r="F113" s="0" t="s">
         <v>547</v>
       </c>
-      <c r="G113" s="1" t="s">
+      <c r="G113" s="0" t="s">
         <v>548</v>
       </c>
-      <c r="H113" s="1" t="s">
+      <c r="H113" s="0" t="s">
         <v>549</v>
       </c>
     </row>
@@ -6342,16 +6374,16 @@
       <c r="B114" s="0" t="s">
         <v>550</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="E114" s="0" t="s">
         <v>551</v>
       </c>
-      <c r="F114" s="1" t="s">
+      <c r="F114" s="0" t="s">
         <v>552</v>
       </c>
-      <c r="G114" s="1" t="s">
+      <c r="G114" s="0" t="s">
         <v>553</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="H114" s="0" t="s">
         <v>554</v>
       </c>
     </row>
@@ -6359,16 +6391,16 @@
       <c r="B115" s="0" t="s">
         <v>555</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="E115" s="0" t="s">
         <v>556</v>
       </c>
-      <c r="F115" s="1" t="s">
+      <c r="F115" s="0" t="s">
         <v>557</v>
       </c>
-      <c r="G115" s="1" t="s">
+      <c r="G115" s="0" t="s">
         <v>558</v>
       </c>
-      <c r="H115" s="1" t="s">
+      <c r="H115" s="0" t="s">
         <v>559</v>
       </c>
     </row>
@@ -6376,16 +6408,16 @@
       <c r="B116" s="0" t="s">
         <v>560</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="E116" s="0" t="s">
         <v>561</v>
       </c>
-      <c r="F116" s="1" t="s">
+      <c r="F116" s="0" t="s">
         <v>562</v>
       </c>
-      <c r="G116" s="1" t="s">
+      <c r="G116" s="0" t="s">
         <v>563</v>
       </c>
-      <c r="H116" s="1" t="s">
+      <c r="H116" s="0" t="s">
         <v>564</v>
       </c>
     </row>
@@ -6393,16 +6425,16 @@
       <c r="B117" s="0" t="s">
         <v>565</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="E117" s="0" t="s">
         <v>566</v>
       </c>
-      <c r="F117" s="1" t="s">
+      <c r="F117" s="0" t="s">
         <v>567</v>
       </c>
-      <c r="G117" s="1" t="s">
+      <c r="G117" s="0" t="s">
         <v>568</v>
       </c>
-      <c r="H117" s="1" t="s">
+      <c r="H117" s="0" t="s">
         <v>569</v>
       </c>
     </row>
@@ -6410,16 +6442,16 @@
       <c r="B118" s="0" t="s">
         <v>570</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="E118" s="0" t="s">
         <v>571</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="F118" s="0" t="s">
         <v>572</v>
       </c>
-      <c r="G118" s="1" t="s">
+      <c r="G118" s="0" t="s">
         <v>573</v>
       </c>
-      <c r="H118" s="1" t="s">
+      <c r="H118" s="0" t="s">
         <v>571</v>
       </c>
     </row>
@@ -6427,16 +6459,16 @@
       <c r="B119" s="0" t="s">
         <v>574</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="E119" s="0" t="s">
         <v>575</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="F119" s="0" t="s">
         <v>576</v>
       </c>
-      <c r="G119" s="1" t="s">
+      <c r="G119" s="0" t="s">
         <v>577</v>
       </c>
-      <c r="H119" s="1" t="s">
+      <c r="H119" s="0" t="s">
         <v>578</v>
       </c>
     </row>
@@ -6444,16 +6476,16 @@
       <c r="B120" s="0" t="s">
         <v>579</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="E120" s="0" t="s">
         <v>580</v>
       </c>
-      <c r="F120" s="1" t="s">
+      <c r="F120" s="0" t="s">
         <v>581</v>
       </c>
-      <c r="G120" s="1" t="s">
+      <c r="G120" s="0" t="s">
         <v>582</v>
       </c>
-      <c r="H120" s="1" t="s">
+      <c r="H120" s="0" t="s">
         <v>583</v>
       </c>
     </row>
@@ -6461,16 +6493,16 @@
       <c r="B121" s="0" t="s">
         <v>584</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="E121" s="0" t="s">
         <v>585</v>
       </c>
-      <c r="F121" s="1" t="s">
+      <c r="F121" s="0" t="s">
         <v>586</v>
       </c>
-      <c r="G121" s="1" t="s">
+      <c r="G121" s="0" t="s">
         <v>587</v>
       </c>
-      <c r="H121" s="1" t="s">
+      <c r="H121" s="0" t="s">
         <v>588</v>
       </c>
     </row>
@@ -6478,16 +6510,16 @@
       <c r="B122" s="0" t="s">
         <v>589</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="E122" s="0" t="s">
         <v>590</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F122" s="0" t="s">
         <v>591</v>
       </c>
-      <c r="G122" s="1" t="s">
+      <c r="G122" s="0" t="s">
         <v>592</v>
       </c>
-      <c r="H122" s="1" t="s">
+      <c r="H122" s="0" t="s">
         <v>590</v>
       </c>
     </row>
@@ -6495,16 +6527,16 @@
       <c r="B123" s="0" t="s">
         <v>593</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="E123" s="0" t="s">
         <v>594</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="F123" s="0" t="s">
         <v>595</v>
       </c>
-      <c r="G123" s="1" t="s">
+      <c r="G123" s="0" t="s">
         <v>596</v>
       </c>
-      <c r="H123" s="1" t="s">
+      <c r="H123" s="0" t="s">
         <v>597</v>
       </c>
     </row>
@@ -6512,16 +6544,16 @@
       <c r="B124" s="0" t="s">
         <v>598</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="E124" s="0" t="s">
         <v>599</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="F124" s="0" t="s">
         <v>600</v>
       </c>
-      <c r="G124" s="1" t="s">
+      <c r="G124" s="0" t="s">
         <v>601</v>
       </c>
-      <c r="H124" s="1" t="s">
+      <c r="H124" s="0" t="s">
         <v>602</v>
       </c>
     </row>
@@ -6529,16 +6561,16 @@
       <c r="B125" s="0" t="s">
         <v>603</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="E125" s="0" t="s">
         <v>604</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="F125" s="0" t="s">
         <v>605</v>
       </c>
-      <c r="G125" s="1" t="s">
+      <c r="G125" s="0" t="s">
         <v>606</v>
       </c>
-      <c r="H125" s="1" t="s">
+      <c r="H125" s="0" t="s">
         <v>607</v>
       </c>
     </row>
@@ -6546,16 +6578,16 @@
       <c r="B126" s="0" t="s">
         <v>608</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="E126" s="0" t="s">
         <v>541</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F126" s="0" t="s">
         <v>542</v>
       </c>
-      <c r="G126" s="1" t="s">
+      <c r="G126" s="0" t="s">
         <v>543</v>
       </c>
-      <c r="H126" s="1" t="s">
+      <c r="H126" s="0" t="s">
         <v>544</v>
       </c>
     </row>
@@ -6563,16 +6595,16 @@
       <c r="B127" s="0" t="s">
         <v>609</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="E127" s="0" t="s">
         <v>610</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F127" s="0" t="s">
         <v>611</v>
       </c>
-      <c r="G127" s="1" t="s">
+      <c r="G127" s="0" t="s">
         <v>612</v>
       </c>
-      <c r="H127" s="1" t="s">
+      <c r="H127" s="0" t="s">
         <v>613</v>
       </c>
     </row>
@@ -6580,16 +6612,16 @@
       <c r="B128" s="0" t="s">
         <v>614</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="E128" s="0" t="s">
         <v>615</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="F128" s="0" t="s">
         <v>616</v>
       </c>
-      <c r="G128" s="1" t="s">
+      <c r="G128" s="0" t="s">
         <v>617</v>
       </c>
-      <c r="H128" s="1" t="s">
+      <c r="H128" s="0" t="s">
         <v>618</v>
       </c>
     </row>
@@ -6597,16 +6629,16 @@
       <c r="B129" s="0" t="s">
         <v>619</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="E129" s="0" t="s">
         <v>620</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F129" s="0" t="s">
         <v>621</v>
       </c>
-      <c r="G129" s="1" t="s">
+      <c r="G129" s="0" t="s">
         <v>622</v>
       </c>
-      <c r="H129" s="1" t="s">
+      <c r="H129" s="0" t="s">
         <v>620</v>
       </c>
     </row>
@@ -6614,16 +6646,16 @@
       <c r="B130" s="0" t="s">
         <v>623</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="E130" s="0" t="s">
         <v>624</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="F130" s="0" t="s">
         <v>625</v>
       </c>
-      <c r="G130" s="1" t="s">
+      <c r="G130" s="0" t="s">
         <v>626</v>
       </c>
-      <c r="H130" s="1" t="s">
+      <c r="H130" s="0" t="s">
         <v>627</v>
       </c>
     </row>
@@ -6631,16 +6663,16 @@
       <c r="B131" s="0" t="s">
         <v>628</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="E131" s="0" t="s">
         <v>629</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F131" s="0" t="s">
         <v>630</v>
       </c>
-      <c r="G131" s="1" t="s">
+      <c r="G131" s="0" t="s">
         <v>631</v>
       </c>
-      <c r="H131" s="1" t="s">
+      <c r="H131" s="0" t="s">
         <v>632</v>
       </c>
     </row>
@@ -6648,16 +6680,16 @@
       <c r="B132" s="0" t="s">
         <v>633</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="E132" s="0" t="s">
         <v>634</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="F132" s="0" t="s">
         <v>635</v>
       </c>
-      <c r="G132" s="1" t="s">
+      <c r="G132" s="0" t="s">
         <v>636</v>
       </c>
-      <c r="H132" s="1" t="s">
+      <c r="H132" s="0" t="s">
         <v>637</v>
       </c>
     </row>
@@ -6665,16 +6697,16 @@
       <c r="B133" s="0" t="s">
         <v>638</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="E133" s="0" t="s">
         <v>639</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="F133" s="0" t="s">
         <v>640</v>
       </c>
-      <c r="G133" s="1" t="s">
+      <c r="G133" s="0" t="s">
         <v>641</v>
       </c>
-      <c r="H133" s="1" t="s">
+      <c r="H133" s="0" t="s">
         <v>642</v>
       </c>
     </row>
@@ -6682,16 +6714,16 @@
       <c r="B134" s="0" t="s">
         <v>643</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="E134" s="0" t="s">
         <v>644</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F134" s="0" t="s">
         <v>645</v>
       </c>
-      <c r="G134" s="1" t="s">
+      <c r="G134" s="0" t="s">
         <v>646</v>
       </c>
-      <c r="H134" s="1" t="s">
+      <c r="H134" s="0" t="s">
         <v>647</v>
       </c>
     </row>
@@ -6699,16 +6731,16 @@
       <c r="B135" s="0" t="s">
         <v>648</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="E135" s="0" t="s">
         <v>123</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="F135" s="0" t="s">
         <v>649</v>
       </c>
-      <c r="G135" s="1" t="s">
+      <c r="G135" s="0" t="s">
         <v>650</v>
       </c>
-      <c r="H135" s="1" t="s">
+      <c r="H135" s="0" t="s">
         <v>126</v>
       </c>
     </row>
@@ -6716,16 +6748,16 @@
       <c r="B136" s="0" t="s">
         <v>651</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="E136" s="0" t="s">
         <v>652</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="F136" s="0" t="s">
         <v>653</v>
       </c>
-      <c r="G136" s="1" t="s">
+      <c r="G136" s="0" t="s">
         <v>654</v>
       </c>
-      <c r="H136" s="1" t="s">
+      <c r="H136" s="0" t="s">
         <v>655</v>
       </c>
     </row>
@@ -6733,16 +6765,16 @@
       <c r="B137" s="0" t="s">
         <v>656</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="E137" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="F137" s="0" t="s">
         <v>658</v>
       </c>
-      <c r="G137" s="1" t="s">
+      <c r="G137" s="0" t="s">
         <v>659</v>
       </c>
-      <c r="H137" s="1" t="s">
+      <c r="H137" s="0" t="s">
         <v>660</v>
       </c>
     </row>
@@ -6750,16 +6782,16 @@
       <c r="B138" s="0" t="s">
         <v>661</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="E138" s="0" t="s">
         <v>662</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F138" s="0" t="s">
         <v>663</v>
       </c>
-      <c r="G138" s="1" t="s">
+      <c r="G138" s="0" t="s">
         <v>664</v>
       </c>
-      <c r="H138" s="1" t="s">
+      <c r="H138" s="0" t="s">
         <v>665</v>
       </c>
     </row>
@@ -6767,16 +6799,16 @@
       <c r="B139" s="0" t="s">
         <v>666</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="E139" s="0" t="s">
         <v>667</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="F139" s="0" t="s">
         <v>668</v>
       </c>
-      <c r="G139" s="1" t="s">
+      <c r="G139" s="0" t="s">
         <v>669</v>
       </c>
-      <c r="H139" s="1" t="s">
+      <c r="H139" s="0" t="s">
         <v>670</v>
       </c>
     </row>
@@ -6784,16 +6816,16 @@
       <c r="B140" s="0" t="s">
         <v>671</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="E140" s="0" t="s">
         <v>672</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="F140" s="0" t="s">
         <v>673</v>
       </c>
-      <c r="G140" s="1" t="s">
+      <c r="G140" s="0" t="s">
         <v>674</v>
       </c>
-      <c r="H140" s="1" t="s">
+      <c r="H140" s="0" t="s">
         <v>675</v>
       </c>
     </row>
@@ -6801,16 +6833,16 @@
       <c r="B141" s="0" t="s">
         <v>676</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="E141" s="0" t="s">
         <v>677</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="F141" s="0" t="s">
         <v>678</v>
       </c>
-      <c r="G141" s="1" t="s">
+      <c r="G141" s="0" t="s">
         <v>679</v>
       </c>
-      <c r="H141" s="1" t="s">
+      <c r="H141" s="0" t="s">
         <v>680</v>
       </c>
     </row>
@@ -6818,16 +6850,16 @@
       <c r="B142" s="0" t="s">
         <v>681</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="E142" s="0" t="s">
         <v>682</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="F142" s="0" t="s">
         <v>683</v>
       </c>
-      <c r="G142" s="1" t="s">
+      <c r="G142" s="0" t="s">
         <v>684</v>
       </c>
-      <c r="H142" s="1" t="s">
+      <c r="H142" s="0" t="s">
         <v>685</v>
       </c>
     </row>
@@ -6835,16 +6867,16 @@
       <c r="B143" s="0" t="s">
         <v>686</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="E143" s="0" t="s">
         <v>687</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="F143" s="0" t="s">
         <v>688</v>
       </c>
-      <c r="G143" s="1" t="s">
+      <c r="G143" s="0" t="s">
         <v>689</v>
       </c>
-      <c r="H143" s="1" t="s">
+      <c r="H143" s="0" t="s">
         <v>690</v>
       </c>
     </row>
@@ -6852,16 +6884,16 @@
       <c r="B144" s="0" t="s">
         <v>691</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="E144" s="0" t="s">
         <v>692</v>
       </c>
-      <c r="F144" s="1" t="s">
+      <c r="F144" s="0" t="s">
         <v>693</v>
       </c>
-      <c r="G144" s="1" t="s">
+      <c r="G144" s="0" t="s">
         <v>694</v>
       </c>
-      <c r="H144" s="1" t="s">
+      <c r="H144" s="0" t="s">
         <v>695</v>
       </c>
     </row>
@@ -6869,16 +6901,16 @@
       <c r="B145" s="0" t="s">
         <v>696</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="E145" s="0" t="s">
         <v>697</v>
       </c>
-      <c r="F145" s="1" t="s">
+      <c r="F145" s="0" t="s">
         <v>698</v>
       </c>
-      <c r="G145" s="1" t="s">
+      <c r="G145" s="0" t="s">
         <v>699</v>
       </c>
-      <c r="H145" s="1" t="s">
+      <c r="H145" s="0" t="s">
         <v>700</v>
       </c>
     </row>
@@ -6886,16 +6918,16 @@
       <c r="B146" s="0" t="s">
         <v>701</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="E146" s="0" t="s">
         <v>702</v>
       </c>
-      <c r="F146" s="1" t="s">
+      <c r="F146" s="0" t="s">
         <v>703</v>
       </c>
-      <c r="G146" s="1" t="s">
+      <c r="G146" s="0" t="s">
         <v>704</v>
       </c>
-      <c r="H146" s="1" t="s">
+      <c r="H146" s="0" t="s">
         <v>705</v>
       </c>
     </row>
@@ -6903,16 +6935,16 @@
       <c r="B147" s="0" t="s">
         <v>706</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="E147" s="0" t="s">
         <v>707</v>
       </c>
-      <c r="F147" s="1" t="s">
+      <c r="F147" s="0" t="s">
         <v>708</v>
       </c>
-      <c r="G147" s="1" t="s">
+      <c r="G147" s="0" t="s">
         <v>709</v>
       </c>
-      <c r="H147" s="1" t="s">
+      <c r="H147" s="0" t="s">
         <v>710</v>
       </c>
     </row>
@@ -6920,16 +6952,16 @@
       <c r="B148" s="0" t="s">
         <v>711</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="E148" s="0" t="s">
         <v>712</v>
       </c>
-      <c r="F148" s="1" t="s">
+      <c r="F148" s="0" t="s">
         <v>713</v>
       </c>
-      <c r="G148" s="1" t="s">
+      <c r="G148" s="0" t="s">
         <v>714</v>
       </c>
-      <c r="H148" s="1" t="s">
+      <c r="H148" s="0" t="s">
         <v>715</v>
       </c>
     </row>
@@ -6937,16 +6969,16 @@
       <c r="B149" s="0" t="s">
         <v>716</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="E149" s="0" t="s">
         <v>717</v>
       </c>
-      <c r="F149" s="1" t="s">
+      <c r="F149" s="0" t="s">
         <v>718</v>
       </c>
-      <c r="G149" s="1" t="s">
+      <c r="G149" s="0" t="s">
         <v>719</v>
       </c>
-      <c r="H149" s="1" t="s">
+      <c r="H149" s="0" t="s">
         <v>720</v>
       </c>
     </row>
@@ -6954,16 +6986,16 @@
       <c r="B150" s="0" t="s">
         <v>721</v>
       </c>
-      <c r="D150" s="1" t="s">
+      <c r="E150" s="0" t="s">
         <v>722</v>
       </c>
-      <c r="F150" s="1" t="s">
+      <c r="F150" s="0" t="s">
         <v>723</v>
       </c>
-      <c r="G150" s="1" t="s">
+      <c r="G150" s="0" t="s">
         <v>724</v>
       </c>
-      <c r="H150" s="1" t="s">
+      <c r="H150" s="0" t="s">
         <v>725</v>
       </c>
     </row>
@@ -6971,16 +7003,16 @@
       <c r="B151" s="0" t="s">
         <v>726</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="E151" s="0" t="s">
         <v>727</v>
       </c>
-      <c r="F151" s="1" t="s">
+      <c r="F151" s="0" t="s">
         <v>728</v>
       </c>
-      <c r="G151" s="1" t="s">
+      <c r="G151" s="0" t="s">
         <v>729</v>
       </c>
-      <c r="H151" s="1" t="s">
+      <c r="H151" s="0" t="s">
         <v>730</v>
       </c>
     </row>
@@ -6988,16 +7020,16 @@
       <c r="B152" s="0" t="s">
         <v>731</v>
       </c>
-      <c r="D152" s="1" t="s">
+      <c r="E152" s="0" t="s">
         <v>624</v>
       </c>
-      <c r="F152" s="1" t="s">
+      <c r="F152" s="0" t="s">
         <v>625</v>
       </c>
-      <c r="G152" s="1" t="s">
+      <c r="G152" s="0" t="s">
         <v>732</v>
       </c>
-      <c r="H152" s="1" t="s">
+      <c r="H152" s="0" t="s">
         <v>627</v>
       </c>
     </row>
@@ -7005,16 +7037,16 @@
       <c r="B153" s="0" t="s">
         <v>733</v>
       </c>
-      <c r="D153" s="1" t="s">
+      <c r="E153" s="0" t="s">
         <v>734</v>
       </c>
-      <c r="F153" s="1" t="s">
+      <c r="F153" s="0" t="s">
         <v>735</v>
       </c>
-      <c r="G153" s="1" t="s">
+      <c r="G153" s="0" t="s">
         <v>736</v>
       </c>
-      <c r="H153" s="1" t="s">
+      <c r="H153" s="0" t="s">
         <v>737</v>
       </c>
     </row>
@@ -7022,16 +7054,16 @@
       <c r="B154" s="0" t="s">
         <v>738</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="E154" s="0" t="s">
         <v>739</v>
       </c>
-      <c r="F154" s="1" t="s">
+      <c r="F154" s="0" t="s">
         <v>740</v>
       </c>
-      <c r="G154" s="1" t="s">
+      <c r="G154" s="0" t="s">
         <v>741</v>
       </c>
-      <c r="H154" s="1" t="s">
+      <c r="H154" s="0" t="s">
         <v>742</v>
       </c>
     </row>
@@ -7039,16 +7071,16 @@
       <c r="B155" s="0" t="s">
         <v>743</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="E155" s="0" t="s">
         <v>744</v>
       </c>
-      <c r="F155" s="1" t="s">
+      <c r="F155" s="0" t="s">
         <v>745</v>
       </c>
-      <c r="G155" s="1" t="s">
+      <c r="G155" s="0" t="s">
         <v>746</v>
       </c>
-      <c r="H155" s="1" t="s">
+      <c r="H155" s="0" t="s">
         <v>747</v>
       </c>
     </row>
@@ -7056,16 +7088,16 @@
       <c r="B156" s="0" t="s">
         <v>748</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="E156" s="0" t="s">
         <v>749</v>
       </c>
-      <c r="F156" s="1" t="s">
+      <c r="F156" s="0" t="s">
         <v>750</v>
       </c>
-      <c r="G156" s="1" t="s">
+      <c r="G156" s="0" t="s">
         <v>751</v>
       </c>
-      <c r="H156" s="1" t="s">
+      <c r="H156" s="0" t="s">
         <v>752</v>
       </c>
     </row>
@@ -7073,16 +7105,16 @@
       <c r="B157" s="0" t="s">
         <v>753</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="E157" s="0" t="s">
         <v>754</v>
       </c>
-      <c r="F157" s="1" t="s">
+      <c r="F157" s="0" t="s">
         <v>755</v>
       </c>
-      <c r="G157" s="1" t="s">
+      <c r="G157" s="0" t="s">
         <v>756</v>
       </c>
-      <c r="H157" s="1" t="s">
+      <c r="H157" s="0" t="s">
         <v>757</v>
       </c>
     </row>
@@ -7090,16 +7122,16 @@
       <c r="B158" s="0" t="s">
         <v>758</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="E158" s="0" t="s">
         <v>657</v>
       </c>
-      <c r="F158" s="1" t="s">
+      <c r="F158" s="0" t="s">
         <v>759</v>
       </c>
-      <c r="G158" s="1" t="s">
+      <c r="G158" s="0" t="s">
         <v>659</v>
       </c>
-      <c r="H158" s="1" t="s">
+      <c r="H158" s="0" t="s">
         <v>660</v>
       </c>
     </row>
@@ -7107,16 +7139,16 @@
       <c r="B159" s="0" t="s">
         <v>760</v>
       </c>
-      <c r="D159" s="1" t="s">
+      <c r="E159" s="0" t="s">
         <v>761</v>
       </c>
-      <c r="F159" s="1" t="s">
+      <c r="F159" s="0" t="s">
         <v>762</v>
       </c>
-      <c r="G159" s="1" t="s">
+      <c r="G159" s="0" t="s">
         <v>763</v>
       </c>
-      <c r="H159" s="1" t="s">
+      <c r="H159" s="0" t="s">
         <v>764</v>
       </c>
     </row>
@@ -7124,16 +7156,16 @@
       <c r="B160" s="0" t="s">
         <v>765</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="E160" s="0" t="s">
         <v>766</v>
       </c>
-      <c r="F160" s="1" t="s">
+      <c r="F160" s="0" t="s">
         <v>767</v>
       </c>
-      <c r="G160" s="1" t="s">
+      <c r="G160" s="0" t="s">
         <v>768</v>
       </c>
-      <c r="H160" s="1" t="s">
+      <c r="H160" s="0" t="s">
         <v>769</v>
       </c>
     </row>
@@ -7141,16 +7173,16 @@
       <c r="B161" s="0" t="s">
         <v>770</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="E161" s="0" t="s">
         <v>771</v>
       </c>
-      <c r="F161" s="1" t="s">
+      <c r="F161" s="0" t="s">
         <v>772</v>
       </c>
-      <c r="G161" s="1" t="s">
+      <c r="G161" s="0" t="s">
         <v>773</v>
       </c>
-      <c r="H161" s="1" t="s">
+      <c r="H161" s="0" t="s">
         <v>774</v>
       </c>
     </row>
@@ -7158,16 +7190,16 @@
       <c r="B162" s="0" t="s">
         <v>775</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="E162" s="0" t="s">
         <v>776</v>
       </c>
-      <c r="F162" s="1" t="s">
+      <c r="F162" s="0" t="s">
         <v>777</v>
       </c>
-      <c r="G162" s="1" t="s">
+      <c r="G162" s="0" t="s">
         <v>778</v>
       </c>
-      <c r="H162" s="1" t="s">
+      <c r="H162" s="0" t="s">
         <v>779</v>
       </c>
     </row>
@@ -7175,16 +7207,16 @@
       <c r="B163" s="0" t="s">
         <v>780</v>
       </c>
-      <c r="D163" s="1" t="s">
+      <c r="E163" s="0" t="s">
         <v>781</v>
       </c>
-      <c r="F163" s="1" t="s">
+      <c r="F163" s="0" t="s">
         <v>782</v>
       </c>
-      <c r="G163" s="1" t="s">
+      <c r="G163" s="0" t="s">
         <v>783</v>
       </c>
-      <c r="H163" s="1" t="s">
+      <c r="H163" s="0" t="s">
         <v>784</v>
       </c>
     </row>
@@ -7192,16 +7224,16 @@
       <c r="B164" s="0" t="s">
         <v>785</v>
       </c>
-      <c r="D164" s="1" t="s">
+      <c r="E164" s="0" t="s">
         <v>786</v>
       </c>
-      <c r="F164" s="1" t="s">
+      <c r="F164" s="0" t="s">
         <v>787</v>
       </c>
-      <c r="G164" s="1" t="s">
+      <c r="G164" s="0" t="s">
         <v>788</v>
       </c>
-      <c r="H164" s="1" t="s">
+      <c r="H164" s="0" t="s">
         <v>789</v>
       </c>
     </row>
@@ -7209,16 +7241,16 @@
       <c r="B165" s="0" t="s">
         <v>790</v>
       </c>
-      <c r="D165" s="1" t="s">
+      <c r="E165" s="0" t="s">
         <v>791</v>
       </c>
-      <c r="F165" s="1" t="s">
+      <c r="F165" s="0" t="s">
         <v>792</v>
       </c>
-      <c r="G165" s="1" t="s">
+      <c r="G165" s="0" t="s">
         <v>793</v>
       </c>
-      <c r="H165" s="1" t="s">
+      <c r="H165" s="0" t="s">
         <v>794</v>
       </c>
     </row>
@@ -7226,16 +7258,16 @@
       <c r="B166" s="0" t="s">
         <v>795</v>
       </c>
-      <c r="D166" s="1" t="s">
+      <c r="E166" s="0" t="s">
         <v>796</v>
       </c>
-      <c r="F166" s="1" t="s">
+      <c r="F166" s="0" t="s">
         <v>797</v>
       </c>
-      <c r="G166" s="1" t="s">
+      <c r="G166" s="0" t="s">
         <v>798</v>
       </c>
-      <c r="H166" s="1" t="s">
+      <c r="H166" s="0" t="s">
         <v>799</v>
       </c>
     </row>
@@ -7243,16 +7275,16 @@
       <c r="B167" s="0" t="s">
         <v>800</v>
       </c>
-      <c r="D167" s="1" t="s">
+      <c r="E167" s="0" t="s">
         <v>801</v>
       </c>
-      <c r="F167" s="1" t="s">
+      <c r="F167" s="0" t="s">
         <v>802</v>
       </c>
-      <c r="G167" s="1" t="s">
+      <c r="G167" s="0" t="s">
         <v>803</v>
       </c>
-      <c r="H167" s="1" t="s">
+      <c r="H167" s="0" t="s">
         <v>804</v>
       </c>
     </row>
@@ -7260,16 +7292,16 @@
       <c r="B168" s="0" t="s">
         <v>805</v>
       </c>
-      <c r="D168" s="1" t="s">
+      <c r="E168" s="0" t="s">
         <v>806</v>
       </c>
-      <c r="F168" s="1" t="s">
+      <c r="F168" s="0" t="s">
         <v>807</v>
       </c>
-      <c r="G168" s="1" t="s">
+      <c r="G168" s="0" t="s">
         <v>808</v>
       </c>
-      <c r="H168" s="1" t="s">
+      <c r="H168" s="0" t="s">
         <v>809</v>
       </c>
     </row>
@@ -7277,16 +7309,16 @@
       <c r="B169" s="0" t="s">
         <v>810</v>
       </c>
-      <c r="D169" s="1" t="s">
+      <c r="E169" s="0" t="s">
         <v>811</v>
       </c>
-      <c r="F169" s="1" t="s">
+      <c r="F169" s="0" t="s">
         <v>812</v>
       </c>
-      <c r="G169" s="1" t="s">
+      <c r="G169" s="0" t="s">
         <v>813</v>
       </c>
-      <c r="H169" s="1" t="s">
+      <c r="H169" s="0" t="s">
         <v>814</v>
       </c>
     </row>
@@ -7294,16 +7326,16 @@
       <c r="B170" s="0" t="s">
         <v>815</v>
       </c>
-      <c r="D170" s="1" t="s">
+      <c r="E170" s="0" t="s">
         <v>816</v>
       </c>
-      <c r="F170" s="1" t="s">
+      <c r="F170" s="0" t="s">
         <v>817</v>
       </c>
-      <c r="G170" s="1" t="s">
+      <c r="G170" s="0" t="s">
         <v>818</v>
       </c>
-      <c r="H170" s="1" t="s">
+      <c r="H170" s="0" t="s">
         <v>819</v>
       </c>
     </row>
@@ -7311,16 +7343,16 @@
       <c r="B171" s="0" t="s">
         <v>820</v>
       </c>
-      <c r="D171" s="1" t="s">
+      <c r="E171" s="0" t="s">
         <v>821</v>
       </c>
-      <c r="F171" s="1" t="s">
+      <c r="F171" s="0" t="s">
         <v>822</v>
       </c>
-      <c r="G171" s="1" t="s">
+      <c r="G171" s="0" t="s">
         <v>823</v>
       </c>
-      <c r="H171" s="1" t="s">
+      <c r="H171" s="0" t="s">
         <v>824</v>
       </c>
     </row>
@@ -7328,16 +7360,16 @@
       <c r="B172" s="0" t="s">
         <v>825</v>
       </c>
-      <c r="D172" s="1" t="s">
+      <c r="E172" s="0" t="s">
         <v>826</v>
       </c>
-      <c r="F172" s="1" t="s">
+      <c r="F172" s="0" t="s">
         <v>827</v>
       </c>
-      <c r="G172" s="1" t="s">
+      <c r="G172" s="0" t="s">
         <v>828</v>
       </c>
-      <c r="H172" s="1" t="s">
+      <c r="H172" s="0" t="s">
         <v>829</v>
       </c>
     </row>
@@ -7345,16 +7377,16 @@
       <c r="B173" s="0" t="s">
         <v>830</v>
       </c>
-      <c r="D173" s="1" t="s">
+      <c r="E173" s="0" t="s">
         <v>831</v>
       </c>
-      <c r="F173" s="1" t="s">
+      <c r="F173" s="0" t="s">
         <v>832</v>
       </c>
-      <c r="G173" s="1" t="s">
+      <c r="G173" s="0" t="s">
         <v>833</v>
       </c>
-      <c r="H173" s="1" t="s">
+      <c r="H173" s="0" t="s">
         <v>834</v>
       </c>
     </row>
@@ -7362,16 +7394,16 @@
       <c r="B174" s="0" t="s">
         <v>835</v>
       </c>
-      <c r="D174" s="1" t="s">
+      <c r="E174" s="0" t="s">
         <v>836</v>
       </c>
-      <c r="F174" s="1" t="s">
+      <c r="F174" s="0" t="s">
         <v>837</v>
       </c>
-      <c r="G174" s="1" t="s">
+      <c r="G174" s="0" t="s">
         <v>838</v>
       </c>
-      <c r="H174" s="1" t="s">
+      <c r="H174" s="0" t="s">
         <v>839</v>
       </c>
     </row>
@@ -7379,16 +7411,16 @@
       <c r="B175" s="0" t="s">
         <v>840</v>
       </c>
-      <c r="D175" s="1" t="s">
+      <c r="E175" s="0" t="s">
         <v>841</v>
       </c>
-      <c r="F175" s="1" t="s">
+      <c r="F175" s="0" t="s">
         <v>842</v>
       </c>
-      <c r="G175" s="1" t="s">
+      <c r="G175" s="0" t="s">
         <v>843</v>
       </c>
-      <c r="H175" s="1" t="s">
+      <c r="H175" s="0" t="s">
         <v>844</v>
       </c>
     </row>
@@ -7396,16 +7428,16 @@
       <c r="B176" s="0" t="s">
         <v>845</v>
       </c>
-      <c r="D176" s="1" t="s">
+      <c r="E176" s="0" t="s">
         <v>846</v>
       </c>
-      <c r="F176" s="1" t="s">
+      <c r="F176" s="0" t="s">
         <v>847</v>
       </c>
-      <c r="G176" s="1" t="s">
+      <c r="G176" s="0" t="s">
         <v>848</v>
       </c>
-      <c r="H176" s="1" t="s">
+      <c r="H176" s="0" t="s">
         <v>849</v>
       </c>
     </row>
@@ -7413,16 +7445,16 @@
       <c r="B177" s="0" t="s">
         <v>850</v>
       </c>
-      <c r="D177" s="1" t="s">
+      <c r="E177" s="0" t="s">
         <v>851</v>
       </c>
-      <c r="F177" s="1" t="s">
+      <c r="F177" s="0" t="s">
         <v>852</v>
       </c>
-      <c r="G177" s="1" t="s">
+      <c r="G177" s="0" t="s">
         <v>853</v>
       </c>
-      <c r="H177" s="1" t="s">
+      <c r="H177" s="0" t="s">
         <v>854</v>
       </c>
     </row>
@@ -7430,16 +7462,16 @@
       <c r="B178" s="0" t="s">
         <v>855</v>
       </c>
-      <c r="D178" s="1" t="s">
+      <c r="E178" s="0" t="s">
         <v>856</v>
       </c>
-      <c r="F178" s="1" t="s">
+      <c r="F178" s="0" t="s">
         <v>857</v>
       </c>
-      <c r="G178" s="1" t="s">
+      <c r="G178" s="0" t="s">
         <v>858</v>
       </c>
-      <c r="H178" s="1" t="s">
+      <c r="H178" s="0" t="s">
         <v>859</v>
       </c>
     </row>
@@ -7447,16 +7479,16 @@
       <c r="B179" s="0" t="s">
         <v>860</v>
       </c>
-      <c r="D179" s="1" t="s">
+      <c r="E179" s="0" t="s">
         <v>861</v>
       </c>
-      <c r="F179" s="1" t="s">
+      <c r="F179" s="0" t="s">
         <v>862</v>
       </c>
-      <c r="G179" s="1" t="s">
+      <c r="G179" s="0" t="s">
         <v>863</v>
       </c>
-      <c r="H179" s="1" t="s">
+      <c r="H179" s="0" t="s">
         <v>864</v>
       </c>
     </row>
@@ -7464,16 +7496,16 @@
       <c r="B180" s="0" t="s">
         <v>865</v>
       </c>
-      <c r="D180" s="1" t="s">
+      <c r="E180" s="0" t="s">
         <v>866</v>
       </c>
-      <c r="F180" s="1" t="s">
+      <c r="F180" s="0" t="s">
         <v>867</v>
       </c>
-      <c r="G180" s="1" t="s">
+      <c r="G180" s="0" t="s">
         <v>868</v>
       </c>
-      <c r="H180" s="1" t="s">
+      <c r="H180" s="0" t="s">
         <v>869</v>
       </c>
     </row>
@@ -7481,16 +7513,16 @@
       <c r="B181" s="0" t="s">
         <v>870</v>
       </c>
-      <c r="D181" s="1" t="s">
+      <c r="E181" s="0" t="s">
         <v>871</v>
       </c>
-      <c r="F181" s="1" t="s">
+      <c r="F181" s="0" t="s">
         <v>872</v>
       </c>
-      <c r="G181" s="1" t="s">
+      <c r="G181" s="0" t="s">
         <v>873</v>
       </c>
-      <c r="H181" s="1" t="s">
+      <c r="H181" s="0" t="s">
         <v>874</v>
       </c>
     </row>
@@ -7498,16 +7530,16 @@
       <c r="B182" s="0" t="s">
         <v>875</v>
       </c>
-      <c r="D182" s="1" t="s">
+      <c r="E182" s="0" t="s">
         <v>876</v>
       </c>
-      <c r="F182" s="1" t="s">
+      <c r="F182" s="0" t="s">
         <v>877</v>
       </c>
-      <c r="G182" s="1" t="s">
+      <c r="G182" s="0" t="s">
         <v>878</v>
       </c>
-      <c r="H182" s="1" t="s">
+      <c r="H182" s="0" t="s">
         <v>879</v>
       </c>
     </row>
@@ -7515,16 +7547,16 @@
       <c r="B183" s="0" t="s">
         <v>880</v>
       </c>
-      <c r="D183" s="1" t="s">
+      <c r="E183" s="0" t="s">
         <v>881</v>
       </c>
-      <c r="F183" s="1" t="s">
+      <c r="F183" s="0" t="s">
         <v>882</v>
       </c>
-      <c r="G183" s="1" t="s">
+      <c r="G183" s="0" t="s">
         <v>883</v>
       </c>
-      <c r="H183" s="1" t="s">
+      <c r="H183" s="0" t="s">
         <v>884</v>
       </c>
     </row>
@@ -7532,16 +7564,16 @@
       <c r="B184" s="0" t="s">
         <v>885</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="E184" s="0" t="s">
         <v>886</v>
       </c>
-      <c r="F184" s="1" t="s">
+      <c r="F184" s="0" t="s">
         <v>887</v>
       </c>
-      <c r="G184" s="1" t="s">
+      <c r="G184" s="0" t="s">
         <v>888</v>
       </c>
-      <c r="H184" s="1" t="s">
+      <c r="H184" s="0" t="s">
         <v>889</v>
       </c>
     </row>
@@ -7549,16 +7581,16 @@
       <c r="B185" s="0" t="s">
         <v>890</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="E185" s="0" t="s">
         <v>891</v>
       </c>
-      <c r="F185" s="1" t="s">
+      <c r="F185" s="0" t="s">
         <v>892</v>
       </c>
-      <c r="G185" s="1" t="s">
+      <c r="G185" s="0" t="s">
         <v>893</v>
       </c>
-      <c r="H185" s="1" t="s">
+      <c r="H185" s="0" t="s">
         <v>894</v>
       </c>
     </row>
@@ -7566,16 +7598,16 @@
       <c r="B186" s="0" t="s">
         <v>895</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="E186" s="0" t="s">
         <v>896</v>
       </c>
-      <c r="F186" s="1" t="s">
+      <c r="F186" s="0" t="s">
         <v>897</v>
       </c>
-      <c r="G186" s="1" t="s">
+      <c r="G186" s="0" t="s">
         <v>898</v>
       </c>
-      <c r="H186" s="1" t="s">
+      <c r="H186" s="0" t="s">
         <v>899</v>
       </c>
     </row>
@@ -7583,16 +7615,16 @@
       <c r="B187" s="0" t="s">
         <v>900</v>
       </c>
-      <c r="D187" s="1" t="s">
+      <c r="E187" s="0" t="s">
         <v>901</v>
       </c>
-      <c r="F187" s="1" t="s">
+      <c r="F187" s="0" t="s">
         <v>902</v>
       </c>
-      <c r="G187" s="1" t="s">
+      <c r="G187" s="0" t="s">
         <v>903</v>
       </c>
-      <c r="H187" s="1" t="s">
+      <c r="H187" s="0" t="s">
         <v>904</v>
       </c>
     </row>
@@ -7600,16 +7632,16 @@
       <c r="B188" s="0" t="s">
         <v>905</v>
       </c>
-      <c r="D188" s="1" t="s">
+      <c r="E188" s="0" t="s">
         <v>906</v>
       </c>
-      <c r="F188" s="1" t="s">
+      <c r="F188" s="0" t="s">
         <v>907</v>
       </c>
-      <c r="G188" s="1" t="s">
+      <c r="G188" s="0" t="s">
         <v>908</v>
       </c>
-      <c r="H188" s="1" t="s">
+      <c r="H188" s="0" t="s">
         <v>909</v>
       </c>
     </row>
@@ -7617,16 +7649,16 @@
       <c r="B189" s="0" t="s">
         <v>910</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="E189" s="0" t="s">
         <v>911</v>
       </c>
-      <c r="F189" s="1" t="s">
+      <c r="F189" s="0" t="s">
         <v>912</v>
       </c>
-      <c r="G189" s="1" t="s">
+      <c r="G189" s="0" t="s">
         <v>913</v>
       </c>
-      <c r="H189" s="1" t="s">
+      <c r="H189" s="0" t="s">
         <v>914</v>
       </c>
     </row>
@@ -7634,16 +7666,16 @@
       <c r="B190" s="0" t="s">
         <v>915</v>
       </c>
-      <c r="D190" s="1" t="s">
+      <c r="E190" s="0" t="s">
         <v>916</v>
       </c>
-      <c r="F190" s="1" t="s">
+      <c r="F190" s="0" t="s">
         <v>917</v>
       </c>
-      <c r="G190" s="1" t="s">
+      <c r="G190" s="0" t="s">
         <v>918</v>
       </c>
-      <c r="H190" s="1" t="s">
+      <c r="H190" s="0" t="s">
         <v>919</v>
       </c>
     </row>
@@ -7651,16 +7683,16 @@
       <c r="B191" s="0" t="s">
         <v>920</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="E191" s="0" t="s">
         <v>921</v>
       </c>
-      <c r="F191" s="1" t="s">
+      <c r="F191" s="0" t="s">
         <v>922</v>
       </c>
-      <c r="G191" s="1" t="s">
+      <c r="G191" s="0" t="s">
         <v>923</v>
       </c>
-      <c r="H191" s="1" t="s">
+      <c r="H191" s="0" t="s">
         <v>924</v>
       </c>
     </row>
@@ -7668,16 +7700,16 @@
       <c r="B192" s="0" t="s">
         <v>925</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="E192" s="0" t="s">
         <v>926</v>
       </c>
-      <c r="F192" s="1" t="s">
+      <c r="F192" s="0" t="s">
         <v>927</v>
       </c>
-      <c r="G192" s="1" t="s">
+      <c r="G192" s="0" t="s">
         <v>928</v>
       </c>
-      <c r="H192" s="1" t="s">
+      <c r="H192" s="0" t="s">
         <v>929</v>
       </c>
     </row>
@@ -7685,16 +7717,16 @@
       <c r="B193" s="0" t="s">
         <v>930</v>
       </c>
-      <c r="D193" s="1" t="s">
+      <c r="E193" s="0" t="s">
         <v>931</v>
       </c>
-      <c r="F193" s="1" t="s">
+      <c r="F193" s="0" t="s">
         <v>932</v>
       </c>
-      <c r="G193" s="1" t="s">
+      <c r="G193" s="0" t="s">
         <v>933</v>
       </c>
-      <c r="H193" s="1" t="s">
+      <c r="H193" s="0" t="s">
         <v>934</v>
       </c>
     </row>
@@ -7702,16 +7734,16 @@
       <c r="B194" s="0" t="s">
         <v>935</v>
       </c>
-      <c r="D194" s="1" t="s">
+      <c r="E194" s="0" t="s">
         <v>936</v>
       </c>
-      <c r="F194" s="1" t="s">
+      <c r="F194" s="0" t="s">
         <v>937</v>
       </c>
-      <c r="G194" s="1" t="s">
+      <c r="G194" s="0" t="s">
         <v>938</v>
       </c>
-      <c r="H194" s="1" t="s">
+      <c r="H194" s="0" t="s">
         <v>939</v>
       </c>
     </row>
@@ -7719,16 +7751,16 @@
       <c r="B195" s="0" t="s">
         <v>940</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="E195" s="0" t="s">
         <v>941</v>
       </c>
-      <c r="F195" s="1" t="s">
+      <c r="F195" s="0" t="s">
         <v>942</v>
       </c>
-      <c r="G195" s="1" t="s">
+      <c r="G195" s="0" t="s">
         <v>943</v>
       </c>
-      <c r="H195" s="1" t="s">
+      <c r="H195" s="0" t="s">
         <v>944</v>
       </c>
     </row>
@@ -7736,16 +7768,16 @@
       <c r="B196" s="0" t="s">
         <v>945</v>
       </c>
-      <c r="D196" s="1" t="s">
+      <c r="E196" s="0" t="s">
         <v>946</v>
       </c>
-      <c r="F196" s="1" t="s">
+      <c r="F196" s="0" t="s">
         <v>947</v>
       </c>
-      <c r="G196" s="1" t="s">
+      <c r="G196" s="0" t="s">
         <v>948</v>
       </c>
-      <c r="H196" s="1" t="s">
+      <c r="H196" s="0" t="s">
         <v>949</v>
       </c>
     </row>
@@ -7753,16 +7785,16 @@
       <c r="B197" s="0" t="s">
         <v>950</v>
       </c>
-      <c r="D197" s="1" t="s">
+      <c r="E197" s="0" t="s">
         <v>951</v>
       </c>
-      <c r="F197" s="1" t="s">
+      <c r="F197" s="0" t="s">
         <v>952</v>
       </c>
-      <c r="G197" s="1" t="s">
+      <c r="G197" s="0" t="s">
         <v>953</v>
       </c>
-      <c r="H197" s="1" t="s">
+      <c r="H197" s="0" t="s">
         <v>954</v>
       </c>
     </row>
@@ -7770,16 +7802,16 @@
       <c r="B198" s="0" t="s">
         <v>955</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="E198" s="0" t="s">
         <v>956</v>
       </c>
-      <c r="F198" s="1" t="s">
+      <c r="F198" s="0" t="s">
         <v>957</v>
       </c>
-      <c r="G198" s="1" t="s">
+      <c r="G198" s="0" t="s">
         <v>958</v>
       </c>
-      <c r="H198" s="1" t="s">
+      <c r="H198" s="0" t="s">
         <v>959</v>
       </c>
     </row>
@@ -7787,16 +7819,16 @@
       <c r="B199" s="0" t="s">
         <v>960</v>
       </c>
-      <c r="D199" s="1" t="s">
+      <c r="E199" s="0" t="s">
         <v>961</v>
       </c>
-      <c r="F199" s="1" t="s">
+      <c r="F199" s="0" t="s">
         <v>962</v>
       </c>
-      <c r="G199" s="1" t="s">
+      <c r="G199" s="0" t="s">
         <v>963</v>
       </c>
-      <c r="H199" s="1" t="s">
+      <c r="H199" s="0" t="s">
         <v>964</v>
       </c>
     </row>
@@ -7804,16 +7836,16 @@
       <c r="B200" s="0" t="s">
         <v>965</v>
       </c>
-      <c r="D200" s="1" t="s">
+      <c r="E200" s="0" t="s">
         <v>966</v>
       </c>
-      <c r="F200" s="1" t="s">
+      <c r="F200" s="0" t="s">
         <v>967</v>
       </c>
-      <c r="G200" s="1" t="s">
+      <c r="G200" s="0" t="s">
         <v>968</v>
       </c>
-      <c r="H200" s="1" t="s">
+      <c r="H200" s="0" t="s">
         <v>969</v>
       </c>
     </row>
@@ -7821,16 +7853,16 @@
       <c r="B201" s="0" t="s">
         <v>970</v>
       </c>
-      <c r="D201" s="1" t="s">
+      <c r="E201" s="0" t="s">
         <v>971</v>
       </c>
-      <c r="F201" s="1" t="s">
+      <c r="F201" s="0" t="s">
         <v>972</v>
       </c>
-      <c r="G201" s="1" t="s">
+      <c r="G201" s="0" t="s">
         <v>973</v>
       </c>
-      <c r="H201" s="1" t="s">
+      <c r="H201" s="0" t="s">
         <v>974</v>
       </c>
     </row>
@@ -7838,16 +7870,16 @@
       <c r="B202" s="0" t="s">
         <v>975</v>
       </c>
-      <c r="D202" s="1" t="s">
+      <c r="E202" s="0" t="s">
         <v>976</v>
       </c>
-      <c r="F202" s="1" t="s">
+      <c r="F202" s="0" t="s">
         <v>977</v>
       </c>
-      <c r="G202" s="1" t="s">
+      <c r="G202" s="0" t="s">
         <v>978</v>
       </c>
-      <c r="H202" s="1" t="s">
+      <c r="H202" s="0" t="s">
         <v>979</v>
       </c>
     </row>
@@ -7855,16 +7887,16 @@
       <c r="B203" s="0" t="s">
         <v>980</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="E203" s="0" t="s">
         <v>981</v>
       </c>
-      <c r="F203" s="1" t="s">
+      <c r="F203" s="0" t="s">
         <v>982</v>
       </c>
-      <c r="G203" s="1" t="s">
+      <c r="G203" s="0" t="s">
         <v>983</v>
       </c>
-      <c r="H203" s="1" t="s">
+      <c r="H203" s="0" t="s">
         <v>984</v>
       </c>
     </row>
@@ -7872,16 +7904,16 @@
       <c r="B204" s="0" t="s">
         <v>985</v>
       </c>
-      <c r="D204" s="1" t="s">
+      <c r="E204" s="0" t="s">
         <v>986</v>
       </c>
-      <c r="F204" s="1" t="s">
+      <c r="F204" s="0" t="s">
         <v>987</v>
       </c>
-      <c r="G204" s="1" t="s">
+      <c r="G204" s="0" t="s">
         <v>988</v>
       </c>
-      <c r="H204" s="1" t="s">
+      <c r="H204" s="0" t="s">
         <v>989</v>
       </c>
     </row>
@@ -7889,1631 +7921,1637 @@
       <c r="B205" s="0" t="s">
         <v>990</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="D205" s="0" t="s">
         <v>991</v>
       </c>
-      <c r="F205" s="1" t="s">
+      <c r="E205" s="0" t="s">
         <v>992</v>
       </c>
-      <c r="G205" s="1" t="s">
+      <c r="F205" s="0" t="s">
         <v>993</v>
       </c>
-      <c r="H205" s="1" t="s">
+      <c r="G205" s="0" t="s">
         <v>994</v>
+      </c>
+      <c r="H205" s="0" t="s">
+        <v>995</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" s="0" t="s">
-        <v>995</v>
-      </c>
-      <c r="D206" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="F206" s="1" t="s">
+      <c r="E206" s="0" t="s">
         <v>997</v>
       </c>
-      <c r="G206" s="1" t="s">
+      <c r="F206" s="0" t="s">
         <v>998</v>
       </c>
-      <c r="H206" s="1" t="s">
+      <c r="G206" s="0" t="s">
         <v>999</v>
+      </c>
+      <c r="H206" s="0" t="s">
+        <v>1000</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" s="0" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D207" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="F207" s="1" t="s">
+      <c r="E207" s="0" t="s">
         <v>1002</v>
       </c>
-      <c r="G207" s="1" t="s">
+      <c r="F207" s="0" t="s">
         <v>1003</v>
       </c>
-      <c r="H207" s="1" t="s">
+      <c r="G207" s="0" t="s">
         <v>1004</v>
+      </c>
+      <c r="H207" s="0" t="s">
+        <v>1005</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" s="0" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D208" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="F208" s="1" t="s">
+      <c r="E208" s="0" t="s">
         <v>1007</v>
       </c>
-      <c r="G208" s="1" t="s">
+      <c r="F208" s="0" t="s">
         <v>1008</v>
       </c>
-      <c r="H208" s="1" t="s">
+      <c r="G208" s="0" t="s">
         <v>1009</v>
+      </c>
+      <c r="H208" s="0" t="s">
+        <v>1010</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" s="0" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D209" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="F209" s="1" t="s">
+      <c r="E209" s="0" t="s">
         <v>1012</v>
       </c>
-      <c r="G209" s="1" t="s">
+      <c r="F209" s="0" t="s">
         <v>1013</v>
       </c>
-      <c r="H209" s="1" t="s">
+      <c r="G209" s="0" t="s">
         <v>1014</v>
+      </c>
+      <c r="H209" s="0" t="s">
+        <v>1015</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" s="0" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="F210" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="G210" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="H210" s="1" t="s">
-        <v>874</v>
+      <c r="E210" s="0" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F210" s="0" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G210" s="0" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H210" s="0" t="s">
+        <v>1020</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" s="0" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D211" s="1" t="s">
-        <v>1018</v>
-      </c>
-      <c r="F211" s="1" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G211" s="1" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H211" s="1" t="s">
         <v>1021</v>
+      </c>
+      <c r="E211" s="0" t="s">
+        <v>871</v>
+      </c>
+      <c r="F211" s="0" t="s">
+        <v>872</v>
+      </c>
+      <c r="G211" s="0" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H211" s="0" t="s">
+        <v>874</v>
       </c>
     </row>
     <row r="212">
       <c r="B212" s="0" t="s">
-        <v>1022</v>
-      </c>
-      <c r="D212" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="F212" s="1" t="s">
+      <c r="E212" s="0" t="s">
         <v>1024</v>
       </c>
-      <c r="G212" s="1" t="s">
+      <c r="F212" s="0" t="s">
         <v>1025</v>
       </c>
-      <c r="H212" s="1" t="s">
-        <v>1023</v>
+      <c r="G212" s="0" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H212" s="0" t="s">
+        <v>1027</v>
       </c>
     </row>
     <row r="213">
       <c r="B213" s="0" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F213" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="G213" s="1" t="s">
+      <c r="E213" s="0" t="s">
         <v>1029</v>
       </c>
-      <c r="H213" s="1" t="s">
+      <c r="F213" s="0" t="s">
         <v>1030</v>
+      </c>
+      <c r="G213" s="0" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H213" s="0" t="s">
+        <v>1029</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" s="0" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D214" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="F214" s="1" t="s">
+      <c r="E214" s="0" t="s">
         <v>1033</v>
       </c>
-      <c r="G214" s="1" t="s">
+      <c r="F214" s="0" t="s">
         <v>1034</v>
       </c>
-      <c r="H214" s="1" t="s">
+      <c r="G214" s="0" t="s">
         <v>1035</v>
+      </c>
+      <c r="H214" s="0" t="s">
+        <v>1036</v>
       </c>
     </row>
     <row r="215">
       <c r="B215" s="0" t="s">
-        <v>1036</v>
-      </c>
-      <c r="D215" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="F215" s="1" t="s">
+      <c r="E215" s="0" t="s">
         <v>1038</v>
       </c>
-      <c r="G215" s="1" t="s">
+      <c r="F215" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="H215" s="1" t="s">
+      <c r="G215" s="0" t="s">
         <v>1040</v>
+      </c>
+      <c r="H215" s="0" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" s="0" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D216" s="1" t="s">
         <v>1042</v>
       </c>
-      <c r="F216" s="1" t="s">
+      <c r="E216" s="0" t="s">
         <v>1043</v>
       </c>
-      <c r="G216" s="1" t="s">
+      <c r="F216" s="0" t="s">
         <v>1044</v>
       </c>
-      <c r="H216" s="1" t="s">
-        <v>1042</v>
+      <c r="G216" s="0" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H216" s="0" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" s="0" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F217" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G217" s="1" t="s">
-        <v>1034</v>
-      </c>
-      <c r="H217" s="1" t="s">
-        <v>1035</v>
+        <v>1047</v>
+      </c>
+      <c r="E217" s="0" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F217" s="0" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G217" s="0" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H217" s="0" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" s="0" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D218" s="1" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F218" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E218" s="0" t="s">
         <v>1038</v>
       </c>
-      <c r="G218" s="1" t="s">
+      <c r="F218" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="H218" s="1" t="s">
+      <c r="G218" s="0" t="s">
         <v>1040</v>
+      </c>
+      <c r="H218" s="0" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" s="0" t="s">
-        <v>1047</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F219" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E219" s="0" t="s">
         <v>1043</v>
       </c>
-      <c r="G219" s="1" t="s">
+      <c r="F219" s="0" t="s">
         <v>1044</v>
       </c>
-      <c r="H219" s="1" t="s">
-        <v>1042</v>
+      <c r="G219" s="0" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H219" s="0" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="220">
       <c r="B220" s="0" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E220" s="0" t="s">
         <v>1048</v>
       </c>
-      <c r="D220" s="1" t="s">
+      <c r="F220" s="0" t="s">
         <v>1049</v>
       </c>
-      <c r="F220" s="1" t="s">
+      <c r="G220" s="0" t="s">
         <v>1050</v>
       </c>
-      <c r="G220" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="H220" s="1" t="s">
-        <v>1049</v>
+      <c r="H220" s="0" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="221">
       <c r="B221" s="0" t="s">
-        <v>1052</v>
-      </c>
-      <c r="D221" s="1" t="s">
-        <v>1032</v>
-      </c>
-      <c r="F221" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="G221" s="1" t="s">
-        <v>1034</v>
-      </c>
-      <c r="H221" s="1" t="s">
-        <v>1035</v>
+        <v>1054</v>
+      </c>
+      <c r="E221" s="0" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F221" s="0" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G221" s="0" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H221" s="0" t="s">
+        <v>1055</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" s="0" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D222" s="1" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F222" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E222" s="0" t="s">
         <v>1038</v>
       </c>
-      <c r="G222" s="1" t="s">
+      <c r="F222" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="H222" s="1" t="s">
+      <c r="G222" s="0" t="s">
         <v>1040</v>
+      </c>
+      <c r="H222" s="0" t="s">
+        <v>1041</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" s="0" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>1042</v>
-      </c>
-      <c r="F223" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E223" s="0" t="s">
         <v>1043</v>
       </c>
-      <c r="G223" s="1" t="s">
+      <c r="F223" s="0" t="s">
         <v>1044</v>
       </c>
-      <c r="H223" s="1" t="s">
-        <v>1042</v>
+      <c r="G223" s="0" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H223" s="0" t="s">
+        <v>1046</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" s="0" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D224" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E224" s="0" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F224" s="0" t="s">
         <v>1049</v>
       </c>
-      <c r="F224" s="1" t="s">
+      <c r="G224" s="0" t="s">
         <v>1050</v>
       </c>
-      <c r="G224" s="1" t="s">
-        <v>1051</v>
-      </c>
-      <c r="H224" s="1" t="s">
-        <v>1049</v>
+      <c r="H224" s="0" t="s">
+        <v>1048</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" s="0" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E225" s="0" t="s">
+        <v>1055</v>
+      </c>
+      <c r="F225" s="0" t="s">
         <v>1056</v>
       </c>
-      <c r="D225" s="1" t="s">
+      <c r="G225" s="0" t="s">
         <v>1057</v>
       </c>
-      <c r="F225" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="G225" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="H225" s="1" t="s">
-        <v>1060</v>
+      <c r="H225" s="0" t="s">
+        <v>1055</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" s="0" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D226" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="F226" s="1" t="s">
+      <c r="E226" s="0" t="s">
         <v>1063</v>
       </c>
-      <c r="G226" s="1" t="s">
+      <c r="F226" s="0" t="s">
         <v>1064</v>
       </c>
-      <c r="H226" s="1" t="s">
+      <c r="G226" s="0" t="s">
         <v>1065</v>
+      </c>
+      <c r="H226" s="0" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" s="0" t="s">
-        <v>1066</v>
-      </c>
-      <c r="D227" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="F227" s="1" t="s">
+      <c r="E227" s="0" t="s">
         <v>1068</v>
       </c>
-      <c r="G227" s="1" t="s">
+      <c r="F227" s="0" t="s">
         <v>1069</v>
       </c>
-      <c r="H227" s="1" t="s">
+      <c r="G227" s="0" t="s">
         <v>1070</v>
+      </c>
+      <c r="H227" s="0" t="s">
+        <v>1071</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" s="0" t="s">
-        <v>1071</v>
-      </c>
-      <c r="D228" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="F228" s="1" t="s">
+      <c r="E228" s="0" t="s">
         <v>1073</v>
       </c>
-      <c r="G228" s="1" t="s">
+      <c r="F228" s="0" t="s">
         <v>1074</v>
       </c>
-      <c r="H228" s="1" t="s">
+      <c r="G228" s="0" t="s">
         <v>1075</v>
+      </c>
+      <c r="H228" s="0" t="s">
+        <v>1076</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" s="0" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D229" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="F229" s="1" t="s">
+      <c r="E229" s="0" t="s">
         <v>1078</v>
       </c>
-      <c r="G229" s="1" t="s">
+      <c r="F229" s="0" t="s">
         <v>1079</v>
       </c>
-      <c r="H229" s="1" t="s">
+      <c r="G229" s="0" t="s">
         <v>1080</v>
+      </c>
+      <c r="H229" s="0" t="s">
+        <v>1081</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" s="0" t="s">
-        <v>1081</v>
-      </c>
-      <c r="D230" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="F230" s="1" t="s">
+      <c r="E230" s="0" t="s">
         <v>1083</v>
       </c>
-      <c r="G230" s="1" t="s">
+      <c r="F230" s="0" t="s">
         <v>1084</v>
       </c>
-      <c r="H230" s="1" t="s">
+      <c r="G230" s="0" t="s">
         <v>1085</v>
+      </c>
+      <c r="H230" s="0" t="s">
+        <v>1086</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" s="0" t="s">
-        <v>1086</v>
-      </c>
-      <c r="D231" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="F231" s="1" t="s">
+      <c r="E231" s="0" t="s">
         <v>1088</v>
       </c>
-      <c r="G231" s="1" t="s">
+      <c r="F231" s="0" t="s">
         <v>1089</v>
       </c>
-      <c r="H231" s="1" t="s">
+      <c r="G231" s="0" t="s">
         <v>1090</v>
+      </c>
+      <c r="H231" s="0" t="s">
+        <v>1091</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" s="0" t="s">
-        <v>1091</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="F232" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="G232" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="H232" s="1" t="s">
-        <v>1060</v>
+        <v>1092</v>
+      </c>
+      <c r="E232" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F232" s="0" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G232" s="0" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H232" s="0" t="s">
+        <v>1096</v>
       </c>
     </row>
     <row r="233">
       <c r="B233" s="0" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D233" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="F233" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E233" s="0" t="s">
         <v>1063</v>
       </c>
-      <c r="G233" s="1" t="s">
+      <c r="F233" s="0" t="s">
         <v>1064</v>
       </c>
-      <c r="H233" s="1" t="s">
+      <c r="G233" s="0" t="s">
         <v>1065</v>
+      </c>
+      <c r="H233" s="0" t="s">
+        <v>1066</v>
       </c>
     </row>
     <row r="234">
       <c r="B234" s="0" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D234" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="F234" s="1" t="s">
-        <v>1095</v>
-      </c>
-      <c r="G234" s="1" t="s">
-        <v>1096</v>
-      </c>
-      <c r="H234" s="1" t="s">
-        <v>1097</v>
+        <v>1098</v>
+      </c>
+      <c r="E234" s="0" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F234" s="0" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G234" s="0" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H234" s="0" t="s">
+        <v>1071</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" s="0" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D235" s="1" t="s">
-        <v>1087</v>
-      </c>
-      <c r="F235" s="1" t="s">
-        <v>1088</v>
-      </c>
-      <c r="G235" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="H235" s="1" t="s">
-        <v>1090</v>
+        <v>1099</v>
+      </c>
+      <c r="E235" s="0" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F235" s="0" t="s">
+        <v>1101</v>
+      </c>
+      <c r="G235" s="0" t="s">
+        <v>1102</v>
+      </c>
+      <c r="H235" s="0" t="s">
+        <v>1103</v>
       </c>
     </row>
     <row r="236">
       <c r="B236" s="0" t="s">
-        <v>1099</v>
-      </c>
-      <c r="D236" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F236" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G236" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="H236" s="1" t="s">
-        <v>1103</v>
+        <v>1104</v>
+      </c>
+      <c r="E236" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F236" s="0" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G236" s="0" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H236" s="0" t="s">
+        <v>1096</v>
       </c>
     </row>
     <row r="237">
       <c r="B237" s="0" t="s">
-        <v>1104</v>
-      </c>
-      <c r="D237" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F237" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G237" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="H237" s="1" t="s">
-        <v>1103</v>
+        <v>1105</v>
+      </c>
+      <c r="E237" s="0" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F237" s="0" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G237" s="0" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H237" s="0" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" s="0" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D238" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E238" s="0" t="s">
         <v>1106</v>
       </c>
-      <c r="F238" s="1" t="s">
+      <c r="F238" s="0" t="s">
         <v>1107</v>
       </c>
-      <c r="G238" s="1" t="s">
+      <c r="G238" s="0" t="s">
         <v>1108</v>
       </c>
-      <c r="H238" s="1" t="s">
+      <c r="H238" s="0" t="s">
         <v>1109</v>
       </c>
     </row>
     <row r="239">
       <c r="B239" s="0" t="s">
-        <v>1110</v>
-      </c>
-      <c r="D239" s="1" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F239" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="G239" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="H239" s="1" t="s">
-        <v>1103</v>
+        <v>1111</v>
+      </c>
+      <c r="E239" s="0" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F239" s="0" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G239" s="0" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H239" s="0" t="s">
+        <v>1115</v>
       </c>
     </row>
     <row r="240">
       <c r="B240" s="0" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D240" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F240" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="G240" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H240" s="1" t="s">
-        <v>1115</v>
+        <v>1116</v>
+      </c>
+      <c r="E240" s="0" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F240" s="0" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G240" s="0" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H240" s="0" t="s">
+        <v>1109</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" s="0" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D241" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="F241" s="1" t="s">
+      <c r="E241" s="0" t="s">
         <v>1118</v>
       </c>
-      <c r="G241" s="1" t="s">
+      <c r="F241" s="0" t="s">
         <v>1119</v>
       </c>
-      <c r="H241" s="1" t="s">
+      <c r="G241" s="0" t="s">
         <v>1120</v>
+      </c>
+      <c r="H241" s="0" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="242">
       <c r="B242" s="0" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D242" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="F242" s="1" t="s">
+      <c r="E242" s="0" t="s">
         <v>1123</v>
       </c>
-      <c r="G242" s="1" t="s">
+      <c r="F242" s="0" t="s">
         <v>1124</v>
       </c>
-      <c r="H242" s="1" t="s">
+      <c r="G242" s="0" t="s">
         <v>1125</v>
+      </c>
+      <c r="H242" s="0" t="s">
+        <v>1126</v>
       </c>
     </row>
     <row r="243">
       <c r="B243" s="0" t="s">
-        <v>1126</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F243" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G243" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="H243" s="1" t="s">
-        <v>1125</v>
+        <v>1127</v>
+      </c>
+      <c r="E243" s="0" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F243" s="0" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G243" s="0" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H243" s="0" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="244">
       <c r="B244" s="0" t="s">
-        <v>1127</v>
-      </c>
-      <c r="D244" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E244" s="0" t="s">
         <v>1128</v>
       </c>
-      <c r="F244" s="1" t="s">
+      <c r="F244" s="0" t="s">
         <v>1129</v>
       </c>
-      <c r="G244" s="1" t="s">
+      <c r="G244" s="0" t="s">
         <v>1130</v>
       </c>
-      <c r="H244" s="1" t="s">
+      <c r="H244" s="0" t="s">
         <v>1131</v>
       </c>
     </row>
     <row r="245">
       <c r="B245" s="0" t="s">
-        <v>1132</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F245" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G245" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="H245" s="1" t="s">
-        <v>1125</v>
+        <v>1133</v>
+      </c>
+      <c r="E245" s="0" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F245" s="0" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G245" s="0" t="s">
+        <v>1136</v>
+      </c>
+      <c r="H245" s="0" t="s">
+        <v>1137</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" s="0" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D246" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F246" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G246" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="H246" s="1" t="s">
-        <v>1125</v>
+        <v>1138</v>
+      </c>
+      <c r="E246" s="0" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F246" s="0" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G246" s="0" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H246" s="0" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="247">
       <c r="B247" s="0" t="s">
-        <v>1134</v>
-      </c>
-      <c r="D247" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="F247" s="1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="G247" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="H247" s="1" t="s">
-        <v>1138</v>
+        <v>1139</v>
+      </c>
+      <c r="E247" s="0" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F247" s="0" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G247" s="0" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H247" s="0" t="s">
+        <v>1131</v>
       </c>
     </row>
     <row r="248">
       <c r="B248" s="0" t="s">
-        <v>1139</v>
-      </c>
-      <c r="D248" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F248" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="G248" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H248" s="1" t="s">
-        <v>1115</v>
+        <v>1140</v>
+      </c>
+      <c r="E248" s="0" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F248" s="0" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G248" s="0" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H248" s="0" t="s">
+        <v>1144</v>
       </c>
     </row>
     <row r="249">
       <c r="B249" s="0" t="s">
-        <v>1140</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F249" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="G249" s="1" t="s">
-        <v>1143</v>
-      </c>
-      <c r="H249" s="1" t="s">
-        <v>1144</v>
+        <v>1145</v>
+      </c>
+      <c r="E249" s="0" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F249" s="0" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G249" s="0" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H249" s="0" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="250">
       <c r="B250" s="0" t="s">
-        <v>1145</v>
-      </c>
-      <c r="D250" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F250" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="G250" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H250" s="1" t="s">
-        <v>1115</v>
+        <v>1146</v>
+      </c>
+      <c r="E250" s="0" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F250" s="0" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G250" s="0" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H250" s="0" t="s">
+        <v>1150</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" s="0" t="s">
-        <v>1146</v>
-      </c>
-      <c r="D251" s="1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F251" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="G251" s="1" t="s">
-        <v>1143</v>
-      </c>
-      <c r="H251" s="1" t="s">
-        <v>1144</v>
+        <v>1151</v>
+      </c>
+      <c r="E251" s="0" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F251" s="0" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G251" s="0" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H251" s="0" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="252">
       <c r="B252" s="0" t="s">
-        <v>1148</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F252" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E252" s="0" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F252" s="0" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G252" s="0" t="s">
         <v>1149</v>
       </c>
-      <c r="G252" s="1" t="s">
+      <c r="H252" s="0" t="s">
         <v>1150</v>
-      </c>
-      <c r="H252" s="1" t="s">
-        <v>1115</v>
       </c>
     </row>
     <row r="253">
       <c r="B253" s="0" t="s">
-        <v>1151</v>
-      </c>
-      <c r="D253" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F253" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="G253" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="H253" s="1" t="s">
-        <v>1115</v>
+        <v>1154</v>
+      </c>
+      <c r="E253" s="0" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F253" s="0" t="s">
+        <v>1155</v>
+      </c>
+      <c r="G253" s="0" t="s">
+        <v>1156</v>
+      </c>
+      <c r="H253" s="0" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="254">
       <c r="B254" s="0" t="s">
-        <v>1152</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F254" s="1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="G254" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E254" s="0" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F254" s="0" t="s">
         <v>1155</v>
       </c>
-      <c r="H254" s="1" t="s">
+      <c r="G254" s="0" t="s">
         <v>1156</v>
+      </c>
+      <c r="H254" s="0" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="255">
       <c r="B255" s="0" t="s">
-        <v>1157</v>
-      </c>
-      <c r="D255" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="F255" s="1" t="s">
+      <c r="E255" s="0" t="s">
         <v>1159</v>
       </c>
-      <c r="G255" s="1" t="s">
+      <c r="F255" s="0" t="s">
         <v>1160</v>
       </c>
-      <c r="H255" s="1" t="s">
+      <c r="G255" s="0" t="s">
         <v>1161</v>
+      </c>
+      <c r="H255" s="0" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="256">
       <c r="B256" s="0" t="s">
-        <v>1162</v>
-      </c>
-      <c r="D256" s="1" t="s">
         <v>1163</v>
       </c>
-      <c r="F256" s="1" t="s">
+      <c r="E256" s="0" t="s">
         <v>1164</v>
       </c>
-      <c r="G256" s="1" t="s">
+      <c r="F256" s="0" t="s">
         <v>1165</v>
       </c>
-      <c r="H256" s="1" t="s">
+      <c r="G256" s="0" t="s">
         <v>1166</v>
+      </c>
+      <c r="H256" s="0" t="s">
+        <v>1167</v>
       </c>
     </row>
     <row r="257">
       <c r="B257" s="0" t="s">
-        <v>1167</v>
-      </c>
-      <c r="D257" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="F257" s="1" t="s">
+      <c r="E257" s="0" t="s">
         <v>1169</v>
       </c>
-      <c r="G257" s="1" t="s">
+      <c r="F257" s="0" t="s">
         <v>1170</v>
       </c>
-      <c r="H257" s="1" t="s">
+      <c r="G257" s="0" t="s">
         <v>1171</v>
+      </c>
+      <c r="H257" s="0" t="s">
+        <v>1172</v>
       </c>
     </row>
     <row r="258">
       <c r="B258" s="0" t="s">
-        <v>1172</v>
-      </c>
-      <c r="D258" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="F258" s="1" t="s">
+      <c r="E258" s="0" t="s">
         <v>1174</v>
       </c>
-      <c r="G258" s="1" t="s">
+      <c r="F258" s="0" t="s">
         <v>1175</v>
       </c>
-      <c r="H258" s="1" t="s">
+      <c r="G258" s="0" t="s">
         <v>1176</v>
+      </c>
+      <c r="H258" s="0" t="s">
+        <v>1177</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" s="0" t="s">
-        <v>1177</v>
-      </c>
-      <c r="D259" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="F259" s="1" t="s">
+      <c r="E259" s="0" t="s">
         <v>1179</v>
       </c>
-      <c r="G259" s="1" t="s">
+      <c r="F259" s="0" t="s">
         <v>1180</v>
       </c>
-      <c r="H259" s="1" t="s">
+      <c r="G259" s="0" t="s">
         <v>1181</v>
+      </c>
+      <c r="H259" s="0" t="s">
+        <v>1182</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" s="0" t="s">
-        <v>1182</v>
-      </c>
-      <c r="D260" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="F260" s="1" t="s">
+      <c r="E260" s="0" t="s">
         <v>1184</v>
       </c>
-      <c r="G260" s="1" t="s">
+      <c r="F260" s="0" t="s">
         <v>1185</v>
       </c>
-      <c r="H260" s="1" t="s">
+      <c r="G260" s="0" t="s">
         <v>1186</v>
+      </c>
+      <c r="H260" s="0" t="s">
+        <v>1187</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" s="0" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D261" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="F261" s="1" t="s">
+      <c r="E261" s="0" t="s">
         <v>1189</v>
       </c>
-      <c r="G261" s="1" t="s">
+      <c r="F261" s="0" t="s">
         <v>1190</v>
       </c>
-      <c r="H261" s="1" t="s">
+      <c r="G261" s="0" t="s">
         <v>1191</v>
+      </c>
+      <c r="H261" s="0" t="s">
+        <v>1192</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" s="0" t="s">
-        <v>1192</v>
-      </c>
-      <c r="D262" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="F262" s="1" t="s">
+      <c r="E262" s="0" t="s">
         <v>1194</v>
       </c>
-      <c r="G262" s="1" t="s">
+      <c r="F262" s="0" t="s">
         <v>1195</v>
       </c>
-      <c r="H262" s="1" t="s">
+      <c r="G262" s="0" t="s">
         <v>1196</v>
+      </c>
+      <c r="H262" s="0" t="s">
+        <v>1197</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="0" t="s">
-        <v>1197</v>
-      </c>
-      <c r="D263" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="F263" s="1" t="s">
+      <c r="E263" s="0" t="s">
         <v>1199</v>
       </c>
-      <c r="G263" s="1" t="s">
+      <c r="F263" s="0" t="s">
         <v>1200</v>
       </c>
-      <c r="H263" s="1" t="s">
+      <c r="G263" s="0" t="s">
         <v>1201</v>
+      </c>
+      <c r="H263" s="0" t="s">
+        <v>1202</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="0" t="s">
-        <v>1202</v>
-      </c>
-      <c r="D264" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="F264" s="1" t="s">
+      <c r="E264" s="0" t="s">
         <v>1204</v>
       </c>
-      <c r="G264" s="1" t="s">
+      <c r="F264" s="0" t="s">
         <v>1205</v>
       </c>
-      <c r="H264" s="1" t="s">
+      <c r="G264" s="0" t="s">
         <v>1206</v>
+      </c>
+      <c r="H264" s="0" t="s">
+        <v>1207</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" s="0" t="s">
-        <v>1207</v>
-      </c>
-      <c r="D265" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="F265" s="1" t="s">
+      <c r="E265" s="0" t="s">
         <v>1209</v>
       </c>
-      <c r="G265" s="1" t="s">
+      <c r="F265" s="0" t="s">
         <v>1210</v>
       </c>
-      <c r="H265" s="1" t="s">
+      <c r="G265" s="0" t="s">
         <v>1211</v>
+      </c>
+      <c r="H265" s="0" t="s">
+        <v>1212</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" s="0" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D266" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="F266" s="1" t="s">
+      <c r="E266" s="0" t="s">
         <v>1214</v>
       </c>
-      <c r="G266" s="1" t="s">
+      <c r="F266" s="0" t="s">
         <v>1215</v>
       </c>
-      <c r="H266" s="1" t="s">
+      <c r="G266" s="0" t="s">
         <v>1216</v>
+      </c>
+      <c r="H266" s="0" t="s">
+        <v>1217</v>
       </c>
     </row>
     <row r="267">
       <c r="B267" s="0" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D267" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="F267" s="1" t="s">
+      <c r="E267" s="0" t="s">
         <v>1219</v>
       </c>
-      <c r="G267" s="1" t="s">
+      <c r="F267" s="0" t="s">
         <v>1220</v>
       </c>
-      <c r="H267" s="1" t="s">
-        <v>1218</v>
+      <c r="G267" s="0" t="s">
+        <v>1221</v>
+      </c>
+      <c r="H267" s="0" t="s">
+        <v>1222</v>
       </c>
     </row>
     <row r="268">
       <c r="B268" s="0" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D268" s="1" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F268" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="G268" s="1" t="s">
+      <c r="E268" s="0" t="s">
         <v>1224</v>
       </c>
-      <c r="H268" s="1" t="s">
-        <v>1222</v>
+      <c r="F268" s="0" t="s">
+        <v>1225</v>
+      </c>
+      <c r="G268" s="0" t="s">
+        <v>1226</v>
+      </c>
+      <c r="H268" s="0" t="s">
+        <v>1224</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" s="0" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D269" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="F269" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="G269" s="1" t="s">
+      <c r="E269" s="0" t="s">
         <v>1228</v>
       </c>
-      <c r="H269" s="1" t="s">
+      <c r="F269" s="0" t="s">
         <v>1229</v>
+      </c>
+      <c r="G269" s="0" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H269" s="0" t="s">
+        <v>1228</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" s="0" t="s">
-        <v>1230</v>
-      </c>
-      <c r="D270" s="1" t="s">
         <v>1231</v>
       </c>
-      <c r="F270" s="1" t="s">
+      <c r="E270" s="0" t="s">
         <v>1232</v>
       </c>
-      <c r="G270" s="1" t="s">
+      <c r="F270" s="0" t="s">
         <v>1233</v>
       </c>
-      <c r="H270" s="1" t="s">
+      <c r="G270" s="0" t="s">
         <v>1234</v>
+      </c>
+      <c r="H270" s="0" t="s">
+        <v>1235</v>
       </c>
     </row>
     <row r="271">
       <c r="B271" s="0" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D271" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="F271" s="1" t="s">
+      <c r="E271" s="0" t="s">
         <v>1237</v>
       </c>
-      <c r="G271" s="1" t="s">
+      <c r="F271" s="0" t="s">
         <v>1238</v>
       </c>
-      <c r="H271" s="1" t="s">
+      <c r="G271" s="0" t="s">
         <v>1239</v>
+      </c>
+      <c r="H271" s="0" t="s">
+        <v>1240</v>
       </c>
     </row>
     <row r="272">
       <c r="B272" s="0" t="s">
-        <v>1240</v>
-      </c>
-      <c r="D272" s="1" t="s">
         <v>1241</v>
       </c>
-      <c r="F272" s="1" t="s">
+      <c r="E272" s="0" t="s">
         <v>1242</v>
       </c>
-      <c r="G272" s="1" t="s">
+      <c r="F272" s="0" t="s">
         <v>1243</v>
       </c>
-      <c r="H272" s="1" t="s">
-        <v>1241</v>
+      <c r="G272" s="0" t="s">
+        <v>1244</v>
+      </c>
+      <c r="H272" s="0" t="s">
+        <v>1245</v>
       </c>
     </row>
     <row r="273">
       <c r="B273" s="0" t="s">
-        <v>1244</v>
-      </c>
-      <c r="D273" s="1" t="s">
-        <v>1245</v>
-      </c>
-      <c r="F273" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="G273" s="1" t="s">
+      <c r="E273" s="0" t="s">
         <v>1247</v>
       </c>
-      <c r="H273" s="1" t="s">
-        <v>1245</v>
+      <c r="F273" s="0" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G273" s="0" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H273" s="0" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="274">
       <c r="B274" s="0" t="s">
-        <v>1248</v>
-      </c>
-      <c r="D274" s="1" t="s">
-        <v>1249</v>
-      </c>
-      <c r="F274" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="G274" s="1" t="s">
+      <c r="E274" s="0" t="s">
         <v>1251</v>
       </c>
-      <c r="H274" s="1" t="s">
+      <c r="F274" s="0" t="s">
         <v>1252</v>
+      </c>
+      <c r="G274" s="0" t="s">
+        <v>1253</v>
+      </c>
+      <c r="H274" s="0" t="s">
+        <v>1251</v>
       </c>
     </row>
     <row r="275">
       <c r="B275" s="0" t="s">
-        <v>1253</v>
-      </c>
-      <c r="D275" s="1" t="s">
-        <v>1241</v>
-      </c>
-      <c r="F275" s="1" t="s">
-        <v>1242</v>
-      </c>
-      <c r="G275" s="1" t="s">
-        <v>1243</v>
-      </c>
-      <c r="H275" s="1" t="s">
-        <v>1241</v>
+        <v>1254</v>
+      </c>
+      <c r="E275" s="0" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F275" s="0" t="s">
+        <v>1256</v>
+      </c>
+      <c r="G275" s="0" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H275" s="0" t="s">
+        <v>1258</v>
       </c>
     </row>
     <row r="276">
       <c r="B276" s="0" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D276" s="1" t="s">
-        <v>1241</v>
-      </c>
-      <c r="F276" s="1" t="s">
-        <v>1242</v>
-      </c>
-      <c r="G276" s="1" t="s">
-        <v>1243</v>
-      </c>
-      <c r="H276" s="1" t="s">
-        <v>1241</v>
+        <v>1259</v>
+      </c>
+      <c r="E276" s="0" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F276" s="0" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G276" s="0" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H276" s="0" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="277">
       <c r="B277" s="0" t="s">
-        <v>1255</v>
-      </c>
-      <c r="D277" s="1" t="s">
-        <v>1241</v>
-      </c>
-      <c r="F277" s="1" t="s">
-        <v>1242</v>
-      </c>
-      <c r="G277" s="1" t="s">
-        <v>1243</v>
-      </c>
-      <c r="H277" s="1" t="s">
-        <v>1241</v>
+        <v>1260</v>
+      </c>
+      <c r="E277" s="0" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F277" s="0" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G277" s="0" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H277" s="0" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="278">
       <c r="B278" s="0" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>1257</v>
-      </c>
-      <c r="F278" s="1" t="s">
-        <v>1258</v>
-      </c>
-      <c r="G278" s="1" t="s">
-        <v>1259</v>
-      </c>
-      <c r="H278" s="1" t="s">
-        <v>1257</v>
+        <v>1261</v>
+      </c>
+      <c r="E278" s="0" t="s">
+        <v>1247</v>
+      </c>
+      <c r="F278" s="0" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G278" s="0" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H278" s="0" t="s">
+        <v>1247</v>
       </c>
     </row>
     <row r="279">
       <c r="B279" s="0" t="s">
-        <v>1260</v>
-      </c>
-      <c r="D279" s="1" t="s">
-        <v>1261</v>
-      </c>
-      <c r="F279" s="1" t="s">
         <v>1262</v>
       </c>
-      <c r="G279" s="1" t="s">
+      <c r="E279" s="0" t="s">
         <v>1263</v>
       </c>
-      <c r="H279" s="1" t="s">
+      <c r="F279" s="0" t="s">
         <v>1264</v>
+      </c>
+      <c r="G279" s="0" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H279" s="0" t="s">
+        <v>1263</v>
       </c>
     </row>
     <row r="280">
       <c r="B280" s="0" t="s">
-        <v>1265</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>1257</v>
-      </c>
-      <c r="F280" s="1" t="s">
-        <v>1258</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>1259</v>
-      </c>
-      <c r="H280" s="1" t="s">
-        <v>1257</v>
+        <v>1266</v>
+      </c>
+      <c r="E280" s="0" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F280" s="0" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G280" s="0" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H280" s="0" t="s">
+        <v>1270</v>
       </c>
     </row>
     <row r="281">
       <c r="B281" s="0" t="s">
-        <v>1266</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="F281" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="G281" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="H281" s="1" t="s">
-        <v>1270</v>
+        <v>1271</v>
+      </c>
+      <c r="E281" s="0" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F281" s="0" t="s">
+        <v>1264</v>
+      </c>
+      <c r="G281" s="0" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H281" s="0" t="s">
+        <v>1263</v>
       </c>
     </row>
     <row r="282">
       <c r="B282" s="0" t="s">
-        <v>1271</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="F282" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="H282" s="1" t="s">
-        <v>1270</v>
+        <v>1272</v>
+      </c>
+      <c r="E282" s="0" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F282" s="0" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G282" s="0" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H282" s="0" t="s">
+        <v>1276</v>
       </c>
     </row>
     <row r="283">
       <c r="B283" s="0" t="s">
-        <v>1272</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="F283" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="G283" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="H283" s="1" t="s">
-        <v>1270</v>
+        <v>1277</v>
+      </c>
+      <c r="E283" s="0" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F283" s="0" t="s">
+        <v>1274</v>
+      </c>
+      <c r="G283" s="0" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H283" s="0" t="s">
+        <v>1276</v>
       </c>
     </row>
     <row r="284">
       <c r="B284" s="0" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E284" s="0" t="s">
         <v>1273</v>
       </c>
-      <c r="D284" s="1" t="s">
+      <c r="F284" s="0" t="s">
         <v>1274</v>
       </c>
-      <c r="F284" s="1" t="s">
+      <c r="G284" s="0" t="s">
         <v>1275</v>
       </c>
-      <c r="G284" s="1" t="s">
+      <c r="H284" s="0" t="s">
         <v>1276</v>
-      </c>
-      <c r="H284" s="1" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="285">
       <c r="B285" s="0" t="s">
-        <v>1278</v>
-      </c>
-      <c r="D285" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="F285" s="1" t="s">
+      <c r="E285" s="0" t="s">
         <v>1280</v>
       </c>
-      <c r="G285" s="1" t="s">
+      <c r="F285" s="0" t="s">
         <v>1281</v>
       </c>
-      <c r="H285" s="1" t="s">
-        <v>1279</v>
+      <c r="G285" s="0" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H285" s="0" t="s">
+        <v>1283</v>
       </c>
     </row>
     <row r="286">
       <c r="B286" s="0" t="s">
-        <v>1282</v>
-      </c>
-      <c r="D286" s="1" t="s">
-        <v>1283</v>
-      </c>
-      <c r="F286" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="G286" s="1" t="s">
+      <c r="E286" s="0" t="s">
         <v>1285</v>
       </c>
-      <c r="H286" s="1" t="s">
+      <c r="F286" s="0" t="s">
         <v>1286</v>
+      </c>
+      <c r="G286" s="0" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H286" s="0" t="s">
+        <v>1285</v>
       </c>
     </row>
     <row r="287">
       <c r="B287" s="0" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D287" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="F287" s="1" t="s">
+      <c r="E287" s="0" t="s">
         <v>1289</v>
       </c>
-      <c r="G287" s="1" t="s">
+      <c r="F287" s="0" t="s">
         <v>1290</v>
       </c>
-      <c r="H287" s="1" t="s">
+      <c r="G287" s="0" t="s">
         <v>1291</v>
+      </c>
+      <c r="H287" s="0" t="s">
+        <v>1292</v>
       </c>
     </row>
     <row r="288">
       <c r="B288" s="0" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D288" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="F288" s="1" t="s">
+      <c r="E288" s="0" t="s">
         <v>1294</v>
       </c>
-      <c r="G288" s="1" t="s">
+      <c r="F288" s="0" t="s">
         <v>1295</v>
       </c>
-      <c r="H288" s="1" t="s">
+      <c r="G288" s="0" t="s">
         <v>1296</v>
+      </c>
+      <c r="H288" s="0" t="s">
+        <v>1297</v>
       </c>
     </row>
     <row r="289">
       <c r="B289" s="0" t="s">
-        <v>1297</v>
-      </c>
-      <c r="D289" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="F289" s="1" t="s">
+      <c r="E289" s="0" t="s">
         <v>1299</v>
       </c>
-      <c r="G289" s="1" t="s">
+      <c r="F289" s="0" t="s">
         <v>1300</v>
       </c>
-      <c r="H289" s="1" t="s">
+      <c r="G289" s="0" t="s">
         <v>1301</v>
+      </c>
+      <c r="H289" s="0" t="s">
+        <v>1302</v>
       </c>
     </row>
     <row r="290">
       <c r="B290" s="0" t="s">
-        <v>1302</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>1261</v>
-      </c>
-      <c r="F290" s="1" t="s">
-        <v>1262</v>
-      </c>
-      <c r="G290" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="H290" s="1" t="s">
-        <v>1264</v>
+        <v>1303</v>
+      </c>
+      <c r="E290" s="0" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F290" s="0" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G290" s="0" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H290" s="0" t="s">
+        <v>1307</v>
       </c>
     </row>
     <row r="291">
       <c r="B291" s="0" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D291" s="1" t="s">
-        <v>1261</v>
-      </c>
-      <c r="F291" s="1" t="s">
-        <v>1262</v>
-      </c>
-      <c r="G291" s="1" t="s">
-        <v>1263</v>
-      </c>
-      <c r="H291" s="1" t="s">
-        <v>1264</v>
+        <v>1308</v>
+      </c>
+      <c r="E291" s="0" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F291" s="0" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G291" s="0" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H291" s="0" t="s">
+        <v>1270</v>
       </c>
     </row>
     <row r="292">
       <c r="B292" s="0" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D292" s="1" t="s">
-        <v>1305</v>
-      </c>
-      <c r="F292" s="1" t="s">
-        <v>1306</v>
-      </c>
-      <c r="G292" s="1" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H292" s="1" t="s">
-        <v>1308</v>
+        <v>1309</v>
+      </c>
+      <c r="E292" s="0" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F292" s="0" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G292" s="0" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H292" s="0" t="s">
+        <v>1270</v>
       </c>
     </row>
     <row r="293">
       <c r="B293" s="0" t="s">
-        <v>1309</v>
-      </c>
-      <c r="D293" s="1" t="s">
         <v>1310</v>
       </c>
-      <c r="F293" s="1" t="s">
+      <c r="E293" s="0" t="s">
         <v>1311</v>
       </c>
-      <c r="G293" s="1" t="s">
+      <c r="F293" s="0" t="s">
         <v>1312</v>
       </c>
-      <c r="H293" s="1" t="s">
+      <c r="G293" s="0" t="s">
         <v>1313</v>
+      </c>
+      <c r="H293" s="0" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" s="0" t="s">
-        <v>1314</v>
-      </c>
-      <c r="D294" s="1" t="s">
         <v>1315</v>
       </c>
-      <c r="F294" s="1" t="s">
+      <c r="E294" s="0" t="s">
         <v>1316</v>
       </c>
-      <c r="G294" s="1" t="s">
+      <c r="F294" s="0" t="s">
         <v>1317</v>
       </c>
-      <c r="H294" s="1" t="s">
-        <v>1315</v>
+      <c r="G294" s="0" t="s">
+        <v>1318</v>
+      </c>
+      <c r="H294" s="0" t="s">
+        <v>1319</v>
       </c>
     </row>
     <row r="295">
       <c r="B295" s="0" t="s">
-        <v>1318</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>1319</v>
-      </c>
-      <c r="F295" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="G295" s="1" t="s">
+      <c r="E295" s="0" t="s">
         <v>1321</v>
       </c>
-      <c r="H295" s="1" t="s">
+      <c r="F295" s="0" t="s">
         <v>1322</v>
+      </c>
+      <c r="G295" s="0" t="s">
+        <v>1323</v>
+      </c>
+      <c r="H295" s="0" t="s">
+        <v>1321</v>
       </c>
     </row>
     <row r="296">
       <c r="B296" s="0" t="s">
-        <v>1323</v>
-      </c>
-      <c r="D296" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="F296" s="1" t="s">
+      <c r="E296" s="0" t="s">
         <v>1325</v>
       </c>
-      <c r="G296" s="1" t="s">
+      <c r="F296" s="0" t="s">
         <v>1326</v>
       </c>
-      <c r="H296" s="1" t="s">
+      <c r="G296" s="0" t="s">
         <v>1327</v>
+      </c>
+      <c r="H296" s="0" t="s">
+        <v>1328</v>
       </c>
     </row>
     <row r="297">
       <c r="B297" s="0" t="s">
-        <v>1328</v>
-      </c>
-      <c r="D297" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="F297" s="1" t="s">
+      <c r="E297" s="0" t="s">
         <v>1330</v>
       </c>
-      <c r="G297" s="1" t="s">
+      <c r="F297" s="0" t="s">
         <v>1331</v>
       </c>
-      <c r="H297" s="1" t="s">
+      <c r="G297" s="0" t="s">
         <v>1332</v>
+      </c>
+      <c r="H297" s="0" t="s">
+        <v>1333</v>
       </c>
     </row>
     <row r="298">
       <c r="B298" s="0" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D298" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="F298" s="1" t="s">
+      <c r="E298" s="0" t="s">
         <v>1335</v>
       </c>
-      <c r="G298" s="1" t="s">
+      <c r="F298" s="0" t="s">
         <v>1336</v>
       </c>
-      <c r="H298" s="1" t="s">
+      <c r="G298" s="0" t="s">
         <v>1337</v>
+      </c>
+      <c r="H298" s="0" t="s">
+        <v>1338</v>
       </c>
     </row>
     <row r="299">
       <c r="B299" s="0" t="s">
-        <v>1338</v>
-      </c>
-      <c r="D299" s="1" t="s">
         <v>1339</v>
       </c>
-      <c r="F299" s="1" t="s">
+      <c r="D299" s="0" t="s">
+        <v>991</v>
+      </c>
+      <c r="E299" s="0" t="s">
         <v>1340</v>
       </c>
-      <c r="G299" s="1" t="s">
+      <c r="F299" s="0" t="s">
         <v>1341</v>
       </c>
-      <c r="H299" s="1" t="s">
+      <c r="G299" s="0" t="s">
         <v>1342</v>
+      </c>
+      <c r="H299" s="0" t="s">
+        <v>1340</v>
       </c>
     </row>
     <row r="300">
       <c r="B300" s="0" t="s">
         <v>1343</v>
       </c>
-      <c r="D300" s="1" t="s">
+      <c r="E300" s="0" t="s">
         <v>1344</v>
       </c>
-      <c r="F300" s="1" t="s">
+      <c r="F300" s="0" t="s">
         <v>1345</v>
       </c>
-      <c r="G300" s="1" t="s">
+      <c r="G300" s="0" t="s">
         <v>1346</v>
       </c>
-      <c r="H300" s="1" t="s">
+      <c r="H300" s="0" t="s">
         <v>1347</v>
       </c>
     </row>
@@ -9521,16 +9559,16 @@
       <c r="B301" s="0" t="s">
         <v>1348</v>
       </c>
-      <c r="D301" s="1" t="s">
+      <c r="E301" s="0" t="s">
         <v>1349</v>
       </c>
-      <c r="F301" s="1" t="s">
+      <c r="F301" s="0" t="s">
         <v>1350</v>
       </c>
-      <c r="G301" s="1" t="s">
+      <c r="G301" s="0" t="s">
         <v>1351</v>
       </c>
-      <c r="H301" s="1" t="s">
+      <c r="H301" s="0" t="s">
         <v>1352</v>
       </c>
     </row>
@@ -9538,16 +9576,16 @@
       <c r="B302" s="0" t="s">
         <v>1353</v>
       </c>
-      <c r="D302" s="1" t="s">
+      <c r="E302" s="0" t="s">
         <v>1354</v>
       </c>
-      <c r="F302" s="1" t="s">
+      <c r="F302" s="0" t="s">
         <v>1355</v>
       </c>
-      <c r="G302" s="1" t="s">
+      <c r="G302" s="0" t="s">
         <v>1356</v>
       </c>
-      <c r="H302" s="1" t="s">
+      <c r="H302" s="0" t="s">
         <v>1357</v>
       </c>
     </row>
@@ -9555,16 +9593,16 @@
       <c r="B303" s="0" t="s">
         <v>1358</v>
       </c>
-      <c r="D303" s="1" t="s">
+      <c r="E303" s="0" t="s">
         <v>1359</v>
       </c>
-      <c r="F303" s="1" t="s">
+      <c r="F303" s="0" t="s">
         <v>1360</v>
       </c>
-      <c r="G303" s="1" t="s">
+      <c r="G303" s="0" t="s">
         <v>1361</v>
       </c>
-      <c r="H303" s="1" t="s">
+      <c r="H303" s="0" t="s">
         <v>1362</v>
       </c>
     </row>
@@ -9572,16 +9610,16 @@
       <c r="B304" s="0" t="s">
         <v>1363</v>
       </c>
-      <c r="D304" s="1" t="s">
+      <c r="E304" s="0" t="s">
         <v>1364</v>
       </c>
-      <c r="F304" s="1" t="s">
+      <c r="F304" s="0" t="s">
         <v>1365</v>
       </c>
-      <c r="G304" s="1" t="s">
+      <c r="G304" s="0" t="s">
         <v>1366</v>
       </c>
-      <c r="H304" s="1" t="s">
+      <c r="H304" s="0" t="s">
         <v>1367</v>
       </c>
     </row>
@@ -9589,16 +9627,16 @@
       <c r="B305" s="0" t="s">
         <v>1368</v>
       </c>
-      <c r="D305" s="1" t="s">
+      <c r="E305" s="0" t="s">
         <v>1369</v>
       </c>
-      <c r="F305" s="1" t="s">
+      <c r="F305" s="0" t="s">
         <v>1370</v>
       </c>
-      <c r="G305" s="1" t="s">
+      <c r="G305" s="0" t="s">
         <v>1371</v>
       </c>
-      <c r="H305" s="1" t="s">
+      <c r="H305" s="0" t="s">
         <v>1372</v>
       </c>
     </row>
@@ -9606,16 +9644,16 @@
       <c r="B306" s="0" t="s">
         <v>1373</v>
       </c>
-      <c r="D306" s="1" t="s">
+      <c r="E306" s="0" t="s">
         <v>1374</v>
       </c>
-      <c r="F306" s="1" t="s">
+      <c r="F306" s="0" t="s">
         <v>1375</v>
       </c>
-      <c r="G306" s="1" t="s">
+      <c r="G306" s="0" t="s">
         <v>1376</v>
       </c>
-      <c r="H306" s="1" t="s">
+      <c r="H306" s="0" t="s">
         <v>1377</v>
       </c>
     </row>
@@ -9623,16 +9661,16 @@
       <c r="B307" s="0" t="s">
         <v>1378</v>
       </c>
-      <c r="D307" s="1" t="s">
+      <c r="E307" s="0" t="s">
         <v>1379</v>
       </c>
-      <c r="F307" s="1" t="s">
+      <c r="F307" s="0" t="s">
         <v>1380</v>
       </c>
-      <c r="G307" s="1" t="s">
+      <c r="G307" s="0" t="s">
         <v>1381</v>
       </c>
-      <c r="H307" s="1" t="s">
+      <c r="H307" s="0" t="s">
         <v>1382</v>
       </c>
     </row>
@@ -9640,16 +9678,16 @@
       <c r="B308" s="0" t="s">
         <v>1383</v>
       </c>
-      <c r="D308" s="1" t="s">
+      <c r="E308" s="0" t="s">
         <v>1384</v>
       </c>
-      <c r="F308" s="1" t="s">
+      <c r="F308" s="0" t="s">
         <v>1385</v>
       </c>
-      <c r="G308" s="1" t="s">
+      <c r="G308" s="0" t="s">
         <v>1386</v>
       </c>
-      <c r="H308" s="1" t="s">
+      <c r="H308" s="0" t="s">
         <v>1387</v>
       </c>
     </row>
@@ -9657,67 +9695,67 @@
       <c r="B309" s="0" t="s">
         <v>1388</v>
       </c>
-      <c r="D309" s="1" t="s">
+      <c r="E309" s="0" t="s">
         <v>1389</v>
       </c>
-      <c r="F309" s="1" t="s">
-        <v>1330</v>
-      </c>
-      <c r="G309" s="1" t="s">
+      <c r="F309" s="0" t="s">
         <v>1390</v>
       </c>
-      <c r="H309" s="1" t="s">
+      <c r="G309" s="0" t="s">
         <v>1391</v>
+      </c>
+      <c r="H309" s="0" t="s">
+        <v>1392</v>
       </c>
     </row>
     <row r="310">
       <c r="B310" s="0" t="s">
-        <v>1392</v>
-      </c>
-      <c r="D310" s="1" t="s">
         <v>1393</v>
       </c>
-      <c r="F310" s="1" t="s">
+      <c r="E310" s="0" t="s">
         <v>1394</v>
       </c>
-      <c r="G310" s="1" t="s">
+      <c r="F310" s="0" t="s">
         <v>1395</v>
       </c>
-      <c r="H310" s="1" t="s">
+      <c r="G310" s="0" t="s">
         <v>1396</v>
+      </c>
+      <c r="H310" s="0" t="s">
+        <v>1397</v>
       </c>
     </row>
     <row r="311">
       <c r="B311" s="0" t="s">
-        <v>1397</v>
-      </c>
-      <c r="D311" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="F311" s="1" t="s">
+      <c r="E311" s="0" t="s">
         <v>1399</v>
       </c>
-      <c r="G311" s="1" t="s">
+      <c r="F311" s="0" t="s">
         <v>1400</v>
       </c>
-      <c r="H311" s="1" t="s">
+      <c r="G311" s="0" t="s">
         <v>1401</v>
+      </c>
+      <c r="H311" s="0" t="s">
+        <v>1402</v>
       </c>
     </row>
     <row r="312">
       <c r="B312" s="0" t="s">
-        <v>1402</v>
-      </c>
-      <c r="D312" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="F312" s="1" t="s">
+      <c r="E312" s="0" t="s">
         <v>1404</v>
       </c>
-      <c r="G312" s="1" t="s">
+      <c r="F312" s="0" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G312" s="0" t="s">
         <v>1405</v>
       </c>
-      <c r="H312" s="1" t="s">
+      <c r="H312" s="0" t="s">
         <v>1406</v>
       </c>
     </row>
@@ -9725,16 +9763,16 @@
       <c r="B313" s="0" t="s">
         <v>1407</v>
       </c>
-      <c r="D313" s="1" t="s">
+      <c r="E313" s="0" t="s">
         <v>1408</v>
       </c>
-      <c r="F313" s="1" t="s">
+      <c r="F313" s="0" t="s">
         <v>1409</v>
       </c>
-      <c r="G313" s="1" t="s">
+      <c r="G313" s="0" t="s">
         <v>1410</v>
       </c>
-      <c r="H313" s="1" t="s">
+      <c r="H313" s="0" t="s">
         <v>1411</v>
       </c>
     </row>
@@ -9742,16 +9780,16 @@
       <c r="B314" s="0" t="s">
         <v>1412</v>
       </c>
-      <c r="D314" s="1" t="s">
+      <c r="E314" s="0" t="s">
         <v>1413</v>
       </c>
-      <c r="F314" s="1" t="s">
+      <c r="F314" s="0" t="s">
         <v>1414</v>
       </c>
-      <c r="G314" s="1" t="s">
+      <c r="G314" s="0" t="s">
         <v>1415</v>
       </c>
-      <c r="H314" s="1" t="s">
+      <c r="H314" s="0" t="s">
         <v>1416</v>
       </c>
     </row>
@@ -9759,16 +9797,16 @@
       <c r="B315" s="0" t="s">
         <v>1417</v>
       </c>
-      <c r="D315" s="1" t="s">
+      <c r="E315" s="0" t="s">
         <v>1418</v>
       </c>
-      <c r="F315" s="1" t="s">
+      <c r="F315" s="0" t="s">
         <v>1419</v>
       </c>
-      <c r="G315" s="1" t="s">
+      <c r="G315" s="0" t="s">
         <v>1420</v>
       </c>
-      <c r="H315" s="1" t="s">
+      <c r="H315" s="0" t="s">
         <v>1421</v>
       </c>
     </row>
@@ -9776,16 +9814,16 @@
       <c r="B316" s="0" t="s">
         <v>1422</v>
       </c>
-      <c r="D316" s="1" t="s">
+      <c r="E316" s="0" t="s">
         <v>1423</v>
       </c>
-      <c r="F316" s="1" t="s">
+      <c r="F316" s="0" t="s">
         <v>1424</v>
       </c>
-      <c r="G316" s="1" t="s">
+      <c r="G316" s="0" t="s">
         <v>1425</v>
       </c>
-      <c r="H316" s="1" t="s">
+      <c r="H316" s="0" t="s">
         <v>1426</v>
       </c>
     </row>
@@ -9793,16 +9831,16 @@
       <c r="B317" s="0" t="s">
         <v>1427</v>
       </c>
-      <c r="D317" s="1" t="s">
+      <c r="E317" s="0" t="s">
         <v>1428</v>
       </c>
-      <c r="F317" s="1" t="s">
+      <c r="F317" s="0" t="s">
         <v>1429</v>
       </c>
-      <c r="G317" s="1" t="s">
+      <c r="G317" s="0" t="s">
         <v>1430</v>
       </c>
-      <c r="H317" s="1" t="s">
+      <c r="H317" s="0" t="s">
         <v>1431</v>
       </c>
     </row>
@@ -9810,16 +9848,16 @@
       <c r="B318" s="0" t="s">
         <v>1432</v>
       </c>
-      <c r="D318" s="1" t="s">
+      <c r="E318" s="0" t="s">
         <v>1433</v>
       </c>
-      <c r="F318" s="1" t="s">
+      <c r="F318" s="0" t="s">
         <v>1434</v>
       </c>
-      <c r="G318" s="1" t="s">
+      <c r="G318" s="0" t="s">
         <v>1435</v>
       </c>
-      <c r="H318" s="1" t="s">
+      <c r="H318" s="0" t="s">
         <v>1436</v>
       </c>
     </row>
@@ -9827,17 +9865,68 @@
       <c r="B319" s="0" t="s">
         <v>1437</v>
       </c>
-      <c r="D319" s="1" t="s">
+      <c r="E319" s="0" t="s">
         <v>1438</v>
       </c>
-      <c r="F319" s="1" t="s">
+      <c r="F319" s="0" t="s">
         <v>1439</v>
       </c>
-      <c r="G319" s="1" t="s">
+      <c r="G319" s="0" t="s">
         <v>1440</v>
       </c>
-      <c r="H319" s="1" t="s">
+      <c r="H319" s="0" t="s">
         <v>1441</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="B320" s="0" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E320" s="0" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F320" s="0" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G320" s="0" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H320" s="0" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="B321" s="0" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E321" s="0" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F321" s="0" t="s">
+        <v>1449</v>
+      </c>
+      <c r="G321" s="0" t="s">
+        <v>1450</v>
+      </c>
+      <c r="H321" s="0" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="B322" s="0" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E322" s="0" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F322" s="0" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G322" s="0" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H322" s="0" t="s">
+        <v>1456</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Localization/翻译文本/FlowyGraphLocalizationExport.xlsx
+++ b/Assets/Localization/翻译文本/FlowyGraphLocalizationExport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="1457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="1460">
   <si>
     <t>#var</t>
   </si>
@@ -2987,9 +2987,6 @@
     <t>第一天_白猫_节点图_打招呼.3.0</t>
   </si>
   <si>
-    <t>AI</t>
-  </si>
-  <si>
     <t>到底是怎么回事呢？</t>
   </si>
   <si>
@@ -3035,16 +3032,22 @@
     <t>第一天_警察_节点图_与警察交谈.61.0</t>
   </si>
   <si>
-    <t>我有王发的一些线索。</t>
-  </si>
-  <si>
-    <t>I have some clues about Wang Fa.</t>
-  </si>
-  <si>
-    <t>王に関するいくつかの手がかりを持っている。</t>
-  </si>
-  <si>
-    <t>我有王發的一些線索。</t>
+    <t>修改:[我有王发的一些线索。]-&gt;[我有橘猫的一些线索。] 2026/3/1</t>
+  </si>
+  <si>
+    <t>修改:[我有王发的一些线索。]-&gt;[我有橘猫的一些线索。] 2026/3/1AI</t>
+  </si>
+  <si>
+    <t>我有橘猫的一些线索。</t>
+  </si>
+  <si>
+    <t>I have some clues about the orange cat.</t>
+  </si>
+  <si>
+    <t>私はオレンジ猫に関するいくつかの手がかりを持っています。</t>
+  </si>
+  <si>
+    <t>我有橘貓的一些線索。</t>
   </si>
   <si>
     <t>第一天_警察_节点图_与警察交谈.66.0</t>
@@ -3611,16 +3614,22 @@
     <t>第一天_警察_节点图_与警察交谈.35.0</t>
   </si>
   <si>
-    <t>可以调查王发的货车和手机了。</t>
-  </si>
-  <si>
-    <t>The evidence chain is complete; we can apply for a search warrant to collect evidence from the convenience store.</t>
-  </si>
-  <si>
-    <t>証拠の連鎖が整いました。コンビニの証拠収集のために捜索令状を申請できます。</t>
-  </si>
-  <si>
-    <t>可以調查王發的貨車和手機了。</t>
+    <t>修改:[可以调查王发的货车和手机了。]-&gt;[可以调查橘猫的货车和手机了。] 2026/3/1</t>
+  </si>
+  <si>
+    <t>修改:[可以调查王发的货车和手机了。]-&gt;[可以调查橘猫的货车和手机了。] 2026/3/1AI</t>
+  </si>
+  <si>
+    <t>可以调查橘猫的货车和手机了。</t>
+  </si>
+  <si>
+    <t>You can now investigate the orange cat's truck and phone.</t>
+  </si>
+  <si>
+    <t>オレンジ猫のトラックと携帯電話を調査できるようになりました。</t>
+  </si>
+  <si>
+    <t>可以調查橘貓的貨車和手機了。</t>
   </si>
   <si>
     <t>第一天_警察_节点图_与警察交谈.36.0</t>
@@ -7921,110 +7930,113 @@
       <c r="B205" s="0" t="s">
         <v>990</v>
       </c>
-      <c r="D205" s="0" t="s">
+      <c r="E205" s="0" t="s">
         <v>991</v>
       </c>
-      <c r="E205" s="0" t="s">
+      <c r="F205" s="0" t="s">
         <v>992</v>
       </c>
-      <c r="F205" s="0" t="s">
+      <c r="G205" s="0" t="s">
         <v>993</v>
       </c>
-      <c r="G205" s="0" t="s">
+      <c r="H205" s="0" t="s">
         <v>994</v>
-      </c>
-      <c r="H205" s="0" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="206">
       <c r="B206" s="0" t="s">
+        <v>995</v>
+      </c>
+      <c r="E206" s="0" t="s">
         <v>996</v>
       </c>
-      <c r="E206" s="0" t="s">
+      <c r="F206" s="0" t="s">
         <v>997</v>
       </c>
-      <c r="F206" s="0" t="s">
+      <c r="G206" s="0" t="s">
         <v>998</v>
       </c>
-      <c r="G206" s="0" t="s">
+      <c r="H206" s="0" t="s">
         <v>999</v>
-      </c>
-      <c r="H206" s="0" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="207">
       <c r="B207" s="0" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E207" s="0" t="s">
         <v>1001</v>
       </c>
-      <c r="E207" s="0" t="s">
+      <c r="F207" s="0" t="s">
         <v>1002</v>
       </c>
-      <c r="F207" s="0" t="s">
+      <c r="G207" s="0" t="s">
         <v>1003</v>
       </c>
-      <c r="G207" s="0" t="s">
+      <c r="H207" s="0" t="s">
         <v>1004</v>
-      </c>
-      <c r="H207" s="0" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="208">
       <c r="B208" s="0" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C208" s="0" t="s">
         <v>1006</v>
       </c>
+      <c r="D208" s="0" t="s">
+        <v>1007</v>
+      </c>
       <c r="E208" s="0" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F208" s="0" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="G208" s="0" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="H208" s="0" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" s="0" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E209" s="0" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F209" s="0" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G209" s="0" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="H209" s="0" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" s="0" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="E210" s="0" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F210" s="0" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="G210" s="0" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="H210" s="0" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" s="0" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="E211" s="0" t="s">
         <v>871</v>
@@ -8033,7 +8045,7 @@
         <v>872</v>
       </c>
       <c r="G211" s="0" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="H211" s="0" t="s">
         <v>874</v>
@@ -8041,1892 +8053,1895 @@
     </row>
     <row r="212">
       <c r="B212" s="0" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E212" s="0" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F212" s="0" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="G212" s="0" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="H212" s="0" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="213">
       <c r="B213" s="0" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="E213" s="0" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F213" s="0" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G213" s="0" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H213" s="0" t="s">
         <v>1030</v>
-      </c>
-      <c r="G213" s="0" t="s">
-        <v>1031</v>
-      </c>
-      <c r="H213" s="0" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" s="0" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E214" s="0" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F214" s="0" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G214" s="0" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="H214" s="0" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="215">
       <c r="B215" s="0" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="E215" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F215" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="G215" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H215" s="0" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" s="0" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E216" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F216" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G216" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H216" s="0" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" s="0" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="E217" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F217" s="0" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G217" s="0" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H217" s="0" t="s">
         <v>1049</v>
-      </c>
-      <c r="G217" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="H217" s="0" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" s="0" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E218" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F218" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="G218" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H218" s="0" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" s="0" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="E219" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F219" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G219" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H219" s="0" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="220">
       <c r="B220" s="0" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="E220" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F220" s="0" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G220" s="0" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H220" s="0" t="s">
         <v>1049</v>
-      </c>
-      <c r="G220" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="H220" s="0" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="221">
       <c r="B221" s="0" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E221" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F221" s="0" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G221" s="0" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H221" s="0" t="s">
         <v>1056</v>
-      </c>
-      <c r="G221" s="0" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H221" s="0" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" s="0" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="E222" s="0" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F222" s="0" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="G222" s="0" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H222" s="0" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" s="0" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E223" s="0" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F223" s="0" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="G223" s="0" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="H223" s="0" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" s="0" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="E224" s="0" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F224" s="0" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G224" s="0" t="s">
+        <v>1051</v>
+      </c>
+      <c r="H224" s="0" t="s">
         <v>1049</v>
-      </c>
-      <c r="G224" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="H224" s="0" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" s="0" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="E225" s="0" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F225" s="0" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G225" s="0" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H225" s="0" t="s">
         <v>1056</v>
-      </c>
-      <c r="G225" s="0" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H225" s="0" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" s="0" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="E226" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F226" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="G226" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H226" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" s="0" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="E227" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F227" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G227" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H227" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" s="0" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E228" s="0" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F228" s="0" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G228" s="0" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="H228" s="0" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" s="0" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="E229" s="0" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F229" s="0" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G229" s="0" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="H229" s="0" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" s="0" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E230" s="0" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F230" s="0" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="G230" s="0" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="H230" s="0" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" s="0" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="E231" s="0" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F231" s="0" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G231" s="0" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="H231" s="0" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" s="0" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E232" s="0" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F232" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="G232" s="0" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H232" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="233">
       <c r="B233" s="0" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="E233" s="0" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F233" s="0" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="G233" s="0" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="H233" s="0" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="234">
       <c r="B234" s="0" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="E234" s="0" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F234" s="0" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="G234" s="0" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="H234" s="0" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" s="0" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="E235" s="0" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F235" s="0" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="G235" s="0" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="H235" s="0" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="236">
       <c r="B236" s="0" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="E236" s="0" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F236" s="0" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="G236" s="0" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H236" s="0" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="237">
       <c r="B237" s="0" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="E237" s="0" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F237" s="0" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="G237" s="0" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H237" s="0" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" s="0" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E238" s="0" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F238" s="0" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G238" s="0" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H238" s="0" t="s">
         <v>1110</v>
-      </c>
-      <c r="E238" s="0" t="s">
-        <v>1106</v>
-      </c>
-      <c r="F238" s="0" t="s">
-        <v>1107</v>
-      </c>
-      <c r="G238" s="0" t="s">
-        <v>1108</v>
-      </c>
-      <c r="H238" s="0" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="239">
       <c r="B239" s="0" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="E239" s="0" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F239" s="0" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="G239" s="0" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="H239" s="0" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="240">
       <c r="B240" s="0" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E240" s="0" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F240" s="0" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="G240" s="0" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="H240" s="0" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" s="0" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="E241" s="0" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F241" s="0" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G241" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H241" s="0" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="242">
       <c r="B242" s="0" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="E242" s="0" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F242" s="0" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="G242" s="0" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H242" s="0" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="243">
       <c r="B243" s="0" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E243" s="0" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F243" s="0" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G243" s="0" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H243" s="0" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="244">
       <c r="B244" s="0" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E244" s="0" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F244" s="0" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G244" s="0" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H244" s="0" t="s">
         <v>1132</v>
-      </c>
-      <c r="E244" s="0" t="s">
-        <v>1128</v>
-      </c>
-      <c r="F244" s="0" t="s">
-        <v>1129</v>
-      </c>
-      <c r="G244" s="0" t="s">
-        <v>1130</v>
-      </c>
-      <c r="H244" s="0" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="245">
       <c r="B245" s="0" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="E245" s="0" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="F245" s="0" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="G245" s="0" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="H245" s="0" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" s="0" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="E246" s="0" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F246" s="0" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G246" s="0" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H246" s="0" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="247">
       <c r="B247" s="0" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="E247" s="0" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F247" s="0" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G247" s="0" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H247" s="0" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="248">
       <c r="B248" s="0" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E248" s="0" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F248" s="0" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="G248" s="0" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H248" s="0" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="249">
       <c r="B249" s="0" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="E249" s="0" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F249" s="0" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G249" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H249" s="0" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="250">
       <c r="B250" s="0" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E250" s="0" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="F250" s="0" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="G250" s="0" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H250" s="0" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" s="0" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="E251" s="0" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F251" s="0" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G251" s="0" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H251" s="0" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="252">
       <c r="B252" s="0" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E252" s="0" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="F252" s="0" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="G252" s="0" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H252" s="0" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="253">
       <c r="B253" s="0" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="E253" s="0" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F253" s="0" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G253" s="0" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="H253" s="0" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="254">
       <c r="B254" s="0" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E254" s="0" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F254" s="0" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G254" s="0" t="s">
         <v>1157</v>
       </c>
-      <c r="E254" s="0" t="s">
-        <v>1118</v>
-      </c>
-      <c r="F254" s="0" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G254" s="0" t="s">
-        <v>1156</v>
-      </c>
       <c r="H254" s="0" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="255">
       <c r="B255" s="0" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="E255" s="0" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="F255" s="0" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G255" s="0" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H255" s="0" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="256">
       <c r="B256" s="0" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="E256" s="0" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F256" s="0" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="G256" s="0" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="H256" s="0" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="257">
       <c r="B257" s="0" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E257" s="0" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="F257" s="0" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="G257" s="0" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="H257" s="0" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="258">
       <c r="B258" s="0" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E258" s="0" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="F258" s="0" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="G258" s="0" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H258" s="0" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" s="0" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E259" s="0" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="F259" s="0" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="G259" s="0" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="H259" s="0" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" s="0" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E260" s="0" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="F260" s="0" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="G260" s="0" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="H260" s="0" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" s="0" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E261" s="0" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F261" s="0" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="G261" s="0" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H261" s="0" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" s="0" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E262" s="0" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="F262" s="0" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G262" s="0" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H262" s="0" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="0" t="s">
-        <v>1198</v>
+        <v>1199</v>
+      </c>
+      <c r="C263" s="0" t="s">
+        <v>1200</v>
+      </c>
+      <c r="D263" s="0" t="s">
+        <v>1201</v>
       </c>
       <c r="E263" s="0" t="s">
-        <v>1199</v>
+        <v>1202</v>
       </c>
       <c r="F263" s="0" t="s">
-        <v>1200</v>
+        <v>1203</v>
       </c>
       <c r="G263" s="0" t="s">
-        <v>1201</v>
+        <v>1204</v>
       </c>
       <c r="H263" s="0" t="s">
-        <v>1202</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="0" t="s">
-        <v>1203</v>
+        <v>1206</v>
       </c>
       <c r="E264" s="0" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="F264" s="0" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="G264" s="0" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="H264" s="0" t="s">
-        <v>1207</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" s="0" t="s">
-        <v>1208</v>
+        <v>1211</v>
       </c>
       <c r="E265" s="0" t="s">
-        <v>1209</v>
+        <v>1212</v>
       </c>
       <c r="F265" s="0" t="s">
-        <v>1210</v>
+        <v>1213</v>
       </c>
       <c r="G265" s="0" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
       <c r="H265" s="0" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" s="0" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="E266" s="0" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="F266" s="0" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="G266" s="0" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="H266" s="0" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="267">
       <c r="B267" s="0" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="E267" s="0" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="F267" s="0" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="G267" s="0" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="H267" s="0" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="268">
       <c r="B268" s="0" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="E268" s="0" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" s="0" t="s">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="E269" s="0" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>1228</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" s="0" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="E270" s="0" t="s">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="F270" s="0" t="s">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="G270" s="0" t="s">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="H270" s="0" t="s">
-        <v>1235</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="271">
       <c r="B271" s="0" t="s">
-        <v>1236</v>
+        <v>1239</v>
       </c>
       <c r="E271" s="0" t="s">
-        <v>1237</v>
+        <v>1240</v>
       </c>
       <c r="F271" s="0" t="s">
-        <v>1238</v>
+        <v>1241</v>
       </c>
       <c r="G271" s="0" t="s">
-        <v>1239</v>
+        <v>1242</v>
       </c>
       <c r="H271" s="0" t="s">
-        <v>1240</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="272">
       <c r="B272" s="0" t="s">
-        <v>1241</v>
+        <v>1244</v>
       </c>
       <c r="E272" s="0" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
       <c r="F272" s="0" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="G272" s="0" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="H272" s="0" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="273">
       <c r="B273" s="0" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="E273" s="0" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="G273" s="0" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="274">
       <c r="B274" s="0" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>1252</v>
+        <v>1255</v>
       </c>
       <c r="G274" s="0" t="s">
-        <v>1253</v>
+        <v>1256</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>1251</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="275">
       <c r="B275" s="0" t="s">
-        <v>1254</v>
+        <v>1257</v>
       </c>
       <c r="E275" s="0" t="s">
-        <v>1255</v>
+        <v>1258</v>
       </c>
       <c r="F275" s="0" t="s">
-        <v>1256</v>
+        <v>1259</v>
       </c>
       <c r="G275" s="0" t="s">
-        <v>1257</v>
+        <v>1260</v>
       </c>
       <c r="H275" s="0" t="s">
-        <v>1258</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="276">
       <c r="B276" s="0" t="s">
-        <v>1259</v>
+        <v>1262</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="G276" s="0" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="277">
       <c r="B277" s="0" t="s">
-        <v>1260</v>
+        <v>1263</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="G277" s="0" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="278">
       <c r="B278" s="0" t="s">
-        <v>1261</v>
+        <v>1264</v>
       </c>
       <c r="E278" s="0" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="279">
       <c r="B279" s="0" t="s">
-        <v>1262</v>
+        <v>1265</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="280">
       <c r="B280" s="0" t="s">
-        <v>1266</v>
+        <v>1269</v>
       </c>
       <c r="E280" s="0" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="F280" s="0" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="G280" s="0" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="H280" s="0" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="281">
       <c r="B281" s="0" t="s">
-        <v>1271</v>
+        <v>1274</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>1264</v>
+        <v>1267</v>
       </c>
       <c r="G281" s="0" t="s">
-        <v>1265</v>
+        <v>1268</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>1263</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="282">
       <c r="B282" s="0" t="s">
-        <v>1272</v>
+        <v>1275</v>
       </c>
       <c r="E282" s="0" t="s">
-        <v>1273</v>
+        <v>1276</v>
       </c>
       <c r="F282" s="0" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
       <c r="G282" s="0" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="H282" s="0" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="283">
       <c r="B283" s="0" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E283" s="0" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F283" s="0" t="s">
         <v>1277</v>
       </c>
-      <c r="E283" s="0" t="s">
-        <v>1273</v>
-      </c>
-      <c r="F283" s="0" t="s">
-        <v>1274</v>
-      </c>
       <c r="G283" s="0" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="284">
       <c r="B284" s="0" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E284" s="0" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F284" s="0" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G284" s="0" t="s">
         <v>1278</v>
       </c>
-      <c r="E284" s="0" t="s">
-        <v>1273</v>
-      </c>
-      <c r="F284" s="0" t="s">
-        <v>1274</v>
-      </c>
-      <c r="G284" s="0" t="s">
-        <v>1275</v>
-      </c>
       <c r="H284" s="0" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="285">
       <c r="B285" s="0" t="s">
-        <v>1279</v>
+        <v>1282</v>
       </c>
       <c r="E285" s="0" t="s">
-        <v>1280</v>
+        <v>1283</v>
       </c>
       <c r="F285" s="0" t="s">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="G285" s="0" t="s">
-        <v>1282</v>
+        <v>1285</v>
       </c>
       <c r="H285" s="0" t="s">
-        <v>1283</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="286">
       <c r="B286" s="0" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="E286" s="0" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="G286" s="0" t="s">
-        <v>1287</v>
+        <v>1290</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="287">
       <c r="B287" s="0" t="s">
-        <v>1288</v>
+        <v>1291</v>
       </c>
       <c r="E287" s="0" t="s">
-        <v>1289</v>
+        <v>1292</v>
       </c>
       <c r="F287" s="0" t="s">
-        <v>1290</v>
+        <v>1293</v>
       </c>
       <c r="G287" s="0" t="s">
-        <v>1291</v>
+        <v>1294</v>
       </c>
       <c r="H287" s="0" t="s">
-        <v>1292</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="288">
       <c r="B288" s="0" t="s">
-        <v>1293</v>
+        <v>1296</v>
       </c>
       <c r="E288" s="0" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
       <c r="F288" s="0" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="G288" s="0" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="H288" s="0" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="289">
       <c r="B289" s="0" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="E289" s="0" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="F289" s="0" t="s">
-        <v>1300</v>
+        <v>1303</v>
       </c>
       <c r="G289" s="0" t="s">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="H289" s="0" t="s">
-        <v>1302</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="290">
       <c r="B290" s="0" t="s">
-        <v>1303</v>
+        <v>1306</v>
       </c>
       <c r="E290" s="0" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
       <c r="F290" s="0" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="G290" s="0" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="H290" s="0" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="291">
       <c r="B291" s="0" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="G291" s="0" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="292">
       <c r="B292" s="0" t="s">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="E292" s="0" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>1270</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="293">
       <c r="B293" s="0" t="s">
-        <v>1310</v>
+        <v>1313</v>
       </c>
       <c r="E293" s="0" t="s">
-        <v>1311</v>
+        <v>1314</v>
       </c>
       <c r="F293" s="0" t="s">
-        <v>1312</v>
+        <v>1315</v>
       </c>
       <c r="G293" s="0" t="s">
-        <v>1313</v>
+        <v>1316</v>
       </c>
       <c r="H293" s="0" t="s">
-        <v>1314</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" s="0" t="s">
-        <v>1315</v>
+        <v>1318</v>
       </c>
       <c r="E294" s="0" t="s">
-        <v>1316</v>
+        <v>1319</v>
       </c>
       <c r="F294" s="0" t="s">
-        <v>1317</v>
+        <v>1320</v>
       </c>
       <c r="G294" s="0" t="s">
-        <v>1318</v>
+        <v>1321</v>
       </c>
       <c r="H294" s="0" t="s">
-        <v>1319</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="295">
       <c r="B295" s="0" t="s">
-        <v>1320</v>
+        <v>1323</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="G295" s="0" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>1321</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="296">
       <c r="B296" s="0" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="E296" s="0" t="s">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="F296" s="0" t="s">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="G296" s="0" t="s">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="H296" s="0" t="s">
-        <v>1328</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="297">
       <c r="B297" s="0" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="E297" s="0" t="s">
-        <v>1330</v>
+        <v>1333</v>
       </c>
       <c r="F297" s="0" t="s">
-        <v>1331</v>
+        <v>1334</v>
       </c>
       <c r="G297" s="0" t="s">
-        <v>1332</v>
+        <v>1335</v>
       </c>
       <c r="H297" s="0" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="298">
       <c r="B298" s="0" t="s">
-        <v>1334</v>
+        <v>1337</v>
       </c>
       <c r="E298" s="0" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
       <c r="F298" s="0" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="G298" s="0" t="s">
-        <v>1337</v>
+        <v>1340</v>
       </c>
       <c r="H298" s="0" t="s">
-        <v>1338</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="299">
       <c r="B299" s="0" t="s">
-        <v>1339</v>
-      </c>
-      <c r="D299" s="0" t="s">
-        <v>991</v>
+        <v>1342</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>1341</v>
+        <v>1344</v>
       </c>
       <c r="G299" s="0" t="s">
-        <v>1342</v>
+        <v>1345</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>1340</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="300">
       <c r="B300" s="0" t="s">
-        <v>1343</v>
+        <v>1346</v>
       </c>
       <c r="E300" s="0" t="s">
-        <v>1344</v>
+        <v>1347</v>
       </c>
       <c r="F300" s="0" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="G300" s="0" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="H300" s="0" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="301">
       <c r="B301" s="0" t="s">
-        <v>1348</v>
+        <v>1351</v>
       </c>
       <c r="E301" s="0" t="s">
-        <v>1349</v>
+        <v>1352</v>
       </c>
       <c r="F301" s="0" t="s">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="G301" s="0" t="s">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="H301" s="0" t="s">
-        <v>1352</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="302">
       <c r="B302" s="0" t="s">
-        <v>1353</v>
+        <v>1356</v>
       </c>
       <c r="E302" s="0" t="s">
-        <v>1354</v>
+        <v>1357</v>
       </c>
       <c r="F302" s="0" t="s">
-        <v>1355</v>
+        <v>1358</v>
       </c>
       <c r="G302" s="0" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="H302" s="0" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="303">
       <c r="B303" s="0" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="E303" s="0" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="F303" s="0" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="G303" s="0" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="H303" s="0" t="s">
-        <v>1362</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="304">
       <c r="B304" s="0" t="s">
-        <v>1363</v>
+        <v>1366</v>
       </c>
       <c r="E304" s="0" t="s">
-        <v>1364</v>
+        <v>1367</v>
       </c>
       <c r="F304" s="0" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="G304" s="0" t="s">
-        <v>1366</v>
+        <v>1369</v>
       </c>
       <c r="H304" s="0" t="s">
-        <v>1367</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="305">
       <c r="B305" s="0" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
       <c r="E305" s="0" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="F305" s="0" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="G305" s="0" t="s">
-        <v>1371</v>
+        <v>1374</v>
       </c>
       <c r="H305" s="0" t="s">
-        <v>1372</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="306">
       <c r="B306" s="0" t="s">
-        <v>1373</v>
+        <v>1376</v>
       </c>
       <c r="E306" s="0" t="s">
-        <v>1374</v>
+        <v>1377</v>
       </c>
       <c r="F306" s="0" t="s">
-        <v>1375</v>
+        <v>1378</v>
       </c>
       <c r="G306" s="0" t="s">
-        <v>1376</v>
+        <v>1379</v>
       </c>
       <c r="H306" s="0" t="s">
-        <v>1377</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="307">
       <c r="B307" s="0" t="s">
-        <v>1378</v>
+        <v>1381</v>
       </c>
       <c r="E307" s="0" t="s">
-        <v>1379</v>
+        <v>1382</v>
       </c>
       <c r="F307" s="0" t="s">
-        <v>1380</v>
+        <v>1383</v>
       </c>
       <c r="G307" s="0" t="s">
-        <v>1381</v>
+        <v>1384</v>
       </c>
       <c r="H307" s="0" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="308">
       <c r="B308" s="0" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="E308" s="0" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="F308" s="0" t="s">
-        <v>1385</v>
+        <v>1388</v>
       </c>
       <c r="G308" s="0" t="s">
-        <v>1386</v>
+        <v>1389</v>
       </c>
       <c r="H308" s="0" t="s">
-        <v>1387</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="309">
       <c r="B309" s="0" t="s">
-        <v>1388</v>
+        <v>1391</v>
       </c>
       <c r="E309" s="0" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="F309" s="0" t="s">
-        <v>1390</v>
+        <v>1393</v>
       </c>
       <c r="G309" s="0" t="s">
-        <v>1391</v>
+        <v>1394</v>
       </c>
       <c r="H309" s="0" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="310">
       <c r="B310" s="0" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
       <c r="E310" s="0" t="s">
-        <v>1394</v>
+        <v>1397</v>
       </c>
       <c r="F310" s="0" t="s">
-        <v>1395</v>
+        <v>1398</v>
       </c>
       <c r="G310" s="0" t="s">
-        <v>1396</v>
+        <v>1399</v>
       </c>
       <c r="H310" s="0" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="311">
       <c r="B311" s="0" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="E311" s="0" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="F311" s="0" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="G311" s="0" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="H311" s="0" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="312">
       <c r="B312" s="0" t="s">
-        <v>1403</v>
+        <v>1406</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>1345</v>
+        <v>1348</v>
       </c>
       <c r="G312" s="0" t="s">
-        <v>1405</v>
+        <v>1408</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>1406</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="313">
       <c r="B313" s="0" t="s">
-        <v>1407</v>
+        <v>1410</v>
       </c>
       <c r="E313" s="0" t="s">
-        <v>1408</v>
+        <v>1411</v>
       </c>
       <c r="F313" s="0" t="s">
-        <v>1409</v>
+        <v>1412</v>
       </c>
       <c r="G313" s="0" t="s">
-        <v>1410</v>
+        <v>1413</v>
       </c>
       <c r="H313" s="0" t="s">
-        <v>1411</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="314">
       <c r="B314" s="0" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
       <c r="E314" s="0" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="F314" s="0" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="G314" s="0" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="H314" s="0" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="315">
       <c r="B315" s="0" t="s">
-        <v>1417</v>
+        <v>1420</v>
       </c>
       <c r="E315" s="0" t="s">
-        <v>1418</v>
+        <v>1421</v>
       </c>
       <c r="F315" s="0" t="s">
-        <v>1419</v>
+        <v>1422</v>
       </c>
       <c r="G315" s="0" t="s">
-        <v>1420</v>
+        <v>1423</v>
       </c>
       <c r="H315" s="0" t="s">
-        <v>1421</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="316">
       <c r="B316" s="0" t="s">
-        <v>1422</v>
+        <v>1425</v>
       </c>
       <c r="E316" s="0" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
       <c r="F316" s="0" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="G316" s="0" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="H316" s="0" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="317">
       <c r="B317" s="0" t="s">
-        <v>1427</v>
+        <v>1430</v>
       </c>
       <c r="E317" s="0" t="s">
-        <v>1428</v>
+        <v>1431</v>
       </c>
       <c r="F317" s="0" t="s">
-        <v>1429</v>
+        <v>1432</v>
       </c>
       <c r="G317" s="0" t="s">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="H317" s="0" t="s">
-        <v>1431</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="318">
       <c r="B318" s="0" t="s">
-        <v>1432</v>
+        <v>1435</v>
       </c>
       <c r="E318" s="0" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
       <c r="F318" s="0" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="G318" s="0" t="s">
-        <v>1435</v>
+        <v>1438</v>
       </c>
       <c r="H318" s="0" t="s">
-        <v>1436</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="319">
       <c r="B319" s="0" t="s">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="E319" s="0" t="s">
-        <v>1438</v>
+        <v>1441</v>
       </c>
       <c r="F319" s="0" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
       <c r="G319" s="0" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="H319" s="0" t="s">
-        <v>1441</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="320">
       <c r="B320" s="0" t="s">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="E320" s="0" t="s">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="F320" s="0" t="s">
-        <v>1444</v>
+        <v>1447</v>
       </c>
       <c r="G320" s="0" t="s">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="H320" s="0" t="s">
-        <v>1446</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="321">
       <c r="B321" s="0" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
       <c r="E321" s="0" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="F321" s="0" t="s">
-        <v>1449</v>
+        <v>1452</v>
       </c>
       <c r="G321" s="0" t="s">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="H321" s="0" t="s">
-        <v>1451</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="322">
       <c r="B322" s="0" t="s">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="E322" s="0" t="s">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="F322" s="0" t="s">
-        <v>1454</v>
+        <v>1457</v>
       </c>
       <c r="G322" s="0" t="s">
-        <v>1455</v>
+        <v>1458</v>
       </c>
       <c r="H322" s="0" t="s">
-        <v>1456</v>
+        <v>1459</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Localization/翻译文本/FlowyGraphLocalizationExport.xlsx
+++ b/Assets/Localization/翻译文本/FlowyGraphLocalizationExport.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="1460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1456" uniqueCount="1456">
   <si>
     <t>#var</t>
   </si>
@@ -3032,12 +3032,6 @@
     <t>第一天_警察_节点图_与警察交谈.61.0</t>
   </si>
   <si>
-    <t>修改:[我有王发的一些线索。]-&gt;[我有橘猫的一些线索。] 2026/3/1</t>
-  </si>
-  <si>
-    <t>修改:[我有王发的一些线索。]-&gt;[我有橘猫的一些线索。] 2026/3/1AI</t>
-  </si>
-  <si>
     <t>我有橘猫的一些线索。</t>
   </si>
   <si>
@@ -3612,12 +3606,6 @@
   </si>
   <si>
     <t>第一天_警察_节点图_与警察交谈.35.0</t>
-  </si>
-  <si>
-    <t>修改:[可以调查王发的货车和手机了。]-&gt;[可以调查橘猫的货车和手机了。] 2026/3/1</t>
-  </si>
-  <si>
-    <t>修改:[可以调查王发的货车和手机了。]-&gt;[可以调查橘猫的货车和手机了。] 2026/3/1AI</t>
   </si>
   <si>
     <t>可以调查橘猫的货车和手机了。</t>
@@ -7981,62 +7969,56 @@
       <c r="B208" s="0" t="s">
         <v>1005</v>
       </c>
-      <c r="C208" s="0" t="s">
+      <c r="E208" s="0" t="s">
         <v>1006</v>
       </c>
-      <c r="D208" s="0" t="s">
+      <c r="F208" s="0" t="s">
         <v>1007</v>
       </c>
-      <c r="E208" s="0" t="s">
+      <c r="G208" s="0" t="s">
         <v>1008</v>
       </c>
-      <c r="F208" s="0" t="s">
+      <c r="H208" s="0" t="s">
         <v>1009</v>
-      </c>
-      <c r="G208" s="0" t="s">
-        <v>1010</v>
-      </c>
-      <c r="H208" s="0" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="209">
       <c r="B209" s="0" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E209" s="0" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F209" s="0" t="s">
         <v>1012</v>
       </c>
-      <c r="E209" s="0" t="s">
+      <c r="G209" s="0" t="s">
         <v>1013</v>
       </c>
-      <c r="F209" s="0" t="s">
+      <c r="H209" s="0" t="s">
         <v>1014</v>
-      </c>
-      <c r="G209" s="0" t="s">
-        <v>1015</v>
-      </c>
-      <c r="H209" s="0" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="210">
       <c r="B210" s="0" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E210" s="0" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F210" s="0" t="s">
         <v>1017</v>
       </c>
-      <c r="E210" s="0" t="s">
+      <c r="G210" s="0" t="s">
         <v>1018</v>
       </c>
-      <c r="F210" s="0" t="s">
+      <c r="H210" s="0" t="s">
         <v>1019</v>
-      </c>
-      <c r="G210" s="0" t="s">
-        <v>1020</v>
-      </c>
-      <c r="H210" s="0" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="211">
       <c r="B211" s="0" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E211" s="0" t="s">
         <v>871</v>
@@ -8045,7 +8027,7 @@
         <v>872</v>
       </c>
       <c r="G211" s="0" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="H211" s="0" t="s">
         <v>874</v>
@@ -8053,1895 +8035,1889 @@
     </row>
     <row r="212">
       <c r="B212" s="0" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E212" s="0" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F212" s="0" t="s">
         <v>1024</v>
       </c>
-      <c r="E212" s="0" t="s">
+      <c r="G212" s="0" t="s">
         <v>1025</v>
       </c>
-      <c r="F212" s="0" t="s">
+      <c r="H212" s="0" t="s">
         <v>1026</v>
-      </c>
-      <c r="G212" s="0" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H212" s="0" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="213">
       <c r="B213" s="0" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E213" s="0" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F213" s="0" t="s">
         <v>1029</v>
       </c>
-      <c r="E213" s="0" t="s">
+      <c r="G213" s="0" t="s">
         <v>1030</v>
       </c>
-      <c r="F213" s="0" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G213" s="0" t="s">
-        <v>1032</v>
-      </c>
       <c r="H213" s="0" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="214">
       <c r="B214" s="0" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E214" s="0" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F214" s="0" t="s">
         <v>1033</v>
       </c>
-      <c r="E214" s="0" t="s">
+      <c r="G214" s="0" t="s">
         <v>1034</v>
       </c>
-      <c r="F214" s="0" t="s">
+      <c r="H214" s="0" t="s">
         <v>1035</v>
-      </c>
-      <c r="G214" s="0" t="s">
-        <v>1036</v>
-      </c>
-      <c r="H214" s="0" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="215">
       <c r="B215" s="0" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E215" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F215" s="0" t="s">
         <v>1038</v>
       </c>
-      <c r="E215" s="0" t="s">
+      <c r="G215" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="F215" s="0" t="s">
+      <c r="H215" s="0" t="s">
         <v>1040</v>
-      </c>
-      <c r="G215" s="0" t="s">
-        <v>1041</v>
-      </c>
-      <c r="H215" s="0" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="216">
       <c r="B216" s="0" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E216" s="0" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F216" s="0" t="s">
         <v>1043</v>
       </c>
-      <c r="E216" s="0" t="s">
+      <c r="G216" s="0" t="s">
         <v>1044</v>
       </c>
-      <c r="F216" s="0" t="s">
+      <c r="H216" s="0" t="s">
         <v>1045</v>
-      </c>
-      <c r="G216" s="0" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H216" s="0" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="217">
       <c r="B217" s="0" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E217" s="0" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F217" s="0" t="s">
         <v>1048</v>
       </c>
-      <c r="E217" s="0" t="s">
+      <c r="G217" s="0" t="s">
         <v>1049</v>
       </c>
-      <c r="F217" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="G217" s="0" t="s">
-        <v>1051</v>
-      </c>
       <c r="H217" s="0" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="218">
       <c r="B218" s="0" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E218" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F218" s="0" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G218" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="F218" s="0" t="s">
+      <c r="H218" s="0" t="s">
         <v>1040</v>
-      </c>
-      <c r="G218" s="0" t="s">
-        <v>1041</v>
-      </c>
-      <c r="H218" s="0" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="219">
       <c r="B219" s="0" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E219" s="0" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F219" s="0" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G219" s="0" t="s">
         <v>1044</v>
       </c>
-      <c r="F219" s="0" t="s">
+      <c r="H219" s="0" t="s">
         <v>1045</v>
-      </c>
-      <c r="G219" s="0" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H219" s="0" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="220">
       <c r="B220" s="0" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E220" s="0" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F220" s="0" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G220" s="0" t="s">
         <v>1049</v>
       </c>
-      <c r="F220" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="G220" s="0" t="s">
-        <v>1051</v>
-      </c>
       <c r="H220" s="0" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="221">
       <c r="B221" s="0" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E221" s="0" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F221" s="0" t="s">
         <v>1055</v>
       </c>
-      <c r="E221" s="0" t="s">
+      <c r="G221" s="0" t="s">
         <v>1056</v>
       </c>
-      <c r="F221" s="0" t="s">
-        <v>1057</v>
-      </c>
-      <c r="G221" s="0" t="s">
-        <v>1058</v>
-      </c>
       <c r="H221" s="0" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="222">
       <c r="B222" s="0" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E222" s="0" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F222" s="0" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G222" s="0" t="s">
         <v>1039</v>
       </c>
-      <c r="F222" s="0" t="s">
+      <c r="H222" s="0" t="s">
         <v>1040</v>
-      </c>
-      <c r="G222" s="0" t="s">
-        <v>1041</v>
-      </c>
-      <c r="H222" s="0" t="s">
-        <v>1042</v>
       </c>
     </row>
     <row r="223">
       <c r="B223" s="0" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="E223" s="0" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F223" s="0" t="s">
+        <v>1043</v>
+      </c>
+      <c r="G223" s="0" t="s">
         <v>1044</v>
       </c>
-      <c r="F223" s="0" t="s">
+      <c r="H223" s="0" t="s">
         <v>1045</v>
-      </c>
-      <c r="G223" s="0" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H223" s="0" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="224">
       <c r="B224" s="0" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="E224" s="0" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F224" s="0" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G224" s="0" t="s">
         <v>1049</v>
       </c>
-      <c r="F224" s="0" t="s">
-        <v>1050</v>
-      </c>
-      <c r="G224" s="0" t="s">
-        <v>1051</v>
-      </c>
       <c r="H224" s="0" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="225">
       <c r="B225" s="0" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="E225" s="0" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F225" s="0" t="s">
+        <v>1055</v>
+      </c>
+      <c r="G225" s="0" t="s">
         <v>1056</v>
       </c>
-      <c r="F225" s="0" t="s">
-        <v>1057</v>
-      </c>
-      <c r="G225" s="0" t="s">
-        <v>1058</v>
-      </c>
       <c r="H225" s="0" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="226">
       <c r="B226" s="0" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E226" s="0" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F226" s="0" t="s">
         <v>1063</v>
       </c>
-      <c r="E226" s="0" t="s">
+      <c r="G226" s="0" t="s">
         <v>1064</v>
       </c>
-      <c r="F226" s="0" t="s">
+      <c r="H226" s="0" t="s">
         <v>1065</v>
-      </c>
-      <c r="G226" s="0" t="s">
-        <v>1066</v>
-      </c>
-      <c r="H226" s="0" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="227">
       <c r="B227" s="0" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E227" s="0" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F227" s="0" t="s">
         <v>1068</v>
       </c>
-      <c r="E227" s="0" t="s">
+      <c r="G227" s="0" t="s">
         <v>1069</v>
       </c>
-      <c r="F227" s="0" t="s">
+      <c r="H227" s="0" t="s">
         <v>1070</v>
-      </c>
-      <c r="G227" s="0" t="s">
-        <v>1071</v>
-      </c>
-      <c r="H227" s="0" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="228">
       <c r="B228" s="0" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E228" s="0" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F228" s="0" t="s">
         <v>1073</v>
       </c>
-      <c r="E228" s="0" t="s">
+      <c r="G228" s="0" t="s">
         <v>1074</v>
       </c>
-      <c r="F228" s="0" t="s">
+      <c r="H228" s="0" t="s">
         <v>1075</v>
-      </c>
-      <c r="G228" s="0" t="s">
-        <v>1076</v>
-      </c>
-      <c r="H228" s="0" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="229">
       <c r="B229" s="0" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E229" s="0" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F229" s="0" t="s">
         <v>1078</v>
       </c>
-      <c r="E229" s="0" t="s">
+      <c r="G229" s="0" t="s">
         <v>1079</v>
       </c>
-      <c r="F229" s="0" t="s">
+      <c r="H229" s="0" t="s">
         <v>1080</v>
-      </c>
-      <c r="G229" s="0" t="s">
-        <v>1081</v>
-      </c>
-      <c r="H229" s="0" t="s">
-        <v>1082</v>
       </c>
     </row>
     <row r="230">
       <c r="B230" s="0" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E230" s="0" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F230" s="0" t="s">
         <v>1083</v>
       </c>
-      <c r="E230" s="0" t="s">
+      <c r="G230" s="0" t="s">
         <v>1084</v>
       </c>
-      <c r="F230" s="0" t="s">
+      <c r="H230" s="0" t="s">
         <v>1085</v>
-      </c>
-      <c r="G230" s="0" t="s">
-        <v>1086</v>
-      </c>
-      <c r="H230" s="0" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="231">
       <c r="B231" s="0" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E231" s="0" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F231" s="0" t="s">
         <v>1088</v>
       </c>
-      <c r="E231" s="0" t="s">
+      <c r="G231" s="0" t="s">
         <v>1089</v>
       </c>
-      <c r="F231" s="0" t="s">
+      <c r="H231" s="0" t="s">
         <v>1090</v>
-      </c>
-      <c r="G231" s="0" t="s">
-        <v>1091</v>
-      </c>
-      <c r="H231" s="0" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="232">
       <c r="B232" s="0" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E232" s="0" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F232" s="0" t="s">
         <v>1093</v>
       </c>
-      <c r="E232" s="0" t="s">
+      <c r="G232" s="0" t="s">
         <v>1094</v>
       </c>
-      <c r="F232" s="0" t="s">
+      <c r="H232" s="0" t="s">
         <v>1095</v>
-      </c>
-      <c r="G232" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="H232" s="0" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="233">
       <c r="B233" s="0" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="E233" s="0" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F233" s="0" t="s">
+        <v>1063</v>
+      </c>
+      <c r="G233" s="0" t="s">
         <v>1064</v>
       </c>
-      <c r="F233" s="0" t="s">
+      <c r="H233" s="0" t="s">
         <v>1065</v>
-      </c>
-      <c r="G233" s="0" t="s">
-        <v>1066</v>
-      </c>
-      <c r="H233" s="0" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="234">
       <c r="B234" s="0" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="E234" s="0" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F234" s="0" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G234" s="0" t="s">
         <v>1069</v>
       </c>
-      <c r="F234" s="0" t="s">
+      <c r="H234" s="0" t="s">
         <v>1070</v>
-      </c>
-      <c r="G234" s="0" t="s">
-        <v>1071</v>
-      </c>
-      <c r="H234" s="0" t="s">
-        <v>1072</v>
       </c>
     </row>
     <row r="235">
       <c r="B235" s="0" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E235" s="0" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F235" s="0" t="s">
         <v>1100</v>
       </c>
-      <c r="E235" s="0" t="s">
+      <c r="G235" s="0" t="s">
         <v>1101</v>
       </c>
-      <c r="F235" s="0" t="s">
+      <c r="H235" s="0" t="s">
         <v>1102</v>
-      </c>
-      <c r="G235" s="0" t="s">
-        <v>1103</v>
-      </c>
-      <c r="H235" s="0" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="236">
       <c r="B236" s="0" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="E236" s="0" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F236" s="0" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G236" s="0" t="s">
         <v>1094</v>
       </c>
-      <c r="F236" s="0" t="s">
+      <c r="H236" s="0" t="s">
         <v>1095</v>
-      </c>
-      <c r="G236" s="0" t="s">
-        <v>1096</v>
-      </c>
-      <c r="H236" s="0" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="237">
       <c r="B237" s="0" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E237" s="0" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F237" s="0" t="s">
         <v>1106</v>
       </c>
-      <c r="E237" s="0" t="s">
+      <c r="G237" s="0" t="s">
         <v>1107</v>
       </c>
-      <c r="F237" s="0" t="s">
+      <c r="H237" s="0" t="s">
         <v>1108</v>
-      </c>
-      <c r="G237" s="0" t="s">
-        <v>1109</v>
-      </c>
-      <c r="H237" s="0" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="238">
       <c r="B238" s="0" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="E238" s="0" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F238" s="0" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G238" s="0" t="s">
         <v>1107</v>
       </c>
-      <c r="F238" s="0" t="s">
+      <c r="H238" s="0" t="s">
         <v>1108</v>
-      </c>
-      <c r="G238" s="0" t="s">
-        <v>1109</v>
-      </c>
-      <c r="H238" s="0" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="239">
       <c r="B239" s="0" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E239" s="0" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F239" s="0" t="s">
         <v>1112</v>
       </c>
-      <c r="E239" s="0" t="s">
+      <c r="G239" s="0" t="s">
         <v>1113</v>
       </c>
-      <c r="F239" s="0" t="s">
+      <c r="H239" s="0" t="s">
         <v>1114</v>
-      </c>
-      <c r="G239" s="0" t="s">
-        <v>1115</v>
-      </c>
-      <c r="H239" s="0" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="240">
       <c r="B240" s="0" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="E240" s="0" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F240" s="0" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G240" s="0" t="s">
         <v>1107</v>
       </c>
-      <c r="F240" s="0" t="s">
+      <c r="H240" s="0" t="s">
         <v>1108</v>
-      </c>
-      <c r="G240" s="0" t="s">
-        <v>1109</v>
-      </c>
-      <c r="H240" s="0" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="241">
       <c r="B241" s="0" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E241" s="0" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F241" s="0" t="s">
         <v>1118</v>
       </c>
-      <c r="E241" s="0" t="s">
+      <c r="G241" s="0" t="s">
         <v>1119</v>
       </c>
-      <c r="F241" s="0" t="s">
+      <c r="H241" s="0" t="s">
         <v>1120</v>
-      </c>
-      <c r="G241" s="0" t="s">
-        <v>1121</v>
-      </c>
-      <c r="H241" s="0" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="242">
       <c r="B242" s="0" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E242" s="0" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F242" s="0" t="s">
         <v>1123</v>
       </c>
-      <c r="E242" s="0" t="s">
+      <c r="G242" s="0" t="s">
         <v>1124</v>
       </c>
-      <c r="F242" s="0" t="s">
+      <c r="H242" s="0" t="s">
         <v>1125</v>
-      </c>
-      <c r="G242" s="0" t="s">
-        <v>1126</v>
-      </c>
-      <c r="H242" s="0" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="243">
       <c r="B243" s="0" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E243" s="0" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F243" s="0" t="s">
         <v>1128</v>
       </c>
-      <c r="E243" s="0" t="s">
+      <c r="G243" s="0" t="s">
         <v>1129</v>
       </c>
-      <c r="F243" s="0" t="s">
+      <c r="H243" s="0" t="s">
         <v>1130</v>
-      </c>
-      <c r="G243" s="0" t="s">
-        <v>1131</v>
-      </c>
-      <c r="H243" s="0" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="244">
       <c r="B244" s="0" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
       <c r="E244" s="0" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F244" s="0" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G244" s="0" t="s">
         <v>1129</v>
       </c>
-      <c r="F244" s="0" t="s">
+      <c r="H244" s="0" t="s">
         <v>1130</v>
-      </c>
-      <c r="G244" s="0" t="s">
-        <v>1131</v>
-      </c>
-      <c r="H244" s="0" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="245">
       <c r="B245" s="0" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E245" s="0" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F245" s="0" t="s">
         <v>1134</v>
       </c>
-      <c r="E245" s="0" t="s">
+      <c r="G245" s="0" t="s">
         <v>1135</v>
       </c>
-      <c r="F245" s="0" t="s">
+      <c r="H245" s="0" t="s">
         <v>1136</v>
-      </c>
-      <c r="G245" s="0" t="s">
-        <v>1137</v>
-      </c>
-      <c r="H245" s="0" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="246">
       <c r="B246" s="0" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="E246" s="0" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F246" s="0" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G246" s="0" t="s">
         <v>1129</v>
       </c>
-      <c r="F246" s="0" t="s">
+      <c r="H246" s="0" t="s">
         <v>1130</v>
-      </c>
-      <c r="G246" s="0" t="s">
-        <v>1131</v>
-      </c>
-      <c r="H246" s="0" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="247">
       <c r="B247" s="0" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="E247" s="0" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F247" s="0" t="s">
+        <v>1128</v>
+      </c>
+      <c r="G247" s="0" t="s">
         <v>1129</v>
       </c>
-      <c r="F247" s="0" t="s">
+      <c r="H247" s="0" t="s">
         <v>1130</v>
-      </c>
-      <c r="G247" s="0" t="s">
-        <v>1131</v>
-      </c>
-      <c r="H247" s="0" t="s">
-        <v>1132</v>
       </c>
     </row>
     <row r="248">
       <c r="B248" s="0" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E248" s="0" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F248" s="0" t="s">
         <v>1141</v>
       </c>
-      <c r="E248" s="0" t="s">
+      <c r="G248" s="0" t="s">
         <v>1142</v>
       </c>
-      <c r="F248" s="0" t="s">
+      <c r="H248" s="0" t="s">
         <v>1143</v>
-      </c>
-      <c r="G248" s="0" t="s">
-        <v>1144</v>
-      </c>
-      <c r="H248" s="0" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="249">
       <c r="B249" s="0" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="E249" s="0" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F249" s="0" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G249" s="0" t="s">
         <v>1119</v>
       </c>
-      <c r="F249" s="0" t="s">
+      <c r="H249" s="0" t="s">
         <v>1120</v>
-      </c>
-      <c r="G249" s="0" t="s">
-        <v>1121</v>
-      </c>
-      <c r="H249" s="0" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="250">
       <c r="B250" s="0" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E250" s="0" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F250" s="0" t="s">
         <v>1147</v>
       </c>
-      <c r="E250" s="0" t="s">
+      <c r="G250" s="0" t="s">
         <v>1148</v>
       </c>
-      <c r="F250" s="0" t="s">
+      <c r="H250" s="0" t="s">
         <v>1149</v>
-      </c>
-      <c r="G250" s="0" t="s">
-        <v>1150</v>
-      </c>
-      <c r="H250" s="0" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="251">
       <c r="B251" s="0" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="E251" s="0" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F251" s="0" t="s">
+        <v>1118</v>
+      </c>
+      <c r="G251" s="0" t="s">
         <v>1119</v>
       </c>
-      <c r="F251" s="0" t="s">
+      <c r="H251" s="0" t="s">
         <v>1120</v>
-      </c>
-      <c r="G251" s="0" t="s">
-        <v>1121</v>
-      </c>
-      <c r="H251" s="0" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="252">
       <c r="B252" s="0" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="E252" s="0" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F252" s="0" t="s">
+        <v>1152</v>
+      </c>
+      <c r="G252" s="0" t="s">
         <v>1148</v>
       </c>
-      <c r="F252" s="0" t="s">
-        <v>1154</v>
-      </c>
-      <c r="G252" s="0" t="s">
-        <v>1150</v>
-      </c>
       <c r="H252" s="0" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="253">
       <c r="B253" s="0" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E253" s="0" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F253" s="0" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G253" s="0" t="s">
         <v>1155</v>
       </c>
-      <c r="E253" s="0" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F253" s="0" t="s">
-        <v>1156</v>
-      </c>
-      <c r="G253" s="0" t="s">
-        <v>1157</v>
-      </c>
       <c r="H253" s="0" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="254">
       <c r="B254" s="0" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="E254" s="0" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="F254" s="0" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="G254" s="0" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="H254" s="0" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="255">
       <c r="B255" s="0" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E255" s="0" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F255" s="0" t="s">
         <v>1159</v>
       </c>
-      <c r="E255" s="0" t="s">
+      <c r="G255" s="0" t="s">
         <v>1160</v>
       </c>
-      <c r="F255" s="0" t="s">
+      <c r="H255" s="0" t="s">
         <v>1161</v>
-      </c>
-      <c r="G255" s="0" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H255" s="0" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="256">
       <c r="B256" s="0" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E256" s="0" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F256" s="0" t="s">
         <v>1164</v>
       </c>
-      <c r="E256" s="0" t="s">
+      <c r="G256" s="0" t="s">
         <v>1165</v>
       </c>
-      <c r="F256" s="0" t="s">
+      <c r="H256" s="0" t="s">
         <v>1166</v>
-      </c>
-      <c r="G256" s="0" t="s">
-        <v>1167</v>
-      </c>
-      <c r="H256" s="0" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="257">
       <c r="B257" s="0" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E257" s="0" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F257" s="0" t="s">
         <v>1169</v>
       </c>
-      <c r="E257" s="0" t="s">
+      <c r="G257" s="0" t="s">
         <v>1170</v>
       </c>
-      <c r="F257" s="0" t="s">
+      <c r="H257" s="0" t="s">
         <v>1171</v>
-      </c>
-      <c r="G257" s="0" t="s">
-        <v>1172</v>
-      </c>
-      <c r="H257" s="0" t="s">
-        <v>1173</v>
       </c>
     </row>
     <row r="258">
       <c r="B258" s="0" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E258" s="0" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F258" s="0" t="s">
         <v>1174</v>
       </c>
-      <c r="E258" s="0" t="s">
+      <c r="G258" s="0" t="s">
         <v>1175</v>
       </c>
-      <c r="F258" s="0" t="s">
+      <c r="H258" s="0" t="s">
         <v>1176</v>
-      </c>
-      <c r="G258" s="0" t="s">
-        <v>1177</v>
-      </c>
-      <c r="H258" s="0" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="259">
       <c r="B259" s="0" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E259" s="0" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F259" s="0" t="s">
         <v>1179</v>
       </c>
-      <c r="E259" s="0" t="s">
+      <c r="G259" s="0" t="s">
         <v>1180</v>
       </c>
-      <c r="F259" s="0" t="s">
+      <c r="H259" s="0" t="s">
         <v>1181</v>
-      </c>
-      <c r="G259" s="0" t="s">
-        <v>1182</v>
-      </c>
-      <c r="H259" s="0" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="260">
       <c r="B260" s="0" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E260" s="0" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F260" s="0" t="s">
         <v>1184</v>
       </c>
-      <c r="E260" s="0" t="s">
+      <c r="G260" s="0" t="s">
         <v>1185</v>
       </c>
-      <c r="F260" s="0" t="s">
+      <c r="H260" s="0" t="s">
         <v>1186</v>
-      </c>
-      <c r="G260" s="0" t="s">
-        <v>1187</v>
-      </c>
-      <c r="H260" s="0" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="261">
       <c r="B261" s="0" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E261" s="0" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F261" s="0" t="s">
         <v>1189</v>
       </c>
-      <c r="E261" s="0" t="s">
+      <c r="G261" s="0" t="s">
         <v>1190</v>
       </c>
-      <c r="F261" s="0" t="s">
+      <c r="H261" s="0" t="s">
         <v>1191</v>
-      </c>
-      <c r="G261" s="0" t="s">
-        <v>1192</v>
-      </c>
-      <c r="H261" s="0" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="262">
       <c r="B262" s="0" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E262" s="0" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F262" s="0" t="s">
         <v>1194</v>
       </c>
-      <c r="E262" s="0" t="s">
+      <c r="G262" s="0" t="s">
         <v>1195</v>
       </c>
-      <c r="F262" s="0" t="s">
+      <c r="H262" s="0" t="s">
         <v>1196</v>
-      </c>
-      <c r="G262" s="0" t="s">
-        <v>1197</v>
-      </c>
-      <c r="H262" s="0" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="263">
       <c r="B263" s="0" t="s">
+        <v>1197</v>
+      </c>
+      <c r="E263" s="0" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F263" s="0" t="s">
         <v>1199</v>
       </c>
-      <c r="C263" s="0" t="s">
+      <c r="G263" s="0" t="s">
         <v>1200</v>
       </c>
-      <c r="D263" s="0" t="s">
+      <c r="H263" s="0" t="s">
         <v>1201</v>
-      </c>
-      <c r="E263" s="0" t="s">
-        <v>1202</v>
-      </c>
-      <c r="F263" s="0" t="s">
-        <v>1203</v>
-      </c>
-      <c r="G263" s="0" t="s">
-        <v>1204</v>
-      </c>
-      <c r="H263" s="0" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="264">
       <c r="B264" s="0" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E264" s="0" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F264" s="0" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G264" s="0" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H264" s="0" t="s">
         <v>1206</v>
-      </c>
-      <c r="E264" s="0" t="s">
-        <v>1207</v>
-      </c>
-      <c r="F264" s="0" t="s">
-        <v>1208</v>
-      </c>
-      <c r="G264" s="0" t="s">
-        <v>1209</v>
-      </c>
-      <c r="H264" s="0" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="265">
       <c r="B265" s="0" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E265" s="0" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F265" s="0" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G265" s="0" t="s">
+        <v>1210</v>
+      </c>
+      <c r="H265" s="0" t="s">
         <v>1211</v>
-      </c>
-      <c r="E265" s="0" t="s">
-        <v>1212</v>
-      </c>
-      <c r="F265" s="0" t="s">
-        <v>1213</v>
-      </c>
-      <c r="G265" s="0" t="s">
-        <v>1214</v>
-      </c>
-      <c r="H265" s="0" t="s">
-        <v>1215</v>
       </c>
     </row>
     <row r="266">
       <c r="B266" s="0" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E266" s="0" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F266" s="0" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G266" s="0" t="s">
+        <v>1215</v>
+      </c>
+      <c r="H266" s="0" t="s">
         <v>1216</v>
-      </c>
-      <c r="E266" s="0" t="s">
-        <v>1217</v>
-      </c>
-      <c r="F266" s="0" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G266" s="0" t="s">
-        <v>1219</v>
-      </c>
-      <c r="H266" s="0" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="267">
       <c r="B267" s="0" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E267" s="0" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F267" s="0" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G267" s="0" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H267" s="0" t="s">
         <v>1221</v>
-      </c>
-      <c r="E267" s="0" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F267" s="0" t="s">
-        <v>1223</v>
-      </c>
-      <c r="G267" s="0" t="s">
-        <v>1224</v>
-      </c>
-      <c r="H267" s="0" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="268">
       <c r="B268" s="0" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="E268" s="0" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="F268" s="0" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="G268" s="0" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="H268" s="0" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="269">
       <c r="B269" s="0" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="E269" s="0" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="F269" s="0" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="G269" s="0" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="H269" s="0" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="270">
       <c r="B270" s="0" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E270" s="0" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F270" s="0" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G270" s="0" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H270" s="0" t="s">
         <v>1234</v>
-      </c>
-      <c r="E270" s="0" t="s">
-        <v>1235</v>
-      </c>
-      <c r="F270" s="0" t="s">
-        <v>1236</v>
-      </c>
-      <c r="G270" s="0" t="s">
-        <v>1237</v>
-      </c>
-      <c r="H270" s="0" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="271">
       <c r="B271" s="0" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E271" s="0" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F271" s="0" t="s">
+        <v>1237</v>
+      </c>
+      <c r="G271" s="0" t="s">
+        <v>1238</v>
+      </c>
+      <c r="H271" s="0" t="s">
         <v>1239</v>
-      </c>
-      <c r="E271" s="0" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F271" s="0" t="s">
-        <v>1241</v>
-      </c>
-      <c r="G271" s="0" t="s">
-        <v>1242</v>
-      </c>
-      <c r="H271" s="0" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="272">
       <c r="B272" s="0" t="s">
+        <v>1240</v>
+      </c>
+      <c r="E272" s="0" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F272" s="0" t="s">
+        <v>1242</v>
+      </c>
+      <c r="G272" s="0" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H272" s="0" t="s">
         <v>1244</v>
-      </c>
-      <c r="E272" s="0" t="s">
-        <v>1245</v>
-      </c>
-      <c r="F272" s="0" t="s">
-        <v>1246</v>
-      </c>
-      <c r="G272" s="0" t="s">
-        <v>1247</v>
-      </c>
-      <c r="H272" s="0" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="273">
       <c r="B273" s="0" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="E273" s="0" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="F273" s="0" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="G273" s="0" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="H273" s="0" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="274">
       <c r="B274" s="0" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="E274" s="0" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="F274" s="0" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="G274" s="0" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="H274" s="0" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="275">
       <c r="B275" s="0" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E275" s="0" t="s">
+        <v>1254</v>
+      </c>
+      <c r="F275" s="0" t="s">
+        <v>1255</v>
+      </c>
+      <c r="G275" s="0" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H275" s="0" t="s">
         <v>1257</v>
-      </c>
-      <c r="E275" s="0" t="s">
-        <v>1258</v>
-      </c>
-      <c r="F275" s="0" t="s">
-        <v>1259</v>
-      </c>
-      <c r="G275" s="0" t="s">
-        <v>1260</v>
-      </c>
-      <c r="H275" s="0" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="276">
       <c r="B276" s="0" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="E276" s="0" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="F276" s="0" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="G276" s="0" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="H276" s="0" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="277">
       <c r="B277" s="0" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="E277" s="0" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="F277" s="0" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="G277" s="0" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="H277" s="0" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="278">
       <c r="B278" s="0" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="E278" s="0" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="F278" s="0" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="G278" s="0" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="H278" s="0" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="279">
       <c r="B279" s="0" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="E279" s="0" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="F279" s="0" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="G279" s="0" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="H279" s="0" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="280">
       <c r="B280" s="0" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E280" s="0" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F280" s="0" t="s">
+        <v>1267</v>
+      </c>
+      <c r="G280" s="0" t="s">
+        <v>1268</v>
+      </c>
+      <c r="H280" s="0" t="s">
         <v>1269</v>
-      </c>
-      <c r="E280" s="0" t="s">
-        <v>1270</v>
-      </c>
-      <c r="F280" s="0" t="s">
-        <v>1271</v>
-      </c>
-      <c r="G280" s="0" t="s">
-        <v>1272</v>
-      </c>
-      <c r="H280" s="0" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="281">
       <c r="B281" s="0" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="E281" s="0" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="F281" s="0" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="G281" s="0" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="H281" s="0" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="282">
       <c r="B282" s="0" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E282" s="0" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F282" s="0" t="s">
+        <v>1273</v>
+      </c>
+      <c r="G282" s="0" t="s">
+        <v>1274</v>
+      </c>
+      <c r="H282" s="0" t="s">
         <v>1275</v>
-      </c>
-      <c r="E282" s="0" t="s">
-        <v>1276</v>
-      </c>
-      <c r="F282" s="0" t="s">
-        <v>1277</v>
-      </c>
-      <c r="G282" s="0" t="s">
-        <v>1278</v>
-      </c>
-      <c r="H282" s="0" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="283">
       <c r="B283" s="0" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="E283" s="0" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F283" s="0" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="G283" s="0" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="H283" s="0" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="284">
       <c r="B284" s="0" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="E284" s="0" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="F284" s="0" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="G284" s="0" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="H284" s="0" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="285">
       <c r="B285" s="0" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E285" s="0" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F285" s="0" t="s">
+        <v>1280</v>
+      </c>
+      <c r="G285" s="0" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H285" s="0" t="s">
         <v>1282</v>
-      </c>
-      <c r="E285" s="0" t="s">
-        <v>1283</v>
-      </c>
-      <c r="F285" s="0" t="s">
-        <v>1284</v>
-      </c>
-      <c r="G285" s="0" t="s">
-        <v>1285</v>
-      </c>
-      <c r="H285" s="0" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="286">
       <c r="B286" s="0" t="s">
-        <v>1287</v>
+        <v>1283</v>
       </c>
       <c r="E286" s="0" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="F286" s="0" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="G286" s="0" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="H286" s="0" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="287">
       <c r="B287" s="0" t="s">
+        <v>1287</v>
+      </c>
+      <c r="E287" s="0" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F287" s="0" t="s">
+        <v>1289</v>
+      </c>
+      <c r="G287" s="0" t="s">
+        <v>1290</v>
+      </c>
+      <c r="H287" s="0" t="s">
         <v>1291</v>
-      </c>
-      <c r="E287" s="0" t="s">
-        <v>1292</v>
-      </c>
-      <c r="F287" s="0" t="s">
-        <v>1293</v>
-      </c>
-      <c r="G287" s="0" t="s">
-        <v>1294</v>
-      </c>
-      <c r="H287" s="0" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="288">
       <c r="B288" s="0" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E288" s="0" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F288" s="0" t="s">
+        <v>1294</v>
+      </c>
+      <c r="G288" s="0" t="s">
+        <v>1295</v>
+      </c>
+      <c r="H288" s="0" t="s">
         <v>1296</v>
-      </c>
-      <c r="E288" s="0" t="s">
-        <v>1297</v>
-      </c>
-      <c r="F288" s="0" t="s">
-        <v>1298</v>
-      </c>
-      <c r="G288" s="0" t="s">
-        <v>1299</v>
-      </c>
-      <c r="H288" s="0" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="289">
       <c r="B289" s="0" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E289" s="0" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F289" s="0" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G289" s="0" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H289" s="0" t="s">
         <v>1301</v>
-      </c>
-      <c r="E289" s="0" t="s">
-        <v>1302</v>
-      </c>
-      <c r="F289" s="0" t="s">
-        <v>1303</v>
-      </c>
-      <c r="G289" s="0" t="s">
-        <v>1304</v>
-      </c>
-      <c r="H289" s="0" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="290">
       <c r="B290" s="0" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E290" s="0" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F290" s="0" t="s">
+        <v>1304</v>
+      </c>
+      <c r="G290" s="0" t="s">
+        <v>1305</v>
+      </c>
+      <c r="H290" s="0" t="s">
         <v>1306</v>
-      </c>
-      <c r="E290" s="0" t="s">
-        <v>1307</v>
-      </c>
-      <c r="F290" s="0" t="s">
-        <v>1308</v>
-      </c>
-      <c r="G290" s="0" t="s">
-        <v>1309</v>
-      </c>
-      <c r="H290" s="0" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="291">
       <c r="B291" s="0" t="s">
-        <v>1311</v>
+        <v>1307</v>
       </c>
       <c r="E291" s="0" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="F291" s="0" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G291" s="0" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H291" s="0" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="292">
       <c r="B292" s="0" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="E292" s="0" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="F292" s="0" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="G292" s="0" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="H292" s="0" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="293">
       <c r="B293" s="0" t="s">
+        <v>1309</v>
+      </c>
+      <c r="E293" s="0" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F293" s="0" t="s">
+        <v>1311</v>
+      </c>
+      <c r="G293" s="0" t="s">
+        <v>1312</v>
+      </c>
+      <c r="H293" s="0" t="s">
         <v>1313</v>
-      </c>
-      <c r="E293" s="0" t="s">
-        <v>1314</v>
-      </c>
-      <c r="F293" s="0" t="s">
-        <v>1315</v>
-      </c>
-      <c r="G293" s="0" t="s">
-        <v>1316</v>
-      </c>
-      <c r="H293" s="0" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="294">
       <c r="B294" s="0" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E294" s="0" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F294" s="0" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G294" s="0" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H294" s="0" t="s">
         <v>1318</v>
-      </c>
-      <c r="E294" s="0" t="s">
-        <v>1319</v>
-      </c>
-      <c r="F294" s="0" t="s">
-        <v>1320</v>
-      </c>
-      <c r="G294" s="0" t="s">
-        <v>1321</v>
-      </c>
-      <c r="H294" s="0" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="295">
       <c r="B295" s="0" t="s">
-        <v>1323</v>
+        <v>1319</v>
       </c>
       <c r="E295" s="0" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
       <c r="F295" s="0" t="s">
-        <v>1325</v>
+        <v>1321</v>
       </c>
       <c r="G295" s="0" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="H295" s="0" t="s">
-        <v>1324</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="296">
       <c r="B296" s="0" t="s">
+        <v>1323</v>
+      </c>
+      <c r="E296" s="0" t="s">
+        <v>1324</v>
+      </c>
+      <c r="F296" s="0" t="s">
+        <v>1325</v>
+      </c>
+      <c r="G296" s="0" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H296" s="0" t="s">
         <v>1327</v>
-      </c>
-      <c r="E296" s="0" t="s">
-        <v>1328</v>
-      </c>
-      <c r="F296" s="0" t="s">
-        <v>1329</v>
-      </c>
-      <c r="G296" s="0" t="s">
-        <v>1330</v>
-      </c>
-      <c r="H296" s="0" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="297">
       <c r="B297" s="0" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E297" s="0" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F297" s="0" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G297" s="0" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H297" s="0" t="s">
         <v>1332</v>
-      </c>
-      <c r="E297" s="0" t="s">
-        <v>1333</v>
-      </c>
-      <c r="F297" s="0" t="s">
-        <v>1334</v>
-      </c>
-      <c r="G297" s="0" t="s">
-        <v>1335</v>
-      </c>
-      <c r="H297" s="0" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="298">
       <c r="B298" s="0" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E298" s="0" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F298" s="0" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G298" s="0" t="s">
+        <v>1336</v>
+      </c>
+      <c r="H298" s="0" t="s">
         <v>1337</v>
-      </c>
-      <c r="E298" s="0" t="s">
-        <v>1338</v>
-      </c>
-      <c r="F298" s="0" t="s">
-        <v>1339</v>
-      </c>
-      <c r="G298" s="0" t="s">
-        <v>1340</v>
-      </c>
-      <c r="H298" s="0" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="299">
       <c r="B299" s="0" t="s">
-        <v>1342</v>
+        <v>1338</v>
       </c>
       <c r="E299" s="0" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
       <c r="F299" s="0" t="s">
-        <v>1344</v>
+        <v>1340</v>
       </c>
       <c r="G299" s="0" t="s">
-        <v>1345</v>
+        <v>1341</v>
       </c>
       <c r="H299" s="0" t="s">
-        <v>1343</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="300">
       <c r="B300" s="0" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E300" s="0" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F300" s="0" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G300" s="0" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H300" s="0" t="s">
         <v>1346</v>
-      </c>
-      <c r="E300" s="0" t="s">
-        <v>1347</v>
-      </c>
-      <c r="F300" s="0" t="s">
-        <v>1348</v>
-      </c>
-      <c r="G300" s="0" t="s">
-        <v>1349</v>
-      </c>
-      <c r="H300" s="0" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="301">
       <c r="B301" s="0" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E301" s="0" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F301" s="0" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G301" s="0" t="s">
+        <v>1350</v>
+      </c>
+      <c r="H301" s="0" t="s">
         <v>1351</v>
-      </c>
-      <c r="E301" s="0" t="s">
-        <v>1352</v>
-      </c>
-      <c r="F301" s="0" t="s">
-        <v>1353</v>
-      </c>
-      <c r="G301" s="0" t="s">
-        <v>1354</v>
-      </c>
-      <c r="H301" s="0" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="302">
       <c r="B302" s="0" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E302" s="0" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F302" s="0" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G302" s="0" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H302" s="0" t="s">
         <v>1356</v>
-      </c>
-      <c r="E302" s="0" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F302" s="0" t="s">
-        <v>1358</v>
-      </c>
-      <c r="G302" s="0" t="s">
-        <v>1359</v>
-      </c>
-      <c r="H302" s="0" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="303">
       <c r="B303" s="0" t="s">
+        <v>1357</v>
+      </c>
+      <c r="E303" s="0" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F303" s="0" t="s">
+        <v>1359</v>
+      </c>
+      <c r="G303" s="0" t="s">
+        <v>1360</v>
+      </c>
+      <c r="H303" s="0" t="s">
         <v>1361</v>
-      </c>
-      <c r="E303" s="0" t="s">
-        <v>1362</v>
-      </c>
-      <c r="F303" s="0" t="s">
-        <v>1363</v>
-      </c>
-      <c r="G303" s="0" t="s">
-        <v>1364</v>
-      </c>
-      <c r="H303" s="0" t="s">
-        <v>1365</v>
       </c>
     </row>
     <row r="304">
       <c r="B304" s="0" t="s">
+        <v>1362</v>
+      </c>
+      <c r="E304" s="0" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F304" s="0" t="s">
+        <v>1364</v>
+      </c>
+      <c r="G304" s="0" t="s">
+        <v>1365</v>
+      </c>
+      <c r="H304" s="0" t="s">
         <v>1366</v>
-      </c>
-      <c r="E304" s="0" t="s">
-        <v>1367</v>
-      </c>
-      <c r="F304" s="0" t="s">
-        <v>1368</v>
-      </c>
-      <c r="G304" s="0" t="s">
-        <v>1369</v>
-      </c>
-      <c r="H304" s="0" t="s">
-        <v>1370</v>
       </c>
     </row>
     <row r="305">
       <c r="B305" s="0" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E305" s="0" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F305" s="0" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G305" s="0" t="s">
+        <v>1370</v>
+      </c>
+      <c r="H305" s="0" t="s">
         <v>1371</v>
-      </c>
-      <c r="E305" s="0" t="s">
-        <v>1372</v>
-      </c>
-      <c r="F305" s="0" t="s">
-        <v>1373</v>
-      </c>
-      <c r="G305" s="0" t="s">
-        <v>1374</v>
-      </c>
-      <c r="H305" s="0" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="306">
       <c r="B306" s="0" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E306" s="0" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F306" s="0" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G306" s="0" t="s">
+        <v>1375</v>
+      </c>
+      <c r="H306" s="0" t="s">
         <v>1376</v>
-      </c>
-      <c r="E306" s="0" t="s">
-        <v>1377</v>
-      </c>
-      <c r="F306" s="0" t="s">
-        <v>1378</v>
-      </c>
-      <c r="G306" s="0" t="s">
-        <v>1379</v>
-      </c>
-      <c r="H306" s="0" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="307">
       <c r="B307" s="0" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E307" s="0" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F307" s="0" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G307" s="0" t="s">
+        <v>1380</v>
+      </c>
+      <c r="H307" s="0" t="s">
         <v>1381</v>
-      </c>
-      <c r="E307" s="0" t="s">
-        <v>1382</v>
-      </c>
-      <c r="F307" s="0" t="s">
-        <v>1383</v>
-      </c>
-      <c r="G307" s="0" t="s">
-        <v>1384</v>
-      </c>
-      <c r="H307" s="0" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="308">
       <c r="B308" s="0" t="s">
+        <v>1382</v>
+      </c>
+      <c r="E308" s="0" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F308" s="0" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G308" s="0" t="s">
+        <v>1385</v>
+      </c>
+      <c r="H308" s="0" t="s">
         <v>1386</v>
-      </c>
-      <c r="E308" s="0" t="s">
-        <v>1387</v>
-      </c>
-      <c r="F308" s="0" t="s">
-        <v>1388</v>
-      </c>
-      <c r="G308" s="0" t="s">
-        <v>1389</v>
-      </c>
-      <c r="H308" s="0" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="309">
       <c r="B309" s="0" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E309" s="0" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F309" s="0" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G309" s="0" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H309" s="0" t="s">
         <v>1391</v>
-      </c>
-      <c r="E309" s="0" t="s">
-        <v>1392</v>
-      </c>
-      <c r="F309" s="0" t="s">
-        <v>1393</v>
-      </c>
-      <c r="G309" s="0" t="s">
-        <v>1394</v>
-      </c>
-      <c r="H309" s="0" t="s">
-        <v>1395</v>
       </c>
     </row>
     <row r="310">
       <c r="B310" s="0" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E310" s="0" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F310" s="0" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G310" s="0" t="s">
+        <v>1395</v>
+      </c>
+      <c r="H310" s="0" t="s">
         <v>1396</v>
-      </c>
-      <c r="E310" s="0" t="s">
-        <v>1397</v>
-      </c>
-      <c r="F310" s="0" t="s">
-        <v>1398</v>
-      </c>
-      <c r="G310" s="0" t="s">
-        <v>1399</v>
-      </c>
-      <c r="H310" s="0" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="311">
       <c r="B311" s="0" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E311" s="0" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F311" s="0" t="s">
+        <v>1399</v>
+      </c>
+      <c r="G311" s="0" t="s">
+        <v>1400</v>
+      </c>
+      <c r="H311" s="0" t="s">
         <v>1401</v>
-      </c>
-      <c r="E311" s="0" t="s">
-        <v>1402</v>
-      </c>
-      <c r="F311" s="0" t="s">
-        <v>1403</v>
-      </c>
-      <c r="G311" s="0" t="s">
-        <v>1404</v>
-      </c>
-      <c r="H311" s="0" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="312">
       <c r="B312" s="0" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="E312" s="0" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="F312" s="0" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="G312" s="0" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="H312" s="0" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="313">
       <c r="B313" s="0" t="s">
+        <v>1406</v>
+      </c>
+      <c r="E313" s="0" t="s">
+        <v>1407</v>
+      </c>
+      <c r="F313" s="0" t="s">
+        <v>1408</v>
+      </c>
+      <c r="G313" s="0" t="s">
+        <v>1409</v>
+      </c>
+      <c r="H313" s="0" t="s">
         <v>1410</v>
-      </c>
-      <c r="E313" s="0" t="s">
-        <v>1411</v>
-      </c>
-      <c r="F313" s="0" t="s">
-        <v>1412</v>
-      </c>
-      <c r="G313" s="0" t="s">
-        <v>1413</v>
-      </c>
-      <c r="H313" s="0" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="314">
       <c r="B314" s="0" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E314" s="0" t="s">
+        <v>1412</v>
+      </c>
+      <c r="F314" s="0" t="s">
+        <v>1413</v>
+      </c>
+      <c r="G314" s="0" t="s">
+        <v>1414</v>
+      </c>
+      <c r="H314" s="0" t="s">
         <v>1415</v>
-      </c>
-      <c r="E314" s="0" t="s">
-        <v>1416</v>
-      </c>
-      <c r="F314" s="0" t="s">
-        <v>1417</v>
-      </c>
-      <c r="G314" s="0" t="s">
-        <v>1418</v>
-      </c>
-      <c r="H314" s="0" t="s">
-        <v>1419</v>
       </c>
     </row>
     <row r="315">
       <c r="B315" s="0" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E315" s="0" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F315" s="0" t="s">
+        <v>1418</v>
+      </c>
+      <c r="G315" s="0" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H315" s="0" t="s">
         <v>1420</v>
-      </c>
-      <c r="E315" s="0" t="s">
-        <v>1421</v>
-      </c>
-      <c r="F315" s="0" t="s">
-        <v>1422</v>
-      </c>
-      <c r="G315" s="0" t="s">
-        <v>1423</v>
-      </c>
-      <c r="H315" s="0" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="316">
       <c r="B316" s="0" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E316" s="0" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F316" s="0" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G316" s="0" t="s">
+        <v>1424</v>
+      </c>
+      <c r="H316" s="0" t="s">
         <v>1425</v>
-      </c>
-      <c r="E316" s="0" t="s">
-        <v>1426</v>
-      </c>
-      <c r="F316" s="0" t="s">
-        <v>1427</v>
-      </c>
-      <c r="G316" s="0" t="s">
-        <v>1428</v>
-      </c>
-      <c r="H316" s="0" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="317">
       <c r="B317" s="0" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E317" s="0" t="s">
+        <v>1427</v>
+      </c>
+      <c r="F317" s="0" t="s">
+        <v>1428</v>
+      </c>
+      <c r="G317" s="0" t="s">
+        <v>1429</v>
+      </c>
+      <c r="H317" s="0" t="s">
         <v>1430</v>
-      </c>
-      <c r="E317" s="0" t="s">
-        <v>1431</v>
-      </c>
-      <c r="F317" s="0" t="s">
-        <v>1432</v>
-      </c>
-      <c r="G317" s="0" t="s">
-        <v>1433</v>
-      </c>
-      <c r="H317" s="0" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="318">
       <c r="B318" s="0" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E318" s="0" t="s">
+        <v>1432</v>
+      </c>
+      <c r="F318" s="0" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G318" s="0" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H318" s="0" t="s">
         <v>1435</v>
-      </c>
-      <c r="E318" s="0" t="s">
-        <v>1436</v>
-      </c>
-      <c r="F318" s="0" t="s">
-        <v>1437</v>
-      </c>
-      <c r="G318" s="0" t="s">
-        <v>1438</v>
-      </c>
-      <c r="H318" s="0" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="319">
       <c r="B319" s="0" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E319" s="0" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F319" s="0" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G319" s="0" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H319" s="0" t="s">
         <v>1440</v>
-      </c>
-      <c r="E319" s="0" t="s">
-        <v>1441</v>
-      </c>
-      <c r="F319" s="0" t="s">
-        <v>1442</v>
-      </c>
-      <c r="G319" s="0" t="s">
-        <v>1443</v>
-      </c>
-      <c r="H319" s="0" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="320">
       <c r="B320" s="0" t="s">
+        <v>1441</v>
+      </c>
+      <c r="E320" s="0" t="s">
+        <v>1442</v>
+      </c>
+      <c r="F320" s="0" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G320" s="0" t="s">
+        <v>1444</v>
+      </c>
+      <c r="H320" s="0" t="s">
         <v>1445</v>
-      </c>
-      <c r="E320" s="0" t="s">
-        <v>1446</v>
-      </c>
-      <c r="F320" s="0" t="s">
-        <v>1447</v>
-      </c>
-      <c r="G320" s="0" t="s">
-        <v>1448</v>
-      </c>
-      <c r="H320" s="0" t="s">
-        <v>1449</v>
       </c>
     </row>
     <row r="321">
       <c r="B321" s="0" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E321" s="0" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F321" s="0" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G321" s="0" t="s">
+        <v>1449</v>
+      </c>
+      <c r="H321" s="0" t="s">
         <v>1450</v>
-      </c>
-      <c r="E321" s="0" t="s">
-        <v>1451</v>
-      </c>
-      <c r="F321" s="0" t="s">
-        <v>1452</v>
-      </c>
-      <c r="G321" s="0" t="s">
-        <v>1453</v>
-      </c>
-      <c r="H321" s="0" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="322">
       <c r="B322" s="0" t="s">
+        <v>1451</v>
+      </c>
+      <c r="E322" s="0" t="s">
+        <v>1452</v>
+      </c>
+      <c r="F322" s="0" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G322" s="0" t="s">
+        <v>1454</v>
+      </c>
+      <c r="H322" s="0" t="s">
         <v>1455</v>
-      </c>
-      <c r="E322" s="0" t="s">
-        <v>1456</v>
-      </c>
-      <c r="F322" s="0" t="s">
-        <v>1457</v>
-      </c>
-      <c r="G322" s="0" t="s">
-        <v>1458</v>
-      </c>
-      <c r="H322" s="0" t="s">
-        <v>1459</v>
       </c>
     </row>
   </sheetData>
